--- a/research/traditional_assets/database/data/netherlands/netherlands_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_metals_mining.xlsx
@@ -644,10 +644,10 @@
         <v>-0.06663196251952108</v>
       </c>
       <c r="X2">
-        <v>0.1440752617751988</v>
+        <v>0.1440120795195831</v>
       </c>
       <c r="Y2">
-        <v>-0.2107072242947199</v>
+        <v>-0.2106440420391041</v>
       </c>
       <c r="Z2">
         <v>1.526771570387581</v>
@@ -656,10 +656,10 @@
         <v>0.04065899250184814</v>
       </c>
       <c r="AB2">
-        <v>0.08808807374280714</v>
+        <v>0.08806516622131316</v>
       </c>
       <c r="AC2">
-        <v>-0.04742908124095899</v>
+        <v>-0.04740617371946502</v>
       </c>
       <c r="AD2">
         <v>814.9</v>
@@ -775,10 +775,10 @@
         <v>-0.06663196251952108</v>
       </c>
       <c r="X3">
-        <v>0.1440752617751988</v>
+        <v>0.1440120795195831</v>
       </c>
       <c r="Y3">
-        <v>-0.2107072242947199</v>
+        <v>-0.2106440420391041</v>
       </c>
       <c r="Z3">
         <v>1.526771570387581</v>
@@ -787,10 +787,10 @@
         <v>0.04065899250184814</v>
       </c>
       <c r="AB3">
-        <v>0.08808807374280714</v>
+        <v>0.08806516622131316</v>
       </c>
       <c r="AC3">
-        <v>-0.04742908124095899</v>
+        <v>-0.04740617371946502</v>
       </c>
       <c r="AD3">
         <v>814.9</v>
@@ -1127,49 +1127,49 @@
         <v>1.45557655954631</v>
       </c>
       <c r="F2">
-        <v>4.50152500643075</v>
+        <v>4.5318941763865</v>
       </c>
       <c r="G2">
         <v>6.06324404761905</v>
       </c>
       <c r="H2">
-        <v>4.75595238095238</v>
+        <v>4.94619047619048</v>
       </c>
       <c r="I2">
         <v>0.637437421777222</v>
       </c>
       <c r="J2">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="K2">
         <v>463.5</v>
       </c>
       <c r="L2">
-        <v>824.1953944292</v>
+        <v>843.098821662859</v>
       </c>
       <c r="M2">
         <v>1006.8</v>
       </c>
       <c r="N2">
-        <v>1191.7953944292</v>
+        <v>1236.26682166286</v>
       </c>
       <c r="O2">
         <v>814.9</v>
       </c>
       <c r="P2">
-        <v>639.2</v>
+        <v>664.768</v>
       </c>
       <c r="Q2">
-        <v>0.0880880737428071</v>
+        <v>0.0880651662213132</v>
       </c>
       <c r="R2">
-        <v>0.0815239445992737</v>
+        <v>0.08022021463811679</v>
       </c>
       <c r="S2">
         <v>0.0562436</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.144075261775199</v>
+        <v>0.144012079519583</v>
       </c>
       <c r="X2">
-        <v>0.120086089198547</v>
+        <v>0.12267346382941</v>
       </c>
       <c r="Y2">
         <v>2.26817735611046</v>
       </c>
       <c r="Z2">
-        <v>1.71451108194015</v>
+        <v>1.77536867966305</v>
       </c>
       <c r="AA2">
         <v>814.9000000000001</v>
@@ -1224,7 +1224,7 @@
         <v>463.5</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08844413846070455</v>
+        <v>0.08841672207118731</v>
       </c>
       <c r="C2">
-        <v>1269.993546711949</v>
+        <v>1270.094658517799</v>
       </c>
       <c r="D2">
-        <v>998.3935467119485</v>
+        <v>998.4946585177984</v>
       </c>
       <c r="E2">
         <v>-814.9000000000001</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08844413846070455</v>
+        <v>0.08841672207118731</v>
       </c>
       <c r="T2">
         <v>0.9842199092652959</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08825973058347591</v>
+        <v>0.08822199692824366</v>
       </c>
       <c r="C3">
-        <v>1261.545693740153</v>
+        <v>1261.893941465021</v>
       </c>
       <c r="D3">
-        <v>1002.729693740153</v>
+        <v>1003.077941465021</v>
       </c>
       <c r="E3">
         <v>-802.1160000000001</v>
@@ -1527,37 +1527,37 @@
         <v>166.6</v>
       </c>
       <c r="M3">
-        <v>0.6609328000000002</v>
+        <v>0.6430352000000001</v>
       </c>
       <c r="N3">
-        <v>165.9390672</v>
+        <v>165.9569648</v>
       </c>
       <c r="O3">
-        <v>42.8122793376</v>
+        <v>42.8168969184</v>
       </c>
       <c r="P3">
-        <v>123.1267878624</v>
+        <v>123.1400678816</v>
       </c>
       <c r="Q3">
-        <v>180.5267878624</v>
+        <v>180.5400678816</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08876375412472315</v>
+        <v>0.08873613225075117</v>
       </c>
       <c r="T3">
         <v>0.991596587777163</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>252.0679863368862</v>
+        <v>259.08379510173</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08807532270624731</v>
+        <v>0.08802727178529997</v>
       </c>
       <c r="C4">
-        <v>1253.135669913951</v>
+        <v>1253.735494745577</v>
       </c>
       <c r="D4">
-        <v>1007.103669913951</v>
+        <v>1007.703494745577</v>
       </c>
       <c r="E4">
         <v>-789.3320000000001</v>
@@ -1609,37 +1609,37 @@
         <v>166.6</v>
       </c>
       <c r="M4">
-        <v>1.3218656</v>
+        <v>1.2860704</v>
       </c>
       <c r="N4">
-        <v>165.2781344</v>
+        <v>165.3139296</v>
       </c>
       <c r="O4">
-        <v>42.64175867520001</v>
+        <v>42.6509938368</v>
       </c>
       <c r="P4">
-        <v>122.6363757248</v>
+        <v>122.6629357632</v>
       </c>
       <c r="Q4">
-        <v>180.0363757248</v>
+        <v>180.0629357632</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08908989255739522</v>
+        <v>0.08906206100540814</v>
       </c>
       <c r="T4">
         <v>0.9991238107484561</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>126.0339931684431</v>
+        <v>129.541897550865</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08789091482901867</v>
+        <v>0.08783254664235632</v>
       </c>
       <c r="C5">
-        <v>1244.763972442238</v>
+        <v>1245.619905839694</v>
       </c>
       <c r="D5">
-        <v>1011.515972442238</v>
+        <v>1012.371905839694</v>
       </c>
       <c r="E5">
         <v>-776.5480000000001</v>
@@ -1691,37 +1691,37 @@
         <v>166.6</v>
       </c>
       <c r="M5">
-        <v>1.982798400000001</v>
+        <v>1.9291056</v>
       </c>
       <c r="N5">
-        <v>164.6172016</v>
+        <v>164.6708944</v>
       </c>
       <c r="O5">
-        <v>42.47123801280001</v>
+        <v>42.48509075520001</v>
       </c>
       <c r="P5">
-        <v>122.1459635872</v>
+        <v>122.1858036448</v>
       </c>
       <c r="Q5">
-        <v>179.5459635872</v>
+        <v>179.5858036448</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08942275549383369</v>
+        <v>0.08939470994057352</v>
       </c>
       <c r="T5">
         <v>1.006806234193384</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>84.02266211229542</v>
+        <v>86.36126503391</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08770650695179008</v>
+        <v>0.08763782149941265</v>
       </c>
       <c r="C6">
-        <v>1236.431107285699</v>
+        <v>1237.547773164802</v>
       </c>
       <c r="D6">
-        <v>1015.9671072857</v>
+        <v>1017.083773164802</v>
       </c>
       <c r="E6">
         <v>-763.7640000000001</v>
@@ -1773,37 +1773,37 @@
         <v>166.6</v>
       </c>
       <c r="M6">
-        <v>2.643731200000001</v>
+        <v>2.572140800000001</v>
       </c>
       <c r="N6">
-        <v>163.9562688</v>
+        <v>164.0278592</v>
       </c>
       <c r="O6">
-        <v>42.30071735040001</v>
+        <v>42.31918767360001</v>
       </c>
       <c r="P6">
-        <v>121.6555514496</v>
+        <v>121.7086715264</v>
       </c>
       <c r="Q6">
-        <v>179.0555514496</v>
+        <v>179.1086715264</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08976255307478133</v>
+        <v>0.08973428906188818</v>
       </c>
       <c r="T6">
         <v>1.014648708126748</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.01699658422157</v>
+        <v>64.77094877543252</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08752209907456146</v>
+        <v>0.08744309635646899</v>
       </c>
       <c r="C7">
-        <v>1228.137589350225</v>
+        <v>1229.519706331247</v>
       </c>
       <c r="D7">
-        <v>1020.457589350225</v>
+        <v>1021.839706331247</v>
       </c>
       <c r="E7">
         <v>-750.9800000000001</v>
@@ -1855,37 +1855,37 @@
         <v>166.6</v>
       </c>
       <c r="M7">
-        <v>3.304664000000001</v>
+        <v>3.215176000000001</v>
       </c>
       <c r="N7">
-        <v>163.295336</v>
+        <v>163.384824</v>
       </c>
       <c r="O7">
-        <v>42.13019668800001</v>
+        <v>42.15328459200001</v>
       </c>
       <c r="P7">
-        <v>121.165139312</v>
+        <v>121.231539408</v>
       </c>
       <c r="Q7">
-        <v>178.565139312</v>
+        <v>178.631539408</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09010950428901207</v>
+        <v>0.09008101721733579</v>
       </c>
       <c r="T7">
         <v>1.022656286774499</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>50.41359726737725</v>
+        <v>51.816759020346</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08733769119733283</v>
+        <v>0.08724837121352533</v>
       </c>
       <c r="C8">
-        <v>1219.883942685463</v>
+        <v>1221.536326405213</v>
       </c>
       <c r="D8">
-        <v>1024.987942685463</v>
+        <v>1026.640326405213</v>
       </c>
       <c r="E8">
         <v>-738.1960000000001</v>
@@ -1937,37 +1937,37 @@
         <v>166.6</v>
       </c>
       <c r="M8">
-        <v>3.965596800000001</v>
+        <v>3.858211200000001</v>
       </c>
       <c r="N8">
-        <v>162.6344032</v>
+        <v>162.7417888</v>
       </c>
       <c r="O8">
-        <v>41.9596760256</v>
+        <v>41.98738151040001</v>
       </c>
       <c r="P8">
-        <v>120.6747271744</v>
+        <v>120.7544072896</v>
       </c>
       <c r="Q8">
-        <v>178.0747271744</v>
+        <v>178.1544072896</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0904638374439711</v>
+        <v>0.09043512256758014</v>
       </c>
       <c r="T8">
         <v>1.030834239436031</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.0113310561477</v>
+        <v>43.18063251695501</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08715328332010422</v>
+        <v>0.08705364607058166</v>
       </c>
       <c r="C9">
-        <v>1211.670700688701</v>
+        <v>1213.598266179093</v>
       </c>
       <c r="D9">
-        <v>1029.558700688701</v>
+        <v>1031.486266179093</v>
       </c>
       <c r="E9">
         <v>-725.412</v>
@@ -2019,37 +2019,37 @@
         <v>166.6</v>
       </c>
       <c r="M9">
-        <v>4.626529600000001</v>
+        <v>4.501246400000001</v>
       </c>
       <c r="N9">
-        <v>161.9734704</v>
+        <v>162.0987536</v>
       </c>
       <c r="O9">
-        <v>41.78915536320001</v>
+        <v>41.82147842880001</v>
       </c>
       <c r="P9">
-        <v>120.1843150368</v>
+        <v>120.2772751712</v>
       </c>
       <c r="Q9">
-        <v>177.5843150368</v>
+        <v>177.6772751712</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09082579066677873</v>
+        <v>0.09079684308664696</v>
       </c>
       <c r="T9">
         <v>1.039188062047274</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.00971233384089</v>
+        <v>37.01197072881857</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08696887544287563</v>
+        <v>0.08685892092763801</v>
       </c>
       <c r="C10">
-        <v>1203.498406314221</v>
+        <v>1205.706170449547</v>
       </c>
       <c r="D10">
-        <v>1034.170406314221</v>
+        <v>1036.378170449547</v>
       </c>
       <c r="E10">
         <v>-712.628</v>
@@ -2101,37 +2101,37 @@
         <v>166.6</v>
       </c>
       <c r="M10">
-        <v>5.287462400000002</v>
+        <v>5.144281600000001</v>
       </c>
       <c r="N10">
-        <v>161.3125376</v>
+        <v>161.4557184</v>
       </c>
       <c r="O10">
-        <v>41.6186347008</v>
+        <v>41.65557534720001</v>
       </c>
       <c r="P10">
-        <v>119.6939028992</v>
+        <v>119.8001430528</v>
       </c>
       <c r="Q10">
-        <v>177.0939028992</v>
+        <v>177.2001430528</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09119561243790827</v>
+        <v>0.0911664270952587</v>
       </c>
       <c r="T10">
         <v>1.047723489497892</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.50849829211078</v>
+        <v>32.38547438771626</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08678446756564699</v>
+        <v>0.08666419578469434</v>
       </c>
       <c r="C11">
-        <v>1195.367612288304</v>
+        <v>1197.860696303519</v>
       </c>
       <c r="D11">
-        <v>1038.823612288304</v>
+        <v>1041.316696303519</v>
       </c>
       <c r="E11">
         <v>-699.8440000000001</v>
@@ -2183,37 +2183,37 @@
         <v>166.6</v>
       </c>
       <c r="M11">
-        <v>5.948395200000001</v>
+        <v>5.7873168</v>
       </c>
       <c r="N11">
-        <v>160.6516048</v>
+        <v>160.8126832</v>
       </c>
       <c r="O11">
-        <v>41.44811403840001</v>
+        <v>41.48967226560001</v>
       </c>
       <c r="P11">
-        <v>119.2034907616</v>
+        <v>119.3230109344</v>
       </c>
       <c r="Q11">
-        <v>176.6034907616</v>
+        <v>176.7230109344</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09157356216005164</v>
+        <v>0.09154413382933443</v>
       </c>
       <c r="T11">
         <v>1.056446508760611</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.00755403743181</v>
+        <v>28.78708834463667</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08660005968841838</v>
+        <v>0.08646947064175069</v>
       </c>
       <c r="C12">
-        <v>1187.278881330065</v>
+        <v>1190.062513412462</v>
       </c>
       <c r="D12">
-        <v>1043.518881330065</v>
+        <v>1046.302513412462</v>
       </c>
       <c r="E12">
         <v>-687.0600000000001</v>
@@ -2265,37 +2265,37 @@
         <v>166.6</v>
       </c>
       <c r="M12">
-        <v>6.609328000000002</v>
+        <v>6.430352000000002</v>
       </c>
       <c r="N12">
-        <v>159.990672</v>
+        <v>160.169648</v>
       </c>
       <c r="O12">
-        <v>41.27759337600001</v>
+        <v>41.32376918400001</v>
       </c>
       <c r="P12">
-        <v>118.713078624</v>
+        <v>118.845878816</v>
       </c>
       <c r="Q12">
-        <v>176.113078624</v>
+        <v>176.245878816</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09195991076490931</v>
+        <v>0.09193023404638964</v>
       </c>
       <c r="T12">
         <v>1.065363372895835</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.20679863368862</v>
+        <v>25.908379510173</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08641565181118976</v>
+        <v>0.08627474549880702</v>
       </c>
       <c r="C13">
-        <v>1179.232786378311</v>
+        <v>1182.312304335065</v>
       </c>
       <c r="D13">
-        <v>1048.256786378312</v>
+        <v>1051.336304335065</v>
       </c>
       <c r="E13">
         <v>-674.2760000000001</v>
@@ -2347,37 +2347,37 @@
         <v>166.6</v>
       </c>
       <c r="M13">
-        <v>7.270260800000003</v>
+        <v>7.073387200000002</v>
       </c>
       <c r="N13">
-        <v>159.3297392</v>
+        <v>159.5266128</v>
       </c>
       <c r="O13">
-        <v>41.1070727136</v>
+        <v>41.15786610240001</v>
       </c>
       <c r="P13">
-        <v>118.2226664864</v>
+        <v>118.3687466976</v>
       </c>
       <c r="Q13">
-        <v>175.6226664864</v>
+        <v>175.7687466976</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09235494136088737</v>
+        <v>0.09232501067281687</v>
       </c>
       <c r="T13">
         <v>1.07448061600039</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.91527148517147</v>
+        <v>23.55307228197545</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08623124393396114</v>
+        <v>0.08608002035586335</v>
       </c>
       <c r="C14">
-        <v>1171.2299108246</v>
+        <v>1174.610764828751</v>
       </c>
       <c r="D14">
-        <v>1053.0379108246</v>
+        <v>1056.418764828751</v>
       </c>
       <c r="E14">
         <v>-661.4920000000001</v>
@@ -2429,37 +2429,37 @@
         <v>166.6</v>
       </c>
       <c r="M14">
-        <v>7.931193600000002</v>
+        <v>7.716422400000002</v>
       </c>
       <c r="N14">
-        <v>158.6688064</v>
+        <v>158.8835776</v>
       </c>
       <c r="O14">
-        <v>40.93655205120001</v>
+        <v>40.99196302080001</v>
       </c>
       <c r="P14">
-        <v>117.7322543488</v>
+        <v>117.8916145792</v>
       </c>
       <c r="Q14">
-        <v>175.1322543488</v>
+        <v>175.2916145792</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09275894992495584</v>
+        <v>0.09272875949529927</v>
       </c>
       <c r="T14">
         <v>1.083805069175503</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.00566552807386</v>
+        <v>21.5903162584775</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08604683605673252</v>
+        <v>0.08588529521291968</v>
       </c>
       <c r="C15">
-        <v>1163.270848752707</v>
+        <v>1166.958604170259</v>
       </c>
       <c r="D15">
-        <v>1057.862848752707</v>
+        <v>1061.550604170259</v>
       </c>
       <c r="E15">
         <v>-648.7080000000001</v>
@@ -2511,37 +2511,37 @@
         <v>166.6</v>
       </c>
       <c r="M15">
-        <v>8.592126400000001</v>
+        <v>8.359457600000001</v>
       </c>
       <c r="N15">
-        <v>158.0078736</v>
+        <v>158.2405424</v>
       </c>
       <c r="O15">
-        <v>40.7660313888</v>
+        <v>40.8260599392</v>
       </c>
       <c r="P15">
-        <v>117.2418422112</v>
+        <v>117.4144824608</v>
       </c>
       <c r="Q15">
-        <v>174.6418422112</v>
+        <v>174.8144824608</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09317224604222128</v>
+        <v>0.09314178989990768</v>
       </c>
       <c r="T15">
         <v>1.09334387759602</v>
       </c>
       <c r="U15">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.38984510283741</v>
+        <v>19.92952270013308</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0858624281795039</v>
+        <v>0.08569057006997603</v>
       </c>
       <c r="C16">
-        <v>1155.356205184709</v>
+        <v>1159.356545485622</v>
       </c>
       <c r="D16">
-        <v>1062.73220518471</v>
+        <v>1066.732545485622</v>
       </c>
       <c r="E16">
         <v>-635.9240000000001</v>
@@ -2593,37 +2593,37 @@
         <v>166.6</v>
       </c>
       <c r="M16">
-        <v>9.253059200000003</v>
+        <v>9.002492800000002</v>
       </c>
       <c r="N16">
-        <v>157.3469408</v>
+        <v>157.5975072</v>
       </c>
       <c r="O16">
-        <v>40.59551072640001</v>
+        <v>40.66015685760001</v>
       </c>
       <c r="P16">
-        <v>116.7514300736</v>
+        <v>116.9373503424</v>
       </c>
       <c r="Q16">
-        <v>174.1514300736</v>
+        <v>174.3373503424</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09359515369709756</v>
+        <v>0.09356442566276282</v>
       </c>
       <c r="T16">
         <v>1.103104518770504</v>
       </c>
       <c r="U16">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.00485616692045</v>
+        <v>18.50598536440929</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08567802030227527</v>
+        <v>0.08549584492703236</v>
       </c>
       <c r="C17">
-        <v>1147.486596333897</v>
+        <v>1151.805326089843</v>
       </c>
       <c r="D17">
-        <v>1067.646596333897</v>
+        <v>1071.965326089844</v>
       </c>
       <c r="E17">
         <v>-623.1400000000001</v>
@@ -2675,37 +2675,37 @@
         <v>166.6</v>
       </c>
       <c r="M17">
-        <v>9.913992000000002</v>
+        <v>9.645528000000002</v>
       </c>
       <c r="N17">
-        <v>156.686008</v>
+        <v>156.954472</v>
       </c>
       <c r="O17">
-        <v>40.42499006400001</v>
+        <v>40.494253776</v>
       </c>
       <c r="P17">
-        <v>116.261017936</v>
+        <v>116.460218224</v>
       </c>
       <c r="Q17">
-        <v>173.661017936</v>
+        <v>173.860218224</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09402801212032386</v>
+        <v>0.09399700579650866</v>
       </c>
       <c r="T17">
         <v>1.113094822090269</v>
       </c>
       <c r="U17">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.80453242245908</v>
+        <v>17.272253006782</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08549361242504665</v>
+        <v>0.08530111978408869</v>
       </c>
       <c r="C18">
-        <v>1139.662649864728</v>
+        <v>1144.305697836631</v>
       </c>
       <c r="D18">
-        <v>1072.606649864728</v>
+        <v>1077.249697836631</v>
       </c>
       <c r="E18">
         <v>-610.3560000000001</v>
@@ -2757,37 +2757,37 @@
         <v>166.6</v>
       </c>
       <c r="M18">
-        <v>10.5749248</v>
+        <v>10.2885632</v>
       </c>
       <c r="N18">
-        <v>156.0250752</v>
+        <v>156.3114368</v>
       </c>
       <c r="O18">
-        <v>40.25446940160001</v>
+        <v>40.32835069440001</v>
       </c>
       <c r="P18">
-        <v>115.7706057984</v>
+        <v>115.9830861056</v>
       </c>
       <c r="Q18">
-        <v>173.1706057984</v>
+        <v>173.3830861056</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09447117669648411</v>
+        <v>0.09443988545724845</v>
       </c>
       <c r="T18">
         <v>1.123322989774791</v>
       </c>
       <c r="U18">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.75424914605539</v>
+        <v>16.19273719385813</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08530920454781805</v>
+        <v>0.08510639464114504</v>
       </c>
       <c r="C19">
-        <v>1131.885005160073</v>
+        <v>1136.858427478521</v>
       </c>
       <c r="D19">
-        <v>1077.613005160073</v>
+        <v>1082.586427478521</v>
       </c>
       <c r="E19">
         <v>-597.5720000000001</v>
@@ -2839,37 +2839,37 @@
         <v>166.6</v>
       </c>
       <c r="M19">
-        <v>11.2358576</v>
+        <v>10.9315984</v>
       </c>
       <c r="N19">
-        <v>155.3641424</v>
+        <v>155.6684016</v>
       </c>
       <c r="O19">
-        <v>40.0839487392</v>
+        <v>40.1624476128</v>
       </c>
       <c r="P19">
-        <v>115.2801936608</v>
+        <v>115.5059539872</v>
       </c>
       <c r="Q19">
-        <v>172.6801936608</v>
+        <v>172.9059539872</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09492501993713018</v>
+        <v>0.09489343691704222</v>
       </c>
       <c r="T19">
         <v>1.133797619331229</v>
       </c>
       <c r="U19">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.82752860805213</v>
+        <v>15.24022324127824</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08512479667058942</v>
+        <v>0.08491166949820136</v>
       </c>
       <c r="C20">
-        <v>1124.154313595973</v>
+        <v>1129.464297037767</v>
       </c>
       <c r="D20">
-        <v>1082.666313595973</v>
+        <v>1087.976297037767</v>
       </c>
       <c r="E20">
         <v>-584.7880000000001</v>
@@ -2921,37 +2921,37 @@
         <v>166.6</v>
       </c>
       <c r="M20">
-        <v>11.8967904</v>
+        <v>11.5746336</v>
       </c>
       <c r="N20">
-        <v>154.7032096</v>
+        <v>155.0253664</v>
       </c>
       <c r="O20">
-        <v>39.9134280768</v>
+        <v>39.99654453120001</v>
       </c>
       <c r="P20">
-        <v>114.7897815232</v>
+        <v>115.0288218688</v>
       </c>
       <c r="Q20">
-        <v>172.1897815232</v>
+        <v>172.4288218688</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09538993252510905</v>
+        <v>0.09535805060756264</v>
       </c>
       <c r="T20">
         <v>1.144527727657336</v>
       </c>
       <c r="U20">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.0037770187159</v>
+        <v>14.39354417231834</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08494038879336081</v>
+        <v>0.08471694435525771</v>
       </c>
       <c r="C21">
-        <v>1116.471238824161</v>
+        <v>1122.12410418835</v>
       </c>
       <c r="D21">
-        <v>1087.767238824161</v>
+        <v>1093.42010418835</v>
       </c>
       <c r="E21">
         <v>-572.0040000000001</v>
@@ -3003,37 +3003,37 @@
         <v>166.6</v>
       </c>
       <c r="M21">
-        <v>12.5577232</v>
+        <v>12.2176688</v>
       </c>
       <c r="N21">
-        <v>154.0422768</v>
+        <v>154.3823312</v>
       </c>
       <c r="O21">
-        <v>39.74290741440001</v>
+        <v>39.8306414496</v>
       </c>
       <c r="P21">
-        <v>114.2993693856</v>
+        <v>114.5516897504</v>
       </c>
       <c r="Q21">
-        <v>171.6993693856</v>
+        <v>171.9516897504</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09586632443624792</v>
+        <v>0.09583413624105891</v>
       </c>
       <c r="T21">
         <v>1.155522776929767</v>
       </c>
       <c r="U21">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.26673612299401</v>
+        <v>13.63598921588053</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.0849192209161322</v>
+        <v>0.08452221921231405</v>
       </c>
       <c r="C22">
-        <v>1104.275842656893</v>
+        <v>1114.83866264953</v>
       </c>
       <c r="D22">
-        <v>1088.355842656893</v>
+        <v>1098.91866264953</v>
       </c>
       <c r="E22">
         <v>-559.22</v>
@@ -3085,45 +3085,45 @@
         <v>166.6</v>
       </c>
       <c r="M22">
-        <v>13.499904</v>
+        <v>12.860704</v>
       </c>
       <c r="N22">
-        <v>153.100096</v>
+        <v>153.739296</v>
       </c>
       <c r="O22">
-        <v>39.499824768</v>
+        <v>39.66473836800001</v>
       </c>
       <c r="P22">
-        <v>113.600271232</v>
+        <v>114.074557632</v>
       </c>
       <c r="Q22">
-        <v>171.000271232</v>
+        <v>171.474557632</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09635462614516524</v>
+        <v>0.09632212401539256</v>
       </c>
       <c r="T22">
         <v>1.166792702434008</v>
       </c>
       <c r="U22">
-        <v>0.05280000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.03917760000000001</v>
+        <v>0.0373226</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>12.34082849774339</v>
+        <v>12.9541897550865</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08474297503890357</v>
+        <v>0.08456122406937039</v>
       </c>
       <c r="C23">
-        <v>1096.417460949649</v>
+        <v>1100.948836753101</v>
       </c>
       <c r="D23">
-        <v>1093.281460949649</v>
+        <v>1097.812836753101</v>
       </c>
       <c r="E23">
         <v>-546.4360000000001</v>
@@ -3167,37 +3167,37 @@
         <v>166.6</v>
       </c>
       <c r="M23">
-        <v>14.1748992</v>
+        <v>13.9064352</v>
       </c>
       <c r="N23">
-        <v>152.4251008</v>
+        <v>152.6935648</v>
       </c>
       <c r="O23">
-        <v>39.32567600640001</v>
+        <v>39.3949397184</v>
       </c>
       <c r="P23">
-        <v>113.0994247936</v>
+        <v>113.2986250816</v>
       </c>
       <c r="Q23">
-        <v>170.4994247936</v>
+        <v>170.6986250816</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09685528992266274</v>
+        <v>0.09682246591059541</v>
       </c>
       <c r="T23">
         <v>1.178347942507977</v>
       </c>
       <c r="U23">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.03917760000000001</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.75316999785085</v>
+        <v>11.98006517155453</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08456672916167497</v>
+        <v>0.08437762892642672</v>
       </c>
       <c r="C24">
-        <v>1088.60386609627</v>
+        <v>1093.389447759482</v>
       </c>
       <c r="D24">
-        <v>1098.25186609627</v>
+        <v>1103.037447759482</v>
       </c>
       <c r="E24">
         <v>-533.652</v>
@@ -3249,37 +3249,37 @@
         <v>166.6</v>
       </c>
       <c r="M24">
-        <v>14.8498944</v>
+        <v>14.5686464</v>
       </c>
       <c r="N24">
-        <v>151.7501056</v>
+        <v>152.0313536</v>
       </c>
       <c r="O24">
-        <v>39.15152724480001</v>
+        <v>39.2240892288</v>
       </c>
       <c r="P24">
-        <v>112.5985783552</v>
+        <v>112.8072643712</v>
       </c>
       <c r="Q24">
-        <v>169.9985783552</v>
+        <v>170.2072643712</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09736879123291661</v>
+        <v>0.09733563708516246</v>
       </c>
       <c r="T24">
         <v>1.190199470788971</v>
       </c>
       <c r="U24">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.03917760000000001</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.21893499794854</v>
+        <v>11.43551675466569</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08439048328444634</v>
+        <v>0.08419403378348306</v>
       </c>
       <c r="C25">
-        <v>1080.835671732374</v>
+        <v>1085.880025550283</v>
       </c>
       <c r="D25">
-        <v>1103.267671732374</v>
+        <v>1108.312025550283</v>
       </c>
       <c r="E25">
         <v>-520.8680000000001</v>
@@ -3331,37 +3331,37 @@
         <v>166.6</v>
       </c>
       <c r="M25">
-        <v>15.5248896</v>
+        <v>15.2308576</v>
       </c>
       <c r="N25">
-        <v>151.0751104</v>
+        <v>151.3691424</v>
       </c>
       <c r="O25">
-        <v>38.97737848320001</v>
+        <v>39.0532387392</v>
       </c>
       <c r="P25">
-        <v>112.0977319168</v>
+        <v>112.3159036608</v>
       </c>
       <c r="Q25">
-        <v>169.4977319168</v>
+        <v>169.7159036608</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0978956302395407</v>
+        <v>0.09786213738114682</v>
       </c>
       <c r="T25">
         <v>1.202358830973368</v>
       </c>
       <c r="U25">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.03917760000000001</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.73115521542904</v>
+        <v>10.93832037402805</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08421423740721773</v>
+        <v>0.08401043864053939</v>
       </c>
       <c r="C26">
-        <v>1073.113502755107</v>
+        <v>1078.421290373105</v>
       </c>
       <c r="D26">
-        <v>1108.329502755106</v>
+        <v>1113.637290373105</v>
       </c>
       <c r="E26">
         <v>-508.0840000000001</v>
@@ -3413,37 +3413,37 @@
         <v>166.6</v>
       </c>
       <c r="M26">
-        <v>16.1998848</v>
+        <v>15.8930688</v>
       </c>
       <c r="N26">
-        <v>150.4001152</v>
+        <v>150.7069312</v>
       </c>
       <c r="O26">
-        <v>38.8032297216</v>
+        <v>38.88238824960001</v>
       </c>
       <c r="P26">
-        <v>111.5968854784</v>
+        <v>111.8245429504</v>
       </c>
       <c r="Q26">
-        <v>168.9968854784</v>
+        <v>169.2245429504</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09843633343054964</v>
+        <v>0.09840249294807815</v>
       </c>
       <c r="T26">
         <v>1.214838174320512</v>
       </c>
       <c r="U26">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.03917760000000001</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.28402374811949</v>
+        <v>10.48255702511022</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08444609152998911</v>
+        <v>0.08382684349759573</v>
       </c>
       <c r="C27">
-        <v>1053.680168904528</v>
+        <v>1071.01397638509</v>
       </c>
       <c r="D27">
-        <v>1101.680168904528</v>
+        <v>1119.01397638509</v>
       </c>
       <c r="E27">
         <v>-495.3000000000001</v>
@@ -3495,45 +3495,45 @@
         <v>166.6</v>
       </c>
       <c r="M27">
-        <v>17.578</v>
+        <v>16.55528</v>
       </c>
       <c r="N27">
-        <v>149.022</v>
+        <v>150.04472</v>
       </c>
       <c r="O27">
-        <v>38.44767600000001</v>
+        <v>38.71153776000001</v>
       </c>
       <c r="P27">
-        <v>110.574324</v>
+        <v>111.33318224</v>
       </c>
       <c r="Q27">
-        <v>167.974324</v>
+        <v>168.73318224</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09899145537331881</v>
+        <v>0.09895725799679431</v>
       </c>
       <c r="T27">
         <v>1.227650300156913</v>
       </c>
       <c r="U27">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.04081000000000001</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.477756286266924</v>
+        <v>10.06325474410581</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08428616965276048</v>
+        <v>0.08397121235465206</v>
       </c>
       <c r="C28">
-        <v>1045.47398899695</v>
+        <v>1053.997709217367</v>
       </c>
       <c r="D28">
-        <v>1106.25798899695</v>
+        <v>1114.781709217367</v>
       </c>
       <c r="E28">
         <v>-482.5160000000001</v>
@@ -3577,37 +3577,37 @@
         <v>166.6</v>
       </c>
       <c r="M28">
-        <v>18.28112</v>
+        <v>17.782544</v>
       </c>
       <c r="N28">
-        <v>148.31888</v>
+        <v>148.817456</v>
       </c>
       <c r="O28">
-        <v>38.26627104</v>
+        <v>38.394903648</v>
       </c>
       <c r="P28">
-        <v>110.05260896</v>
+        <v>110.422552352</v>
       </c>
       <c r="Q28">
-        <v>167.45260896</v>
+        <v>167.822552352</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09956158061183849</v>
+        <v>0.09952701669547576</v>
       </c>
       <c r="T28">
         <v>1.240808699664567</v>
       </c>
       <c r="U28">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.04081000000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.113227198333579</v>
+        <v>9.368738241277514</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08412624777553188</v>
+        <v>0.0838002312117084</v>
       </c>
       <c r="C29">
-        <v>1037.306012337812</v>
+        <v>1046.229643191894</v>
       </c>
       <c r="D29">
-        <v>1110.874012337812</v>
+        <v>1119.797643191893</v>
       </c>
       <c r="E29">
         <v>-469.732</v>
@@ -3659,37 +3659,37 @@
         <v>166.6</v>
       </c>
       <c r="M29">
-        <v>18.98424000000001</v>
+        <v>18.46648800000001</v>
       </c>
       <c r="N29">
-        <v>147.61576</v>
+        <v>148.133512</v>
       </c>
       <c r="O29">
-        <v>38.08486608</v>
+        <v>38.21844609600001</v>
       </c>
       <c r="P29">
-        <v>109.53089392</v>
+        <v>109.915065904</v>
       </c>
       <c r="Q29">
-        <v>166.93089392</v>
+        <v>167.315065904</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1001473257199067</v>
+        <v>0.1001123852215184</v>
       </c>
       <c r="T29">
         <v>1.254327603268323</v>
       </c>
       <c r="U29">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.04081000000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.775700265061966</v>
+        <v>9.021747936045012</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08396632589830325</v>
+        <v>0.08362925006876473</v>
       </c>
       <c r="C30">
-        <v>1029.176719156879</v>
+        <v>1038.506919335368</v>
       </c>
       <c r="D30">
-        <v>1115.528719156879</v>
+        <v>1124.858919335368</v>
       </c>
       <c r="E30">
         <v>-456.948</v>
@@ -3741,37 +3741,37 @@
         <v>166.6</v>
       </c>
       <c r="M30">
-        <v>19.68736000000001</v>
+        <v>19.15043200000001</v>
       </c>
       <c r="N30">
-        <v>146.91264</v>
+        <v>147.449568</v>
       </c>
       <c r="O30">
-        <v>37.90346112</v>
+        <v>38.04198854400001</v>
       </c>
       <c r="P30">
-        <v>109.00917888</v>
+        <v>109.407579456</v>
       </c>
       <c r="Q30">
-        <v>166.40917888</v>
+        <v>166.807579456</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1007493415254212</v>
+        <v>0.1007140139843955</v>
       </c>
       <c r="T30">
         <v>1.268222031972182</v>
       </c>
       <c r="U30">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.04081000000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.46228239845261</v>
+        <v>8.699542652614834</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08380640402107463</v>
+        <v>0.08345826892582107</v>
       </c>
       <c r="C31">
-        <v>1021.08659776668</v>
+        <v>1030.830155253652</v>
       </c>
       <c r="D31">
-        <v>1120.22259776668</v>
+        <v>1129.966155253652</v>
       </c>
       <c r="E31">
         <v>-444.1640000000001</v>
@@ -3823,37 +3823,37 @@
         <v>166.6</v>
       </c>
       <c r="M31">
-        <v>20.39048</v>
+        <v>19.834376</v>
       </c>
       <c r="N31">
-        <v>146.20952</v>
+        <v>146.765624</v>
       </c>
       <c r="O31">
-        <v>37.72205616000001</v>
+        <v>37.86553099200001</v>
       </c>
       <c r="P31">
-        <v>108.48746384</v>
+        <v>108.900093008</v>
       </c>
       <c r="Q31">
-        <v>165.88746384</v>
+        <v>166.300093008</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1013683155226403</v>
+        <v>0.1013325900363677</v>
       </c>
       <c r="T31">
         <v>1.282507853033896</v>
       </c>
       <c r="U31">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.04081000000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.170479557126658</v>
+        <v>8.399558423214323</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08364648214384601</v>
+        <v>0.08328728778287742</v>
       </c>
       <c r="C32">
-        <v>1013.036144733288</v>
+        <v>1023.199979820313</v>
       </c>
       <c r="D32">
-        <v>1124.956144733288</v>
+        <v>1135.119979820313</v>
       </c>
       <c r="E32">
         <v>-431.3800000000001</v>
@@ -3905,37 +3905,37 @@
         <v>166.6</v>
       </c>
       <c r="M32">
-        <v>21.09360000000001</v>
+        <v>20.51832</v>
       </c>
       <c r="N32">
-        <v>145.5064</v>
+        <v>146.08168</v>
       </c>
       <c r="O32">
-        <v>37.54065120000001</v>
+        <v>37.68907344</v>
       </c>
       <c r="P32">
-        <v>107.9657488</v>
+        <v>108.39260656</v>
       </c>
       <c r="Q32">
-        <v>165.3657488</v>
+        <v>165.79260656</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1020049744912086</v>
+        <v>0.1019688396898249</v>
       </c>
       <c r="T32">
         <v>1.29720184041166</v>
       </c>
       <c r="U32">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.04081000000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.898130238555769</v>
+        <v>8.119573142440512</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08383159026661739</v>
+        <v>0.08311630663993375</v>
       </c>
       <c r="C33">
-        <v>994.7767355092224</v>
+        <v>1015.617033434772</v>
       </c>
       <c r="D33">
-        <v>1119.480735509223</v>
+        <v>1140.321033434772</v>
       </c>
       <c r="E33">
         <v>-418.5960000000001</v>
@@ -3987,45 +3987,45 @@
         <v>166.6</v>
       </c>
       <c r="M33">
-        <v>22.39117600000001</v>
+        <v>21.202264</v>
       </c>
       <c r="N33">
-        <v>144.208824</v>
+        <v>145.397736</v>
       </c>
       <c r="O33">
-        <v>37.20587659200001</v>
+        <v>37.51261588800001</v>
       </c>
       <c r="P33">
-        <v>107.002947408</v>
+        <v>107.885120112</v>
       </c>
       <c r="Q33">
-        <v>164.402947408</v>
+        <v>165.285120112</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1026600873429238</v>
+        <v>0.1026235313622228</v>
       </c>
       <c r="T33">
         <v>1.31232174046704</v>
       </c>
       <c r="U33">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.04192300000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.440430998353994</v>
+        <v>7.857651428168237</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08368279838938877</v>
+        <v>0.0831352774969901</v>
       </c>
       <c r="C34">
-        <v>986.3897084689695</v>
+        <v>1002.253611805312</v>
       </c>
       <c r="D34">
-        <v>1123.87770846897</v>
+        <v>1139.741611805312</v>
       </c>
       <c r="E34">
         <v>-405.8120000000001</v>
@@ -4069,37 +4069,37 @@
         <v>166.6</v>
       </c>
       <c r="M34">
-        <v>23.11347200000001</v>
+        <v>22.2134784</v>
       </c>
       <c r="N34">
-        <v>143.486528</v>
+        <v>144.3865216</v>
       </c>
       <c r="O34">
-        <v>37.01952422400001</v>
+        <v>37.25172257280001</v>
       </c>
       <c r="P34">
-        <v>106.467003776</v>
+        <v>107.1347990272</v>
       </c>
       <c r="Q34">
-        <v>163.867003776</v>
+        <v>164.5347990272</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1033344682196894</v>
+        <v>0.1032974786720443</v>
       </c>
       <c r="T34">
         <v>1.327886343465225</v>
       </c>
       <c r="U34">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.207917529655432</v>
+        <v>7.499951020728028</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08353400651216017</v>
+        <v>0.08297023235404642</v>
       </c>
       <c r="C35">
-        <v>978.0373575164829</v>
+        <v>994.5303500715552</v>
       </c>
       <c r="D35">
-        <v>1128.309357516483</v>
+        <v>1144.802350071555</v>
       </c>
       <c r="E35">
         <v>-393.028</v>
@@ -4151,37 +4151,37 @@
         <v>166.6</v>
       </c>
       <c r="M35">
-        <v>23.83576800000001</v>
+        <v>22.90764960000001</v>
       </c>
       <c r="N35">
-        <v>142.764232</v>
+        <v>143.6923504</v>
       </c>
       <c r="O35">
-        <v>36.83317185600001</v>
+        <v>37.0726264032</v>
       </c>
       <c r="P35">
-        <v>105.931060144</v>
+        <v>106.6197239968</v>
       </c>
       <c r="Q35">
-        <v>163.331060144</v>
+        <v>164.0197239968</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1040289798688958</v>
+        <v>0.1039915438120096</v>
       </c>
       <c r="T35">
         <v>1.343915561478282</v>
       </c>
       <c r="U35">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.989495786332539</v>
+        <v>7.272679777675662</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08338521463493154</v>
+        <v>0.08280518721110275</v>
       </c>
       <c r="C36">
-        <v>969.7200944775508</v>
+        <v>986.8522306723461</v>
       </c>
       <c r="D36">
-        <v>1132.776094477551</v>
+        <v>1149.908230672346</v>
       </c>
       <c r="E36">
         <v>-380.244</v>
@@ -4233,37 +4233,37 @@
         <v>166.6</v>
       </c>
       <c r="M36">
-        <v>24.55806400000001</v>
+        <v>23.60182080000001</v>
       </c>
       <c r="N36">
-        <v>142.041936</v>
+        <v>142.9981792</v>
       </c>
       <c r="O36">
-        <v>36.64681948800001</v>
+        <v>36.8935302336</v>
       </c>
       <c r="P36">
-        <v>105.395116512</v>
+        <v>106.1046489664</v>
       </c>
       <c r="Q36">
-        <v>162.795116512</v>
+        <v>163.5046489664</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1047445373256539</v>
+        <v>0.1047066412289436</v>
       </c>
       <c r="T36">
         <v>1.360430513370521</v>
       </c>
       <c r="U36">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.78392238085217</v>
+        <v>7.058777431273437</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08323642275770292</v>
+        <v>0.08264014206815909</v>
       </c>
       <c r="C37">
-        <v>961.4383377252002</v>
+        <v>979.2198603254642</v>
       </c>
       <c r="D37">
-        <v>1137.2783377252</v>
+        <v>1155.059860325464</v>
       </c>
       <c r="E37">
         <v>-367.46</v>
@@ -4315,37 +4315,37 @@
         <v>166.6</v>
       </c>
       <c r="M37">
-        <v>25.28036000000001</v>
+        <v>24.29599200000001</v>
       </c>
       <c r="N37">
-        <v>141.31964</v>
+        <v>142.304008</v>
       </c>
       <c r="O37">
-        <v>36.46046712</v>
+        <v>36.714434064</v>
       </c>
       <c r="P37">
-        <v>104.85917288</v>
+        <v>105.589573936</v>
       </c>
       <c r="Q37">
-        <v>162.25917288</v>
+        <v>162.989573936</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1054821119349276</v>
+        <v>0.1054437416433217</v>
       </c>
       <c r="T37">
         <v>1.377453617628676</v>
       </c>
       <c r="U37">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.590096027113538</v>
+        <v>6.857098076094196</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08308763088047431</v>
+        <v>0.08247509692521543</v>
       </c>
       <c r="C38">
-        <v>953.1925123103322</v>
+        <v>971.6338566700854</v>
       </c>
       <c r="D38">
-        <v>1141.816512310332</v>
+        <v>1160.257856670085</v>
       </c>
       <c r="E38">
         <v>-354.6760000000001</v>
@@ -4397,37 +4397,37 @@
         <v>166.6</v>
       </c>
       <c r="M38">
-        <v>26.002656</v>
+        <v>24.9901632</v>
       </c>
       <c r="N38">
-        <v>140.597344</v>
+        <v>141.6098368</v>
       </c>
       <c r="O38">
-        <v>36.27411475200001</v>
+        <v>36.5353378944</v>
       </c>
       <c r="P38">
-        <v>104.323229248</v>
+        <v>105.0744989056</v>
       </c>
       <c r="Q38">
-        <v>161.723229248</v>
+        <v>162.4744989056</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1062427357507411</v>
+        <v>0.1062038764456491</v>
       </c>
       <c r="T38">
         <v>1.395008693894899</v>
       </c>
       <c r="U38">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.407037804138162</v>
+        <v>6.666623129536025</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0829388390032457</v>
+        <v>0.08231005178227177</v>
       </c>
       <c r="C39">
-        <v>944.9830500954915</v>
+        <v>964.0948485136357</v>
       </c>
       <c r="D39">
-        <v>1146.391050095492</v>
+        <v>1165.502848513636</v>
       </c>
       <c r="E39">
         <v>-341.8920000000001</v>
@@ -4479,37 +4479,37 @@
         <v>166.6</v>
       </c>
       <c r="M39">
-        <v>26.72495200000001</v>
+        <v>25.6843344</v>
       </c>
       <c r="N39">
-        <v>139.875048</v>
+        <v>140.9156656</v>
       </c>
       <c r="O39">
-        <v>36.08776238400001</v>
+        <v>36.35624172480001</v>
       </c>
       <c r="P39">
-        <v>103.787285616</v>
+        <v>104.5594238752</v>
       </c>
       <c r="Q39">
-        <v>161.187285616</v>
+        <v>161.9594238752</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1070275063543582</v>
+        <v>0.1069881425115425</v>
       </c>
       <c r="T39">
         <v>1.413121074169573</v>
       </c>
       <c r="U39">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.233874620242536</v>
+        <v>6.48644412603505</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08318479112601707</v>
+        <v>0.08214500663932811</v>
       </c>
       <c r="C40">
-        <v>924.6570175254377</v>
+        <v>956.6034760853703</v>
       </c>
       <c r="D40">
-        <v>1138.849017525438</v>
+        <v>1170.79547608537</v>
       </c>
       <c r="E40">
         <v>-329.1080000000001</v>
@@ -4561,45 +4561,45 @@
         <v>166.6</v>
       </c>
       <c r="M40">
-        <v>28.1273568</v>
+        <v>26.3785056</v>
       </c>
       <c r="N40">
-        <v>138.4726432</v>
+        <v>140.2214944</v>
       </c>
       <c r="O40">
-        <v>35.72594194560001</v>
+        <v>36.17714555520001</v>
       </c>
       <c r="P40">
-        <v>102.7467012544</v>
+        <v>104.0443488448</v>
       </c>
       <c r="Q40">
-        <v>160.1467012544</v>
+        <v>161.4443488448</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1078375921387372</v>
+        <v>0.1077977074827873</v>
       </c>
       <c r="T40">
         <v>1.431817724775688</v>
       </c>
       <c r="U40">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>5.923059218987829</v>
+        <v>6.315748227981497</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08304638724878846</v>
+        <v>0.08197996149638445</v>
       </c>
       <c r="C41">
-        <v>916.1048674106537</v>
+        <v>949.1603912968917</v>
       </c>
       <c r="D41">
-        <v>1143.080867410654</v>
+        <v>1176.136391296892</v>
       </c>
       <c r="E41">
         <v>-316.324</v>
@@ -4643,45 +4643,45 @@
         <v>166.6</v>
       </c>
       <c r="M41">
-        <v>28.86755040000001</v>
+        <v>27.07267680000001</v>
       </c>
       <c r="N41">
-        <v>137.7324496</v>
+        <v>139.5273232</v>
       </c>
       <c r="O41">
-        <v>35.53497199680001</v>
+        <v>35.99804938560001</v>
       </c>
       <c r="P41">
-        <v>102.1974776032</v>
+        <v>103.5292738144</v>
       </c>
       <c r="Q41">
-        <v>159.5974776032</v>
+        <v>160.9292738144</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.108674238112768</v>
+        <v>0.1086338155678434</v>
       </c>
       <c r="T41">
         <v>1.451127380319708</v>
       </c>
       <c r="U41">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>5.771185905680448</v>
+        <v>6.15380596572556</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08290798337155983</v>
+        <v>0.08211171635344078</v>
       </c>
       <c r="C42">
-        <v>907.5842848659054</v>
+        <v>932.1088518447282</v>
       </c>
       <c r="D42">
-        <v>1147.344284865906</v>
+        <v>1171.868851844728</v>
       </c>
       <c r="E42">
         <v>-303.54</v>
@@ -4725,37 +4725,37 @@
         <v>166.6</v>
       </c>
       <c r="M42">
-        <v>29.60774400000001</v>
+        <v>28.27820800000001</v>
       </c>
       <c r="N42">
-        <v>136.992256</v>
+        <v>138.321792</v>
       </c>
       <c r="O42">
-        <v>35.34400204800001</v>
+        <v>35.68702233600001</v>
       </c>
       <c r="P42">
-        <v>101.648253952</v>
+        <v>102.634769664</v>
       </c>
       <c r="Q42">
-        <v>159.048253952</v>
+        <v>160.034769664</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1095387722859331</v>
+        <v>0.1094977939224013</v>
       </c>
       <c r="T42">
         <v>1.471080691048529</v>
       </c>
       <c r="U42">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.626906258038437</v>
+        <v>5.891462429302449</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.0827695794943312</v>
+        <v>0.08195409121049711</v>
       </c>
       <c r="C43">
-        <v>899.0956244319369</v>
+        <v>924.4339830411897</v>
       </c>
       <c r="D43">
-        <v>1151.639624431937</v>
+        <v>1176.97798304119</v>
       </c>
       <c r="E43">
         <v>-290.756</v>
@@ -4807,37 +4807,37 @@
         <v>166.6</v>
       </c>
       <c r="M43">
-        <v>30.34793760000001</v>
+        <v>28.98516320000001</v>
       </c>
       <c r="N43">
-        <v>136.2520624</v>
+        <v>137.6148368</v>
       </c>
       <c r="O43">
-        <v>35.1530320992</v>
+        <v>35.5046278944</v>
       </c>
       <c r="P43">
-        <v>101.0990303008</v>
+        <v>102.1102089056</v>
       </c>
       <c r="Q43">
-        <v>158.4990303008</v>
+        <v>159.5102089056</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1104326127022563</v>
+        <v>0.1103910596788087</v>
       </c>
       <c r="T43">
         <v>1.491710385191886</v>
       </c>
       <c r="U43">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.489664641988718</v>
+        <v>5.747768223709707</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08263117561710261</v>
+        <v>0.08179646606755347</v>
       </c>
       <c r="C44">
-        <v>890.6392459786533</v>
+        <v>916.8038590486348</v>
       </c>
       <c r="D44">
-        <v>1155.967245978653</v>
+        <v>1182.131859048635</v>
       </c>
       <c r="E44">
         <v>-277.9720000000001</v>
@@ -4889,37 +4889,37 @@
         <v>166.6</v>
       </c>
       <c r="M44">
-        <v>31.0881312</v>
+        <v>29.69211840000001</v>
       </c>
       <c r="N44">
-        <v>135.5118688</v>
+        <v>136.9078816</v>
       </c>
       <c r="O44">
-        <v>34.96206215040001</v>
+        <v>35.32223345280001</v>
       </c>
       <c r="P44">
-        <v>100.5498066496</v>
+        <v>101.5856481472</v>
       </c>
       <c r="Q44">
-        <v>157.9498066496</v>
+        <v>158.9856481472</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.111357275201901</v>
+        <v>0.1113151277026784</v>
       </c>
       <c r="T44">
         <v>1.513051448098808</v>
       </c>
       <c r="U44">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V44">
         <v>0.258</v>
       </c>
       <c r="W44">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.358958340988988</v>
+        <v>5.610916599335668</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08249277173987399</v>
+        <v>0.0816388409246098</v>
       </c>
       <c r="C45">
-        <v>882.2155148056299</v>
+        <v>909.2190702522785</v>
       </c>
       <c r="D45">
-        <v>1160.32751480563</v>
+        <v>1187.331070252278</v>
       </c>
       <c r="E45">
         <v>-265.1880000000001</v>
@@ -4971,37 +4971,37 @@
         <v>166.6</v>
       </c>
       <c r="M45">
-        <v>31.8283248</v>
+        <v>30.3990736</v>
       </c>
       <c r="N45">
-        <v>134.7716752</v>
+        <v>136.2009264</v>
       </c>
       <c r="O45">
-        <v>34.77109220160001</v>
+        <v>35.1398390112</v>
       </c>
       <c r="P45">
-        <v>100.0005829984</v>
+        <v>101.0610873888</v>
       </c>
       <c r="Q45">
-        <v>157.4005829984</v>
+        <v>158.4610873888</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1123143819997789</v>
+        <v>0.1122716191659821</v>
       </c>
       <c r="T45">
         <v>1.535141320230533</v>
       </c>
       <c r="U45">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.234331402826453</v>
+        <v>5.480430166792977</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08235436786264537</v>
+        <v>0.08148121578166614</v>
       </c>
       <c r="C46">
-        <v>873.8248017448973</v>
+        <v>901.6802174696581</v>
       </c>
       <c r="D46">
-        <v>1164.720801744897</v>
+        <v>1192.576217469658</v>
       </c>
       <c r="E46">
         <v>-252.404</v>
@@ -5053,37 +5053,37 @@
         <v>166.6</v>
       </c>
       <c r="M46">
-        <v>32.56851840000001</v>
+        <v>31.10602880000001</v>
       </c>
       <c r="N46">
-        <v>134.0314816</v>
+        <v>135.4939712</v>
       </c>
       <c r="O46">
-        <v>34.5801222528</v>
+        <v>34.9574445696</v>
       </c>
       <c r="P46">
-        <v>99.4513593472</v>
+        <v>100.5365266304</v>
       </c>
       <c r="Q46">
-        <v>156.8513593472</v>
+        <v>157.9365266304</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1133056711832953</v>
+        <v>0.1132622710386895</v>
       </c>
       <c r="T46">
         <v>1.558020116366963</v>
       </c>
       <c r="U46">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.115369325489488</v>
+        <v>5.355874935729499</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08221596398541677</v>
+        <v>0.08132359063872248</v>
       </c>
       <c r="C47">
-        <v>865.4674832660804</v>
+        <v>894.1879121820999</v>
       </c>
       <c r="D47">
-        <v>1169.14748326608</v>
+        <v>1197.8679121821</v>
       </c>
       <c r="E47">
         <v>-239.62</v>
@@ -5135,37 +5135,37 @@
         <v>166.6</v>
       </c>
       <c r="M47">
-        <v>33.30871200000001</v>
+        <v>31.81298400000001</v>
       </c>
       <c r="N47">
-        <v>133.291288</v>
+        <v>134.787016</v>
       </c>
       <c r="O47">
-        <v>34.38915230400001</v>
+        <v>34.775050128</v>
       </c>
       <c r="P47">
-        <v>98.902135696</v>
+        <v>100.011965872</v>
       </c>
       <c r="Q47">
-        <v>156.302135696</v>
+        <v>157.411965872</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1143330072462123</v>
+        <v>0.114288946615859</v>
       </c>
       <c r="T47">
         <v>1.581730868726537</v>
       </c>
       <c r="U47">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.001694451589722</v>
+        <v>5.236855492713289</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08207756010818813</v>
+        <v>0.08116596549577881</v>
       </c>
       <c r="C48">
-        <v>857.1439415839375</v>
+        <v>886.7427767723477</v>
       </c>
       <c r="D48">
-        <v>1173.607941583937</v>
+        <v>1203.206776772348</v>
       </c>
       <c r="E48">
         <v>-226.836</v>
@@ -5217,37 +5217,37 @@
         <v>166.6</v>
       </c>
       <c r="M48">
-        <v>34.04890560000001</v>
+        <v>32.51993920000001</v>
       </c>
       <c r="N48">
-        <v>132.5510944</v>
+        <v>134.0800608</v>
       </c>
       <c r="O48">
-        <v>34.1981823552</v>
+        <v>34.59265568640001</v>
       </c>
       <c r="P48">
-        <v>98.35291204480001</v>
+        <v>99.4874051136</v>
       </c>
       <c r="Q48">
-        <v>155.7529120448</v>
+        <v>156.8874051136</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.115398392792941</v>
+        <v>0.1153536472144052</v>
       </c>
       <c r="T48">
         <v>1.606319797099427</v>
       </c>
       <c r="U48">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V48">
         <v>0.258</v>
       </c>
       <c r="W48">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.892961963511684</v>
+        <v>5.123010808089087</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08193915623095951</v>
+        <v>0.08100834035283513</v>
       </c>
       <c r="C49">
-        <v>848.8545647683699</v>
+        <v>879.3454447685934</v>
       </c>
       <c r="D49">
-        <v>1178.10256476837</v>
+        <v>1208.593444768594</v>
       </c>
       <c r="E49">
         <v>-214.052</v>
@@ -5299,37 +5299,37 @@
         <v>166.6</v>
       </c>
       <c r="M49">
-        <v>34.78909920000001</v>
+        <v>33.22689440000001</v>
       </c>
       <c r="N49">
-        <v>131.8109008</v>
+        <v>133.3731056</v>
       </c>
       <c r="O49">
-        <v>34.0072124064</v>
+        <v>34.41026124480001</v>
       </c>
       <c r="P49">
-        <v>97.80368839360001</v>
+        <v>98.96284435520002</v>
       </c>
       <c r="Q49">
-        <v>155.2036883936</v>
+        <v>156.3628443552</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1165039815678481</v>
+        <v>0.1164585251940286</v>
       </c>
       <c r="T49">
         <v>1.631836609561861</v>
       </c>
       <c r="U49">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V49">
         <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.788856389819946</v>
+        <v>5.014010578129746</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.0818007523537309</v>
+        <v>0.08085071520989148</v>
       </c>
       <c r="C50">
-        <v>840.5997468569781</v>
+        <v>871.9965610950831</v>
       </c>
       <c r="D50">
-        <v>1182.631746856978</v>
+        <v>1214.028561095083</v>
       </c>
       <c r="E50">
         <v>-201.268</v>
@@ -5381,37 +5381,37 @@
         <v>166.6</v>
       </c>
       <c r="M50">
-        <v>35.52929280000001</v>
+        <v>33.93384960000001</v>
       </c>
       <c r="N50">
-        <v>131.0707072</v>
+        <v>132.6661504</v>
       </c>
       <c r="O50">
-        <v>33.8162424576</v>
+        <v>34.22786680320001</v>
       </c>
       <c r="P50">
-        <v>97.25446474240002</v>
+        <v>98.43828359680001</v>
       </c>
       <c r="Q50">
-        <v>154.6544647424</v>
+        <v>155.8382835968</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.117652092987944</v>
+        <v>0.1176058984805605</v>
       </c>
       <c r="T50">
         <v>1.658334837888234</v>
       </c>
       <c r="U50">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.689088548365364</v>
+        <v>4.909552024418709</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08166234847650228</v>
+        <v>0.0806930900669478</v>
       </c>
       <c r="C51">
-        <v>832.37988797021</v>
+        <v>864.6967823295209</v>
       </c>
       <c r="D51">
-        <v>1187.19588797021</v>
+        <v>1219.512782329521</v>
       </c>
       <c r="E51">
         <v>-188.484</v>
@@ -5463,37 +5463,37 @@
         <v>166.6</v>
       </c>
       <c r="M51">
-        <v>36.26948640000001</v>
+        <v>34.64080480000001</v>
       </c>
       <c r="N51">
-        <v>130.3305136</v>
+        <v>131.9591952</v>
       </c>
       <c r="O51">
-        <v>33.6252725088</v>
+        <v>34.04547236160001</v>
       </c>
       <c r="P51">
-        <v>96.70524109120001</v>
+        <v>97.91372283840001</v>
       </c>
       <c r="Q51">
-        <v>154.1052410912</v>
+        <v>155.3137228384</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1188452283852986</v>
+        <v>0.1187982667979369</v>
       </c>
       <c r="T51">
         <v>1.685872212423485</v>
       </c>
       <c r="U51">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.593392863704847</v>
+        <v>4.809357085144858</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08152394459927366</v>
+        <v>0.08053546492400415</v>
       </c>
       <c r="C52">
-        <v>824.1953944291997</v>
+        <v>857.4467769674759</v>
       </c>
       <c r="D52">
-        <v>1191.7953944292</v>
+        <v>1225.046776967476</v>
       </c>
       <c r="E52">
         <v>-175.7</v>
@@ -5545,37 +5545,37 @@
         <v>166.6</v>
       </c>
       <c r="M52">
-        <v>37.00968000000001</v>
+        <v>35.34776000000001</v>
       </c>
       <c r="N52">
-        <v>129.59032</v>
+        <v>131.25224</v>
       </c>
       <c r="O52">
-        <v>33.43430256000001</v>
+        <v>33.86307792000001</v>
       </c>
       <c r="P52">
-        <v>96.15601744000001</v>
+        <v>97.38916208000002</v>
       </c>
       <c r="Q52">
-        <v>153.55601744</v>
+        <v>154.78916208</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1200860891985473</v>
+        <v>0.1200383298480083</v>
       </c>
       <c r="T52">
         <v>1.714511081940145</v>
       </c>
       <c r="U52">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.50152500643075</v>
+        <v>4.713169943441961</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08236943272204504</v>
+        <v>0.08037783978106049</v>
       </c>
       <c r="C53">
-        <v>783.8569924120178</v>
+        <v>850.2472256940254</v>
       </c>
       <c r="D53">
-        <v>1164.240992412018</v>
+        <v>1230.631225694025</v>
       </c>
       <c r="E53">
         <v>-162.9160000000001</v>
@@ -5627,45 +5627,45 @@
         <v>166.6</v>
       </c>
       <c r="M53">
-        <v>39.445032</v>
+        <v>36.05471520000001</v>
       </c>
       <c r="N53">
-        <v>127.154968</v>
+        <v>130.5452848</v>
       </c>
       <c r="O53">
-        <v>32.80598174400001</v>
+        <v>33.68068347840001</v>
       </c>
       <c r="P53">
-        <v>94.34898625600002</v>
+        <v>96.86460132160002</v>
       </c>
       <c r="Q53">
-        <v>151.748986256</v>
+        <v>154.2646013216</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1213775973919287</v>
+        <v>0.12132900771645</v>
       </c>
       <c r="T53">
         <v>1.744318884906466</v>
       </c>
       <c r="U53">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V53">
         <v>0.258</v>
       </c>
       <c r="W53">
-        <v>0.044891</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.223599058051215</v>
+        <v>4.620754846511725</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08225032084481643</v>
+        <v>0.08022021463811682</v>
       </c>
       <c r="C54">
-        <v>774.8774837563624</v>
+        <v>843.0988216628589</v>
       </c>
       <c r="D54">
-        <v>1168.045483756363</v>
+        <v>1236.266821662859</v>
       </c>
       <c r="E54">
         <v>-150.1320000000001</v>
@@ -5709,45 +5709,45 @@
         <v>166.6</v>
       </c>
       <c r="M54">
-        <v>40.218464</v>
+        <v>36.76167040000001</v>
       </c>
       <c r="N54">
-        <v>126.381536</v>
+        <v>129.8383296</v>
       </c>
       <c r="O54">
-        <v>32.606436288</v>
+        <v>33.4982890368</v>
       </c>
       <c r="P54">
-        <v>93.77509971200001</v>
+        <v>96.34004056320001</v>
       </c>
       <c r="Q54">
-        <v>151.175099712</v>
+        <v>153.7400405632</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1227229184267009</v>
+        <v>0.1226734638294101</v>
       </c>
       <c r="T54">
         <v>1.77536867966305</v>
       </c>
       <c r="U54">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.044891</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.142375999242537</v>
+        <v>4.5318941763865</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08213120896758781</v>
+        <v>0.08104573949517316</v>
       </c>
       <c r="C55">
-        <v>765.9229211522593</v>
+        <v>801.3590100994074</v>
       </c>
       <c r="D55">
-        <v>1171.874921152259</v>
+        <v>1207.311010099408</v>
       </c>
       <c r="E55">
         <v>-137.348</v>
@@ -5791,37 +5791,37 @@
         <v>166.6</v>
       </c>
       <c r="M55">
-        <v>40.99189600000001</v>
+        <v>39.16250560000001</v>
       </c>
       <c r="N55">
-        <v>125.608104</v>
+        <v>127.4374944</v>
       </c>
       <c r="O55">
-        <v>32.406890832</v>
+        <v>32.87887355520001</v>
       </c>
       <c r="P55">
-        <v>93.20121316800001</v>
+        <v>94.5586208448</v>
       </c>
       <c r="Q55">
-        <v>150.601213168</v>
+        <v>151.9586208448</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1241254871650805</v>
+        <v>0.124075130840794</v>
       </c>
       <c r="T55">
         <v>1.807739742281616</v>
       </c>
       <c r="U55">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.258</v>
       </c>
       <c r="W55">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.064217961520979</v>
+        <v>4.254068973564348</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08309393309035917</v>
+        <v>0.0809066643522295</v>
       </c>
       <c r="C56">
-        <v>722.8875595506125</v>
+        <v>793.3577758336397</v>
       </c>
       <c r="D56">
-        <v>1141.623559550613</v>
+        <v>1212.09377583364</v>
       </c>
       <c r="E56">
         <v>-124.564</v>
@@ -5873,45 +5873,45 @@
         <v>166.6</v>
       </c>
       <c r="M56">
-        <v>43.62923520000001</v>
+        <v>39.90142080000001</v>
       </c>
       <c r="N56">
-        <v>122.9707648</v>
+        <v>126.6985792</v>
       </c>
       <c r="O56">
-        <v>31.7264573184</v>
+        <v>32.6882334336</v>
       </c>
       <c r="P56">
-        <v>91.2443074816</v>
+        <v>94.01034576640001</v>
       </c>
       <c r="Q56">
-        <v>148.6443074816</v>
+        <v>151.4103457664</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1255890371529547</v>
+        <v>0.1255377398961511</v>
       </c>
       <c r="T56">
         <v>1.841518242405337</v>
       </c>
       <c r="U56">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V56">
         <v>0.258</v>
       </c>
       <c r="W56">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.818540463436773</v>
+        <v>4.17528991849834</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08299485521313058</v>
+        <v>0.08076758920928584</v>
       </c>
       <c r="C57">
-        <v>713.1445618135951</v>
+        <v>785.3945861596319</v>
       </c>
       <c r="D57">
-        <v>1144.664561813595</v>
+        <v>1216.914586159632</v>
       </c>
       <c r="E57">
         <v>-111.78</v>
@@ -5955,45 +5955,45 @@
         <v>166.6</v>
       </c>
       <c r="M57">
-        <v>44.43718400000001</v>
+        <v>40.64033600000001</v>
       </c>
       <c r="N57">
-        <v>122.162816</v>
+        <v>125.959664</v>
       </c>
       <c r="O57">
-        <v>31.51800652800001</v>
+        <v>32.497593312</v>
       </c>
       <c r="P57">
-        <v>90.64480947200002</v>
+        <v>93.46207068800001</v>
       </c>
       <c r="Q57">
-        <v>148.044809472</v>
+        <v>150.862070688</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1271176338069568</v>
+        <v>0.127065353798413</v>
       </c>
       <c r="T57">
         <v>1.876798009201223</v>
       </c>
       <c r="U57">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.74911245501065</v>
+        <v>4.099375556343825</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08289577733590196</v>
+        <v>0.08062851406634218</v>
       </c>
       <c r="C58">
-        <v>703.4178083000719</v>
+        <v>777.4698968295619</v>
       </c>
       <c r="D58">
-        <v>1147.721808300072</v>
+        <v>1221.773896829562</v>
       </c>
       <c r="E58">
         <v>-98.99599999999998</v>
@@ -6037,45 +6037,45 @@
         <v>166.6</v>
       </c>
       <c r="M58">
-        <v>45.24513280000001</v>
+        <v>41.37925120000001</v>
       </c>
       <c r="N58">
-        <v>121.3548672</v>
+        <v>125.2207488</v>
       </c>
       <c r="O58">
-        <v>31.3095557376</v>
+        <v>32.30695319040001</v>
       </c>
       <c r="P58">
-        <v>90.04531146240001</v>
+        <v>92.91379560960002</v>
       </c>
       <c r="Q58">
-        <v>147.4453114624</v>
+        <v>150.3137956096</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1287157121270499</v>
+        <v>0.1286624046962322</v>
       </c>
       <c r="T58">
         <v>1.913681401760559</v>
       </c>
       <c r="U58">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.682164018314031</v>
+        <v>4.026172421409115</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08279669945867334</v>
+        <v>0.08196972892339852</v>
       </c>
       <c r="C59">
-        <v>693.7074295170778</v>
+        <v>719.3811253765648</v>
       </c>
       <c r="D59">
-        <v>1150.795429517078</v>
+        <v>1176.469125376565</v>
       </c>
       <c r="E59">
         <v>-86.21199999999999</v>
@@ -6119,37 +6119,37 @@
         <v>166.6</v>
       </c>
       <c r="M59">
-        <v>46.05308160000001</v>
+        <v>44.66857440000001</v>
       </c>
       <c r="N59">
-        <v>120.5469184</v>
+        <v>121.9314256</v>
       </c>
       <c r="O59">
-        <v>31.1011049472</v>
+        <v>31.4583078048</v>
       </c>
       <c r="P59">
-        <v>89.44581345280001</v>
+        <v>90.47311779520001</v>
       </c>
       <c r="Q59">
-        <v>146.8458134528</v>
+        <v>147.8731177952</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1303881196713333</v>
+        <v>0.1303337370311593</v>
       </c>
       <c r="T59">
         <v>1.952280300950562</v>
       </c>
       <c r="U59">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V59">
         <v>0.258</v>
       </c>
       <c r="W59">
-        <v>0.0468944</v>
+        <v>0.04548460000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.61756464957168</v>
+        <v>3.729691449476838</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08269762158144472</v>
+        <v>0.08185662378045486</v>
       </c>
       <c r="C60">
-        <v>684.0135573734026</v>
+        <v>710.2875626566813</v>
       </c>
       <c r="D60">
-        <v>1153.885557373402</v>
+        <v>1180.159562656681</v>
       </c>
       <c r="E60">
         <v>-73.42800000000011</v>
@@ -6201,37 +6201,37 @@
         <v>166.6</v>
       </c>
       <c r="M60">
-        <v>46.8610304</v>
+        <v>45.45223360000001</v>
       </c>
       <c r="N60">
-        <v>119.7389696</v>
+        <v>121.1477664</v>
       </c>
       <c r="O60">
-        <v>30.89265415680001</v>
+        <v>31.25612373120001</v>
       </c>
       <c r="P60">
-        <v>88.84631544320001</v>
+        <v>89.89164266880002</v>
       </c>
       <c r="Q60">
-        <v>146.2463154432</v>
+        <v>147.2916426688</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1321401656701065</v>
+        <v>0.1320846566201306</v>
       </c>
       <c r="T60">
         <v>1.992717242959136</v>
       </c>
       <c r="U60">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.0468944</v>
+        <v>0.04548460000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.555192845268721</v>
+        <v>3.665386424485859</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08465610970421611</v>
+        <v>0.08174351863751118</v>
       </c>
       <c r="C61">
-        <v>613.0695620378932</v>
+        <v>701.21722567829</v>
       </c>
       <c r="D61">
-        <v>1095.725562037893</v>
+        <v>1183.87322567829</v>
       </c>
       <c r="E61">
         <v>-60.64400000000012</v>
@@ -6283,45 +6283,45 @@
         <v>166.6</v>
       </c>
       <c r="M61">
-        <v>51.21398240000001</v>
+        <v>46.2358928</v>
       </c>
       <c r="N61">
-        <v>115.3860176</v>
+        <v>120.3641072</v>
       </c>
       <c r="O61">
-        <v>29.7695925408</v>
+        <v>31.05393965760001</v>
       </c>
       <c r="P61">
-        <v>85.6164250592</v>
+        <v>89.31016754240001</v>
       </c>
       <c r="Q61">
-        <v>143.0164250592</v>
+        <v>146.7101675424</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1339776773273563</v>
+        <v>0.133920986920759</v>
       </c>
       <c r="T61">
         <v>2.035126718724225</v>
       </c>
       <c r="U61">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V61">
         <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.05038180000000001</v>
+        <v>0.04548460000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.25301787115075</v>
+        <v>3.603261230850505</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08459190582698747</v>
+        <v>0.08163041349456751</v>
       </c>
       <c r="C62">
-        <v>602.0990802954165</v>
+        <v>692.170334390078</v>
       </c>
       <c r="D62">
-        <v>1097.539080295416</v>
+        <v>1187.610334390078</v>
       </c>
       <c r="E62">
         <v>-47.86000000000001</v>
@@ -6365,45 +6365,45 @@
         <v>166.6</v>
       </c>
       <c r="M62">
-        <v>52.08201600000002</v>
+        <v>47.01955200000001</v>
       </c>
       <c r="N62">
-        <v>114.517984</v>
+        <v>119.580448</v>
       </c>
       <c r="O62">
-        <v>29.545639872</v>
+        <v>30.85175558400001</v>
       </c>
       <c r="P62">
-        <v>84.972344128</v>
+        <v>88.72869241600002</v>
       </c>
       <c r="Q62">
-        <v>142.372344128</v>
+        <v>146.128692416</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1359070645674687</v>
+        <v>0.1358491337364188</v>
       </c>
       <c r="T62">
         <v>2.07965666827757</v>
       </c>
       <c r="U62">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V62">
         <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.05038180000000001</v>
+        <v>0.04548460000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.198800906631571</v>
+        <v>3.543206877002997</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08452770194975888</v>
+        <v>0.08278464435162386</v>
       </c>
       <c r="C63">
-        <v>591.1346115564315</v>
+        <v>642.3229390771571</v>
       </c>
       <c r="D63">
-        <v>1099.358611556432</v>
+        <v>1150.546939077157</v>
       </c>
       <c r="E63">
         <v>-35.07600000000002</v>
@@ -6447,37 +6447,37 @@
         <v>166.6</v>
       </c>
       <c r="M63">
-        <v>52.95004960000001</v>
+        <v>49.98671840000001</v>
       </c>
       <c r="N63">
-        <v>113.6499504</v>
+        <v>116.6132816</v>
       </c>
       <c r="O63">
-        <v>29.3216872032</v>
+        <v>30.08622665280001</v>
       </c>
       <c r="P63">
-        <v>84.32826319680001</v>
+        <v>86.52705494720001</v>
       </c>
       <c r="Q63">
-        <v>141.7282631968</v>
+        <v>143.9270549472</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1379353947429715</v>
+        <v>0.1378761598759586</v>
       </c>
       <c r="T63">
         <v>2.126470204987497</v>
       </c>
       <c r="U63">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V63">
         <v>0.258</v>
       </c>
       <c r="W63">
-        <v>0.05038180000000001</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.146361547506463</v>
+        <v>3.332885320993586</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08446349807253026</v>
+        <v>0.08269231520868019</v>
       </c>
       <c r="C64">
-        <v>580.1761857761823</v>
+        <v>632.4183737832897</v>
       </c>
       <c r="D64">
-        <v>1101.184185776182</v>
+        <v>1153.42637378329</v>
       </c>
       <c r="E64">
         <v>-22.29200000000003</v>
@@ -6529,37 +6529,37 @@
         <v>166.6</v>
       </c>
       <c r="M64">
-        <v>53.81808320000002</v>
+        <v>50.80617280000001</v>
       </c>
       <c r="N64">
-        <v>112.7819168</v>
+        <v>115.7938272</v>
       </c>
       <c r="O64">
-        <v>29.0977345344</v>
+        <v>29.8748074176</v>
       </c>
       <c r="P64">
-        <v>83.6841822656</v>
+        <v>85.9190197824</v>
       </c>
       <c r="Q64">
-        <v>141.0841822656</v>
+        <v>143.3190197824</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1400704791382375</v>
+        <v>0.14000987160179</v>
       </c>
       <c r="T64">
         <v>2.175747612050577</v>
       </c>
       <c r="U64">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.258</v>
       </c>
       <c r="W64">
-        <v>0.05038180000000001</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.095613780611197</v>
+        <v>3.279129106138851</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08439929419530164</v>
+        <v>0.08259998606573653</v>
       </c>
       <c r="C65">
-        <v>569.2238331092128</v>
+        <v>622.5282571763371</v>
       </c>
       <c r="D65">
-        <v>1103.015833109213</v>
+        <v>1156.320257176337</v>
       </c>
       <c r="E65">
         <v>-9.508000000000038</v>
@@ -6611,37 +6611,37 @@
         <v>166.6</v>
       </c>
       <c r="M65">
-        <v>54.68611680000001</v>
+        <v>51.6256272</v>
       </c>
       <c r="N65">
-        <v>111.9138832</v>
+        <v>114.9743728</v>
       </c>
       <c r="O65">
-        <v>28.87378186560001</v>
+        <v>29.66338818240001</v>
       </c>
       <c r="P65">
-        <v>83.04010133440001</v>
+        <v>85.31098461760001</v>
       </c>
       <c r="Q65">
-        <v>140.4401013344</v>
+        <v>142.7109846176</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1423209735008152</v>
+        <v>0.1422589190965852</v>
       </c>
       <c r="T65">
         <v>2.227688662738688</v>
       </c>
       <c r="U65">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V65">
         <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.05038180000000001</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.046477053934829</v>
+        <v>3.227079437787441</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08875147431807301</v>
+        <v>0.08250765692279285</v>
       </c>
       <c r="C66">
-        <v>444.6736211182061</v>
+        <v>612.6526982827271</v>
       </c>
       <c r="D66">
-        <v>991.2496211182062</v>
+        <v>1159.228698282727</v>
       </c>
       <c r="E66">
         <v>3.275999999999954</v>
@@ -6693,45 +6693,45 @@
         <v>166.6</v>
       </c>
       <c r="M66">
-        <v>63.16318720000001</v>
+        <v>52.44508160000001</v>
       </c>
       <c r="N66">
-        <v>103.4368128</v>
+        <v>114.1549184</v>
       </c>
       <c r="O66">
-        <v>26.6866977024</v>
+        <v>29.4519689472</v>
       </c>
       <c r="P66">
-        <v>76.7501150976</v>
+        <v>84.70294945280001</v>
       </c>
       <c r="Q66">
-        <v>134.1501150976</v>
+        <v>142.1029494528</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1446964953279806</v>
+        <v>0.1446329136744246</v>
       </c>
       <c r="T66">
         <v>2.282515327353917</v>
       </c>
       <c r="U66">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.258</v>
       </c>
       <c r="W66">
-        <v>0.0572824</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.637612308455517</v>
+        <v>3.176656321572012</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08875627644084438</v>
+        <v>0.0824153277798492</v>
       </c>
       <c r="C67">
-        <v>431.7788083855371</v>
+        <v>602.791807228567</v>
       </c>
       <c r="D67">
-        <v>991.1388083855372</v>
+        <v>1162.151807228567</v>
       </c>
       <c r="E67">
         <v>16.05999999999995</v>
@@ -6775,45 +6775,45 @@
         <v>166.6</v>
       </c>
       <c r="M67">
-        <v>64.15011200000001</v>
+        <v>53.26453600000001</v>
       </c>
       <c r="N67">
-        <v>102.449888</v>
+        <v>113.335464</v>
       </c>
       <c r="O67">
-        <v>26.43207110400001</v>
+        <v>29.240549712</v>
       </c>
       <c r="P67">
-        <v>76.01781689600001</v>
+        <v>84.09491428800001</v>
       </c>
       <c r="Q67">
-        <v>133.417816896</v>
+        <v>141.494914288</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1472077612595554</v>
+        <v>0.1471425650852834</v>
       </c>
       <c r="T67">
         <v>2.340474944232874</v>
       </c>
       <c r="U67">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.258</v>
       </c>
       <c r="W67">
-        <v>0.0572824</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.597033657556202</v>
+        <v>3.127784685855519</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08876107856361579</v>
+        <v>0.08232299863690554</v>
       </c>
       <c r="C68">
-        <v>418.8840204258186</v>
+        <v>592.9456952535497</v>
       </c>
       <c r="D68">
-        <v>991.0280204258188</v>
+        <v>1165.08969525355</v>
       </c>
       <c r="E68">
         <v>28.84400000000005</v>
@@ -6857,45 +6857,45 @@
         <v>166.6</v>
       </c>
       <c r="M68">
-        <v>65.13703680000002</v>
+        <v>54.08399040000001</v>
       </c>
       <c r="N68">
-        <v>101.4629632</v>
+        <v>112.5160096</v>
       </c>
       <c r="O68">
-        <v>26.1774445056</v>
+        <v>29.02913047680001</v>
       </c>
       <c r="P68">
-        <v>75.2855186944</v>
+        <v>83.48687912320001</v>
       </c>
       <c r="Q68">
-        <v>132.6855186944</v>
+        <v>140.8868791232</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.149866748716517</v>
+        <v>0.1497998430497222</v>
       </c>
       <c r="T68">
         <v>2.401843950340004</v>
       </c>
       <c r="U68">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V68">
         <v>0.258</v>
       </c>
       <c r="W68">
-        <v>0.0572824</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.557684662744744</v>
+        <v>3.080394008797102</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08876588068638716</v>
+        <v>0.08223066949396188</v>
       </c>
       <c r="C69">
-        <v>405.9892572307455</v>
+        <v>583.1144747250629</v>
       </c>
       <c r="D69">
-        <v>990.9172572307456</v>
+        <v>1168.042474725063</v>
       </c>
       <c r="E69">
         <v>41.62800000000004</v>
@@ -6939,45 +6939,45 @@
         <v>166.6</v>
       </c>
       <c r="M69">
-        <v>66.12396160000002</v>
+        <v>54.90344480000001</v>
       </c>
       <c r="N69">
-        <v>100.4760384</v>
+        <v>111.6965552</v>
       </c>
       <c r="O69">
-        <v>25.9228179072</v>
+        <v>28.8177112416</v>
       </c>
       <c r="P69">
-        <v>74.55322049280001</v>
+        <v>82.87884395840001</v>
       </c>
       <c r="Q69">
-        <v>131.9532204928</v>
+        <v>140.2788439584</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.152686886928446</v>
+        <v>0.1526181681635209</v>
       </c>
       <c r="T69">
         <v>2.466932290150597</v>
       </c>
       <c r="U69">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.258</v>
       </c>
       <c r="W69">
-        <v>0.0572824</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.51951026479333</v>
+        <v>3.034417978815056</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09114211480915854</v>
+        <v>0.08607390835101822</v>
       </c>
       <c r="C70">
-        <v>341.2744769972853</v>
+        <v>458.8670878982887</v>
       </c>
       <c r="D70">
-        <v>938.9864769972855</v>
+        <v>1056.579087898289</v>
       </c>
       <c r="E70">
         <v>54.41200000000003</v>
@@ -7021,45 +7021,45 @@
         <v>166.6</v>
       </c>
       <c r="M70">
-        <v>71.19665280000001</v>
+        <v>62.50353280000002</v>
       </c>
       <c r="N70">
-        <v>95.40334720000001</v>
+        <v>104.0964672</v>
       </c>
       <c r="O70">
-        <v>24.6140635776</v>
+        <v>26.8568885376</v>
       </c>
       <c r="P70">
-        <v>70.78928362240001</v>
+        <v>77.23957866240001</v>
       </c>
       <c r="Q70">
-        <v>128.1892836224</v>
+        <v>134.6395786624</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1556832837786205</v>
+        <v>0.1556126385969319</v>
       </c>
       <c r="T70">
         <v>2.536088651199352</v>
       </c>
       <c r="U70">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V70">
         <v>0.258</v>
       </c>
       <c r="W70">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.339997646630938</v>
+        <v>2.665449336009372</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09118179093192992</v>
+        <v>0.08603945520807454</v>
       </c>
       <c r="C71">
-        <v>327.6695454743782</v>
+        <v>446.9877341008381</v>
       </c>
       <c r="D71">
-        <v>938.1655454743783</v>
+        <v>1057.483734100838</v>
       </c>
       <c r="E71">
         <v>67.19600000000003</v>
@@ -7103,45 +7103,45 @@
         <v>166.6</v>
       </c>
       <c r="M71">
-        <v>72.24366240000001</v>
+        <v>63.42270240000001</v>
       </c>
       <c r="N71">
-        <v>94.35633760000002</v>
+        <v>103.1772976</v>
       </c>
       <c r="O71">
-        <v>24.34393510080001</v>
+        <v>26.6197427808</v>
       </c>
       <c r="P71">
-        <v>70.01240249920001</v>
+        <v>76.55755481919999</v>
       </c>
       <c r="Q71">
-        <v>127.4124024992</v>
+        <v>133.9575548192</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1588729965546127</v>
+        <v>0.1588003006712082</v>
       </c>
       <c r="T71">
         <v>2.609706712960929</v>
       </c>
       <c r="U71">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.258</v>
       </c>
       <c r="W71">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.306084637259476</v>
+        <v>2.626819635487497</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0912214670547013</v>
+        <v>0.08600500206513088</v>
       </c>
       <c r="C72">
-        <v>314.0660481358777</v>
+        <v>435.1099307525024</v>
       </c>
       <c r="D72">
-        <v>937.3460481358777</v>
+        <v>1058.389930752502</v>
       </c>
       <c r="E72">
         <v>79.98000000000002</v>
@@ -7185,45 +7185,45 @@
         <v>166.6</v>
       </c>
       <c r="M72">
-        <v>73.29067200000001</v>
+        <v>64.34187200000001</v>
       </c>
       <c r="N72">
-        <v>93.30932800000001</v>
+        <v>102.258128</v>
       </c>
       <c r="O72">
-        <v>24.073806624</v>
+        <v>26.382597024</v>
       </c>
       <c r="P72">
-        <v>69.23552137600001</v>
+        <v>75.87553097600001</v>
       </c>
       <c r="Q72">
-        <v>126.635521376</v>
+        <v>133.275530976</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1622753568490044</v>
+        <v>0.1622004735504363</v>
       </c>
       <c r="T72">
         <v>2.688232645506612</v>
       </c>
       <c r="U72">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V72">
         <v>0.258</v>
       </c>
       <c r="W72">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.273140571012911</v>
+        <v>2.589293640694819</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09126114317747269</v>
+        <v>0.08597054892218722</v>
       </c>
       <c r="C73">
-        <v>300.463981226739</v>
+        <v>423.2336818426104</v>
       </c>
       <c r="D73">
-        <v>936.5279812267388</v>
+        <v>1059.29768184261</v>
       </c>
       <c r="E73">
         <v>92.7639999999999</v>
@@ -7267,45 +7267,45 @@
         <v>166.6</v>
       </c>
       <c r="M73">
-        <v>74.3376816</v>
+        <v>65.2610416</v>
       </c>
       <c r="N73">
-        <v>92.26231840000003</v>
+        <v>101.3389584</v>
       </c>
       <c r="O73">
-        <v>23.80367814720001</v>
+        <v>26.14545126720001</v>
       </c>
       <c r="P73">
-        <v>68.45864025280002</v>
+        <v>75.19350713280002</v>
       </c>
       <c r="Q73">
-        <v>125.8586402528</v>
+        <v>132.5935071328</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1659123626809403</v>
+        <v>0.1658351411109904</v>
       </c>
       <c r="T73">
         <v>2.772174159607169</v>
       </c>
       <c r="U73">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0.258</v>
       </c>
       <c r="W73">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.241124506632448</v>
+        <v>2.55282471617799</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09130081930024407</v>
+        <v>0.08593609577924356</v>
       </c>
       <c r="C74">
-        <v>286.8633410050146</v>
+        <v>411.3589913741888</v>
       </c>
       <c r="D74">
-        <v>935.7113410050146</v>
+        <v>1060.206991374189</v>
       </c>
       <c r="E74">
         <v>105.5479999999999</v>
@@ -7349,45 +7349,45 @@
         <v>166.6</v>
       </c>
       <c r="M74">
-        <v>75.38469119999999</v>
+        <v>66.1802112</v>
       </c>
       <c r="N74">
-        <v>91.21530880000003</v>
+        <v>100.4197888</v>
       </c>
       <c r="O74">
-        <v>23.53354967040001</v>
+        <v>25.90830551040001</v>
       </c>
       <c r="P74">
-        <v>67.68175912960002</v>
+        <v>74.51148328960002</v>
       </c>
       <c r="Q74">
-        <v>125.0817591296</v>
+        <v>131.9114832896</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1698091546437288</v>
+        <v>0.1697294277830127</v>
       </c>
       <c r="T74">
         <v>2.86211149614348</v>
       </c>
       <c r="U74">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.258</v>
       </c>
       <c r="W74">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.209997777373665</v>
+        <v>2.517368817342185</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09134049542301545</v>
+        <v>0.08801411663629991</v>
       </c>
       <c r="C75">
-        <v>273.2641237417978</v>
+        <v>346.3855245222861</v>
       </c>
       <c r="D75">
-        <v>934.8961237417979</v>
+        <v>1008.017524522286</v>
       </c>
       <c r="E75">
         <v>118.332</v>
@@ -7431,37 +7431,37 @@
         <v>166.6</v>
       </c>
       <c r="M75">
-        <v>76.4317008</v>
+        <v>70.73898560000001</v>
       </c>
       <c r="N75">
-        <v>90.16829920000002</v>
+        <v>95.86101440000002</v>
       </c>
       <c r="O75">
-        <v>23.26342119360001</v>
+        <v>24.7321417152</v>
       </c>
       <c r="P75">
-        <v>66.90487800640001</v>
+        <v>71.12887268480002</v>
       </c>
       <c r="Q75">
-        <v>124.3048780064</v>
+        <v>128.5288726848</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1739945978630202</v>
+        <v>0.173912180134444</v>
       </c>
       <c r="T75">
         <v>2.958710857608407</v>
       </c>
       <c r="U75">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V75">
         <v>0.258</v>
       </c>
       <c r="W75">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.17972383521786</v>
+        <v>2.355136967075762</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09138017154578684</v>
+        <v>0.08800860149335624</v>
       </c>
       <c r="C76">
-        <v>259.6663257211646</v>
+        <v>333.733236082034</v>
       </c>
       <c r="D76">
-        <v>934.0823257211647</v>
+        <v>1008.149236082034</v>
       </c>
       <c r="E76">
         <v>131.116</v>
@@ -7513,37 +7513,37 @@
         <v>166.6</v>
       </c>
       <c r="M76">
-        <v>77.47871040000001</v>
+        <v>71.70801280000001</v>
       </c>
       <c r="N76">
-        <v>89.12128960000001</v>
+        <v>94.89198720000002</v>
       </c>
       <c r="O76">
-        <v>22.9932927168</v>
+        <v>24.4821326976</v>
       </c>
       <c r="P76">
-        <v>66.12799688320001</v>
+        <v>70.40985450240001</v>
       </c>
       <c r="Q76">
-        <v>123.5279968832</v>
+        <v>127.8098545024</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1785019982530263</v>
+        <v>0.1784166826667547</v>
       </c>
       <c r="T76">
         <v>3.062740939186021</v>
       </c>
       <c r="U76">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.258</v>
       </c>
       <c r="W76">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.150268107714916</v>
+        <v>2.323310791845008</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09141984766855822</v>
+        <v>0.08800308635041257</v>
       </c>
       <c r="C77">
-        <v>246.0699432401194</v>
+        <v>321.0809820661874</v>
       </c>
       <c r="D77">
-        <v>933.2699432401196</v>
+        <v>1008.280982066187</v>
       </c>
       <c r="E77">
         <v>143.9</v>
@@ -7595,37 +7595,37 @@
         <v>166.6</v>
       </c>
       <c r="M77">
-        <v>78.52572000000001</v>
+        <v>72.67704000000001</v>
       </c>
       <c r="N77">
-        <v>88.07428000000002</v>
+        <v>93.92296000000002</v>
       </c>
       <c r="O77">
-        <v>22.72316424000001</v>
+        <v>24.23212368</v>
       </c>
       <c r="P77">
-        <v>65.35111576000001</v>
+        <v>69.69083632000002</v>
       </c>
       <c r="Q77">
-        <v>122.75111576</v>
+        <v>127.09083632</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1833699906742329</v>
+        <v>0.1832815454016503</v>
       </c>
       <c r="T77">
         <v>3.175093427289844</v>
       </c>
       <c r="U77">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V77">
         <v>0.258</v>
       </c>
       <c r="W77">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.121597866278718</v>
+        <v>2.292333314620409</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.0914595237913296</v>
+        <v>0.0879975712074689</v>
       </c>
       <c r="C78">
-        <v>232.4749726085365</v>
+        <v>308.4287624882438</v>
       </c>
       <c r="D78">
-        <v>932.4589726085366</v>
+        <v>1008.412762488244</v>
       </c>
       <c r="E78">
         <v>156.684</v>
@@ -7677,37 +7677,37 @@
         <v>166.6</v>
       </c>
       <c r="M78">
-        <v>79.5727296</v>
+        <v>73.6460672</v>
       </c>
       <c r="N78">
-        <v>87.02727040000002</v>
+        <v>92.95393280000002</v>
       </c>
       <c r="O78">
-        <v>22.45303576320001</v>
+        <v>23.9821146624</v>
       </c>
       <c r="P78">
-        <v>64.57423463680001</v>
+        <v>68.97181813760001</v>
       </c>
       <c r="Q78">
-        <v>121.9742346368</v>
+        <v>126.3718181376</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.18864364913054</v>
+        <v>0.1885518133644538</v>
       </c>
       <c r="T78">
         <v>3.296808622735653</v>
       </c>
       <c r="U78">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.258</v>
       </c>
       <c r="W78">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.093682104880314</v>
+        <v>2.262171034164877</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.09149919991410098</v>
+        <v>0.08799205606452525</v>
       </c>
       <c r="C79">
-        <v>218.8814101491056</v>
+        <v>295.7765773617078</v>
       </c>
       <c r="D79">
-        <v>931.6494101491055</v>
+        <v>1008.544577361708</v>
       </c>
       <c r="E79">
         <v>169.468</v>
@@ -7759,37 +7759,37 @@
         <v>166.6</v>
       </c>
       <c r="M79">
-        <v>80.6197392</v>
+        <v>74.6150944</v>
       </c>
       <c r="N79">
-        <v>85.98026080000002</v>
+        <v>91.98490560000002</v>
       </c>
       <c r="O79">
-        <v>22.18290728640001</v>
+        <v>23.7321056448</v>
       </c>
       <c r="P79">
-        <v>63.79735351360002</v>
+        <v>68.25279995520002</v>
       </c>
       <c r="Q79">
-        <v>121.1973535136</v>
+        <v>125.6527999552</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1943758865830477</v>
+        <v>0.1942803654979358</v>
       </c>
       <c r="T79">
         <v>3.429107748220227</v>
       </c>
       <c r="U79">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.258</v>
       </c>
       <c r="W79">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.066491428193556</v>
+        <v>2.232792189565333</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09153887603687236</v>
+        <v>0.08798654092158158</v>
       </c>
       <c r="C80">
-        <v>205.2892521972757</v>
+        <v>283.1244267000915</v>
       </c>
       <c r="D80">
-        <v>930.8412521972757</v>
+        <v>1008.676426700092</v>
       </c>
       <c r="E80">
         <v>182.2520000000001</v>
@@ -7841,37 +7841,37 @@
         <v>166.6</v>
       </c>
       <c r="M80">
-        <v>81.66674880000001</v>
+        <v>75.58412160000002</v>
       </c>
       <c r="N80">
-        <v>84.93325120000002</v>
+        <v>91.01587840000001</v>
       </c>
       <c r="O80">
-        <v>21.91277880960001</v>
+        <v>23.4820966272</v>
       </c>
       <c r="P80">
-        <v>63.02047239040001</v>
+        <v>67.53378177280001</v>
       </c>
       <c r="Q80">
-        <v>120.4204723904</v>
+        <v>124.9337817728</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.200629236531238</v>
+        <v>0.2005296950980981</v>
       </c>
       <c r="T80">
         <v>3.573434066930672</v>
       </c>
       <c r="U80">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.258</v>
       </c>
       <c r="W80">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.03999794834492</v>
+        <v>2.204166648673469</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09157855215964375</v>
+        <v>0.08798102577863792</v>
       </c>
       <c r="C81">
-        <v>191.6984951012</v>
+        <v>270.4723105169132</v>
       </c>
       <c r="D81">
-        <v>930.0344951012002</v>
+        <v>1008.808310516913</v>
       </c>
       <c r="E81">
         <v>195.0360000000001</v>
@@ -7923,37 +7923,37 @@
         <v>166.6</v>
       </c>
       <c r="M81">
-        <v>82.71375840000002</v>
+        <v>76.55314880000002</v>
       </c>
       <c r="N81">
-        <v>83.88624160000001</v>
+        <v>90.04685120000001</v>
       </c>
       <c r="O81">
-        <v>21.6426503328</v>
+        <v>23.2320876096</v>
       </c>
       <c r="P81">
-        <v>62.2435912672</v>
+        <v>66.81476359040001</v>
       </c>
       <c r="Q81">
-        <v>119.6435912672</v>
+        <v>124.2147635904</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2074781436173512</v>
+        <v>0.2073741989458949</v>
       </c>
       <c r="T81">
         <v>3.731505749327826</v>
       </c>
       <c r="U81">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V81">
         <v>0.258</v>
       </c>
       <c r="W81">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.014175189505111</v>
+        <v>2.176265805019375</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1012939082824151</v>
+        <v>0.08797551063569425</v>
       </c>
       <c r="C82">
-        <v>16.09272590111584</v>
+        <v>257.8202288256995</v>
       </c>
       <c r="D82">
-        <v>767.212725901116</v>
+        <v>1008.9402288257</v>
       </c>
       <c r="E82">
         <v>207.8200000000001</v>
@@ -8005,45 +8005,45 @@
         <v>166.6</v>
       </c>
       <c r="M82">
-        <v>100.431104</v>
+        <v>77.52217600000002</v>
       </c>
       <c r="N82">
-        <v>66.168896</v>
+        <v>89.07782400000001</v>
       </c>
       <c r="O82">
-        <v>17.071575168</v>
+        <v>22.982078592</v>
       </c>
       <c r="P82">
-        <v>49.097320832</v>
+        <v>66.095745408</v>
       </c>
       <c r="Q82">
-        <v>106.497320832</v>
+        <v>123.495745408</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2150119414120757</v>
+        <v>0.2149031531784713</v>
       </c>
       <c r="T82">
         <v>3.905384599964695</v>
       </c>
       <c r="U82">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.258</v>
       </c>
       <c r="W82">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.658848637171209</v>
+        <v>2.149062482456633</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1014545304051865</v>
+        <v>0.08796999549275059</v>
       </c>
       <c r="C83">
-        <v>1.09450657783168</v>
+        <v>245.168181639983</v>
       </c>
       <c r="D83">
-        <v>764.9985065778319</v>
+        <v>1009.072181639983</v>
       </c>
       <c r="E83">
         <v>220.604</v>
@@ -8087,45 +8087,45 @@
         <v>166.6</v>
       </c>
       <c r="M83">
-        <v>101.6864928</v>
+        <v>78.49120320000002</v>
       </c>
       <c r="N83">
-        <v>64.9135072</v>
+        <v>88.10879680000001</v>
       </c>
       <c r="O83">
-        <v>16.7476848576</v>
+        <v>22.7320695744</v>
       </c>
       <c r="P83">
-        <v>48.1658223424</v>
+        <v>65.37672722560001</v>
       </c>
       <c r="Q83">
-        <v>105.5658223424</v>
+        <v>122.7767272256</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2233387705536133</v>
+        <v>0.2232246289092137</v>
       </c>
       <c r="T83">
         <v>4.097566487510708</v>
       </c>
       <c r="U83">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
         <v>0.258</v>
       </c>
       <c r="W83">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.638369024366626</v>
+        <v>2.122530846870748</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1016151525279579</v>
+        <v>0.08796448034980693</v>
       </c>
       <c r="C84">
-        <v>-13.890968800775</v>
+        <v>232.5161689733034</v>
       </c>
       <c r="D84">
-        <v>762.7970311992252</v>
+        <v>1009.204168973304</v>
       </c>
       <c r="E84">
         <v>233.3880000000001</v>
@@ -8169,45 +8169,45 @@
         <v>166.6</v>
       </c>
       <c r="M84">
-        <v>102.9418816</v>
+        <v>79.46023040000003</v>
       </c>
       <c r="N84">
-        <v>63.65811839999999</v>
+        <v>87.13976959999999</v>
       </c>
       <c r="O84">
-        <v>16.4237945472</v>
+        <v>22.4820605568</v>
       </c>
       <c r="P84">
-        <v>47.23432385279999</v>
+        <v>64.65770904319999</v>
       </c>
       <c r="Q84">
-        <v>104.6343238528</v>
+        <v>122.0577090432</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2325908029330995</v>
+        <v>0.232470713054483</v>
       </c>
       <c r="T84">
         <v>4.31110191811739</v>
       </c>
       <c r="U84">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.258</v>
       </c>
       <c r="W84">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.618388914313375</v>
+        <v>2.096646324347934</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1017757746507293</v>
+        <v>0.08795896520686326</v>
       </c>
       <c r="C85">
-        <v>-28.86380994070396</v>
+        <v>219.8641908392087</v>
       </c>
       <c r="D85">
-        <v>760.6081900592961</v>
+        <v>1009.336190839209</v>
       </c>
       <c r="E85">
         <v>246.172</v>
@@ -8251,45 +8251,45 @@
         <v>166.6</v>
       </c>
       <c r="M85">
-        <v>104.1972704</v>
+        <v>80.42925760000001</v>
       </c>
       <c r="N85">
-        <v>62.4027296</v>
+        <v>86.17074240000001</v>
       </c>
       <c r="O85">
-        <v>16.0999042368</v>
+        <v>22.2320515392</v>
       </c>
       <c r="P85">
-        <v>46.3028253632</v>
+        <v>63.93869086080001</v>
       </c>
       <c r="Q85">
-        <v>103.7028253632</v>
+        <v>121.3386908608</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2429313097101723</v>
+        <v>0.2428045718050781</v>
       </c>
       <c r="T85">
         <v>4.549759164089563</v>
       </c>
       <c r="U85">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V85">
         <v>0.258</v>
       </c>
       <c r="W85">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.598890252695142</v>
+        <v>2.071385525259405</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1019363967735007</v>
+        <v>0.08795345006391959</v>
       </c>
       <c r="C86">
-        <v>-43.82412529235626</v>
+        <v>207.2122472512522</v>
       </c>
       <c r="D86">
-        <v>758.4318747076437</v>
+        <v>1009.468247251252</v>
       </c>
       <c r="E86">
         <v>258.9559999999999</v>
@@ -8333,45 +8333,45 @@
         <v>166.6</v>
       </c>
       <c r="M86">
-        <v>105.4526592</v>
+        <v>81.39828480000001</v>
       </c>
       <c r="N86">
-        <v>61.14734080000001</v>
+        <v>85.20171520000001</v>
       </c>
       <c r="O86">
-        <v>15.7760139264</v>
+        <v>21.9820425216</v>
       </c>
       <c r="P86">
-        <v>45.3713268736</v>
+        <v>63.2196726784</v>
       </c>
       <c r="Q86">
-        <v>102.7713268736</v>
+        <v>120.6196726784</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2545643798343791</v>
+        <v>0.2544301628994974</v>
       </c>
       <c r="T86">
         <v>4.818248565808255</v>
       </c>
       <c r="U86">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
         <v>0.258</v>
       </c>
       <c r="W86">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.579855844924961</v>
+        <v>2.046726173768222</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1020970188962721</v>
+        <v>0.08794793492097594</v>
       </c>
       <c r="C87">
-        <v>-58.77202206844481</v>
+        <v>194.5603382229949</v>
       </c>
       <c r="D87">
-        <v>756.2679779315554</v>
+        <v>1009.600338222995</v>
       </c>
       <c r="E87">
         <v>271.74</v>
@@ -8415,45 +8415,45 @@
         <v>166.6</v>
       </c>
       <c r="M87">
-        <v>106.708048</v>
+        <v>82.36731200000001</v>
       </c>
       <c r="N87">
-        <v>59.891952</v>
+        <v>84.23268800000001</v>
       </c>
       <c r="O87">
-        <v>15.452123616</v>
+        <v>21.732033504</v>
       </c>
       <c r="P87">
-        <v>44.439828384</v>
+        <v>62.50065449600001</v>
       </c>
       <c r="Q87">
-        <v>101.839828384</v>
+        <v>119.900654496</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2677485259751469</v>
+        <v>0.2676058328065062</v>
       </c>
       <c r="T87">
         <v>5.122536554422776</v>
       </c>
       <c r="U87">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V87">
         <v>0.258</v>
       </c>
       <c r="W87">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.561269305572903</v>
+        <v>2.022647042312125</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1022576410190434</v>
+        <v>0.09700372377803228</v>
       </c>
       <c r="C88">
-        <v>-73.70760626159927</v>
+        <v>3.22042825453741</v>
       </c>
       <c r="D88">
-        <v>754.1163937384007</v>
+        <v>831.0444282545374</v>
       </c>
       <c r="E88">
         <v>284.5239999999999</v>
@@ -8497,37 +8497,37 @@
         <v>166.6</v>
       </c>
       <c r="M88">
-        <v>107.9634368</v>
+        <v>98.94816000000002</v>
       </c>
       <c r="N88">
-        <v>58.63656320000001</v>
+        <v>67.65184000000001</v>
       </c>
       <c r="O88">
-        <v>15.1282333056</v>
+        <v>17.45417472</v>
       </c>
       <c r="P88">
-        <v>43.50832989440001</v>
+        <v>50.19766528000001</v>
       </c>
       <c r="Q88">
-        <v>100.9083298944</v>
+        <v>107.59766528</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2828161215645958</v>
+        <v>0.2826637412716591</v>
       </c>
       <c r="T88">
         <v>5.470294255696515</v>
       </c>
       <c r="U88">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V88">
         <v>0.258</v>
       </c>
       <c r="W88">
-        <v>0.07286440000000001</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.543115011322055</v>
+        <v>1.683709934575842</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1024182631418148</v>
+        <v>0.09710357263508862</v>
       </c>
       <c r="C89">
-        <v>-88.63098266167651</v>
+        <v>-11.18098028179338</v>
       </c>
       <c r="D89">
-        <v>751.9770173383235</v>
+        <v>829.4270197182067</v>
       </c>
       <c r="E89">
         <v>297.308</v>
@@ -8579,37 +8579,37 @@
         <v>166.6</v>
       </c>
       <c r="M89">
-        <v>109.2188256</v>
+        <v>100.09872</v>
       </c>
       <c r="N89">
-        <v>57.38117440000001</v>
+        <v>66.50128000000001</v>
       </c>
       <c r="O89">
-        <v>14.8043429952</v>
+        <v>17.15733024</v>
       </c>
       <c r="P89">
-        <v>42.5768314048</v>
+        <v>49.34394976</v>
       </c>
       <c r="Q89">
-        <v>99.97683140480001</v>
+        <v>106.74394976</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3002018087831907</v>
+        <v>0.3000382510391431</v>
       </c>
       <c r="T89">
         <v>5.871553141781596</v>
       </c>
       <c r="U89">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V89">
         <v>0.258</v>
       </c>
       <c r="W89">
-        <v>0.07286440000000001</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.525378057168928</v>
+        <v>1.664356946822097</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1025788852645862</v>
+        <v>0.09720342149214495</v>
       </c>
       <c r="C90">
-        <v>-103.5422548727696</v>
+        <v>-25.57610533001935</v>
       </c>
       <c r="D90">
-        <v>749.8497451272306</v>
+        <v>827.8158946699809</v>
       </c>
       <c r="E90">
         <v>310.0920000000001</v>
@@ -8661,37 +8661,37 @@
         <v>166.6</v>
       </c>
       <c r="M90">
-        <v>110.4742144</v>
+        <v>101.24928</v>
       </c>
       <c r="N90">
-        <v>56.1257856</v>
+        <v>65.35072</v>
       </c>
       <c r="O90">
-        <v>14.4804526848</v>
+        <v>16.86048576</v>
       </c>
       <c r="P90">
-        <v>41.6453329152</v>
+        <v>48.49023423999999</v>
       </c>
       <c r="Q90">
-        <v>99.04533291520001</v>
+        <v>105.89023424</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3204851105382183</v>
+        <v>0.3203085124345412</v>
       </c>
       <c r="T90">
         <v>6.33968850888086</v>
       </c>
       <c r="U90">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V90">
         <v>0.258</v>
       </c>
       <c r="W90">
-        <v>0.07286440000000001</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.50804421561019</v>
+        <v>1.645443799699119</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.150899765391656</v>
+        <v>0.09730327034920128</v>
       </c>
       <c r="C91">
-        <v>-461.0786861706167</v>
+        <v>-39.96498343534017</v>
       </c>
       <c r="D91">
-        <v>405.0973138293834</v>
+        <v>826.2110165646599</v>
       </c>
       <c r="E91">
         <v>322.876</v>
@@ -8743,45 +8743,45 @@
         <v>166.6</v>
       </c>
       <c r="M91">
-        <v>186.1401536</v>
+        <v>102.39984</v>
       </c>
       <c r="N91">
-        <v>-19.54015360000002</v>
+        <v>64.20016000000001</v>
       </c>
       <c r="O91">
-        <v>-5.041359628800007</v>
+        <v>16.56364128</v>
       </c>
       <c r="P91">
-        <v>-14.49879397120002</v>
+        <v>47.63651872000001</v>
       </c>
       <c r="Q91">
-        <v>42.90120602879999</v>
+        <v>105.03651872</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3538009619744353</v>
+        <v>0.3442642759018298</v>
       </c>
       <c r="T91">
-        <v>7.108613042503807</v>
+        <v>6.892939397270897</v>
       </c>
       <c r="U91">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V91">
-        <v>0.2309163239027218</v>
+        <v>0.258</v>
       </c>
       <c r="W91">
-        <v>0.1258220894095147</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8950245112508598</v>
+        <v>1.62695566711823</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.152077765391656</v>
+        <v>0.09740311920625763</v>
       </c>
       <c r="C92">
-        <v>-478.3528505425568</v>
+        <v>-54.34765086010589</v>
       </c>
       <c r="D92">
-        <v>400.6071494574434</v>
+        <v>824.6123491398941</v>
       </c>
       <c r="E92">
         <v>335.6600000000001</v>
@@ -8825,45 +8825,45 @@
         <v>166.6</v>
       </c>
       <c r="M92">
-        <v>188.2316160000001</v>
+        <v>103.5504</v>
       </c>
       <c r="N92">
-        <v>-21.63161600000004</v>
+        <v>63.0496</v>
       </c>
       <c r="O92">
-        <v>-5.58095692800001</v>
+        <v>16.2667968</v>
       </c>
       <c r="P92">
-        <v>-16.05065907200003</v>
+        <v>46.7828032</v>
       </c>
       <c r="Q92">
-        <v>41.34934092799998</v>
+        <v>104.1828032</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3846010581718788</v>
+        <v>0.3730111920625762</v>
       </c>
       <c r="T92">
-        <v>7.819474346754189</v>
+        <v>7.556840463338943</v>
       </c>
       <c r="U92">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V92">
-        <v>0.2283505869704694</v>
+        <v>0.258</v>
       </c>
       <c r="W92">
-        <v>0.1262418439716312</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.8850797944591836</v>
+        <v>1.608878381928027</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.153255765391656</v>
+        <v>0.09750296806331396</v>
       </c>
       <c r="C93">
-        <v>-495.5285667091191</v>
+        <v>-68.72414358654532</v>
       </c>
       <c r="D93">
-        <v>396.215433290881</v>
+        <v>823.0198564134548</v>
       </c>
       <c r="E93">
         <v>348.444</v>
@@ -8907,45 +8907,45 @@
         <v>166.6</v>
       </c>
       <c r="M93">
-        <v>190.3230784</v>
+        <v>104.70096</v>
       </c>
       <c r="N93">
-        <v>-23.72307840000002</v>
+        <v>61.89904</v>
       </c>
       <c r="O93">
-        <v>-6.120554227200005</v>
+        <v>15.96995232</v>
       </c>
       <c r="P93">
-        <v>-17.60252417280002</v>
+        <v>45.92908767999999</v>
       </c>
       <c r="Q93">
-        <v>39.79747582719999</v>
+        <v>103.32908768</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4222456201909766</v>
+        <v>0.4081463118145996</v>
       </c>
       <c r="T93">
-        <v>8.688304829726878</v>
+        <v>8.368275099644332</v>
       </c>
       <c r="U93">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V93">
-        <v>0.2258412398609038</v>
+        <v>0.258</v>
       </c>
       <c r="W93">
-        <v>0.1266523731587562</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.8753536428717201</v>
+        <v>1.591198399709038</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.154433765391656</v>
+        <v>0.0976028169203703</v>
       </c>
       <c r="C94">
-        <v>-512.6090373205716</v>
+        <v>-83.09449731946825</v>
       </c>
       <c r="D94">
-        <v>391.9189626794285</v>
+        <v>821.4335026805318</v>
       </c>
       <c r="E94">
         <v>361.2280000000001</v>
@@ -8989,45 +8989,45 @@
         <v>166.6</v>
       </c>
       <c r="M94">
-        <v>192.4145408000001</v>
+        <v>105.85152</v>
       </c>
       <c r="N94">
-        <v>-25.81454080000003</v>
+        <v>60.74848</v>
       </c>
       <c r="O94">
-        <v>-6.660151526400008</v>
+        <v>15.67310784</v>
       </c>
       <c r="P94">
-        <v>-19.15438927360002</v>
+        <v>45.07537216</v>
       </c>
       <c r="Q94">
-        <v>38.24561072639998</v>
+        <v>102.47537216</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4693013227148488</v>
+        <v>0.4520652115046289</v>
       </c>
       <c r="T94">
-        <v>9.774342933442741</v>
+        <v>9.382568395026071</v>
       </c>
       <c r="U94">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V94">
-        <v>0.2233864437754592</v>
+        <v>0.258</v>
       </c>
       <c r="W94">
-        <v>0.1270539777983349</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.8658389293622448</v>
+        <v>1.573902764929592</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.155611765391656</v>
+        <v>0.09770266577742663</v>
       </c>
       <c r="C95">
-        <v>-529.5973276021248</v>
+        <v>-97.45874748893243</v>
       </c>
       <c r="D95">
-        <v>387.7146723978752</v>
+        <v>819.8532525110675</v>
       </c>
       <c r="E95">
         <v>374.0119999999999</v>
@@ -9071,45 +9071,45 @@
         <v>166.6</v>
       </c>
       <c r="M95">
-        <v>194.5060032</v>
+        <v>107.00208</v>
       </c>
       <c r="N95">
-        <v>-27.90600320000001</v>
+        <v>59.59792</v>
       </c>
       <c r="O95">
-        <v>-7.199748825600004</v>
+        <v>15.37626336</v>
       </c>
       <c r="P95">
-        <v>-20.70625437440001</v>
+        <v>44.22165664</v>
       </c>
       <c r="Q95">
-        <v>36.69374562559999</v>
+        <v>101.62165664</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5298015116741128</v>
+        <v>0.5085323682489521</v>
       </c>
       <c r="T95">
-        <v>11.17067763822027</v>
+        <v>10.68665977480259</v>
       </c>
       <c r="U95">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V95">
-        <v>0.2209844390036801</v>
+        <v>0.258</v>
       </c>
       <c r="W95">
-        <v>0.127446945778998</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.8565288333475971</v>
+        <v>1.556979079285188</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.156789765391656</v>
+        <v>0.09780251463448297</v>
       </c>
       <c r="C96">
-        <v>-546.4963726468011</v>
+        <v>-111.8169292528828</v>
       </c>
       <c r="D96">
-        <v>383.599627353199</v>
+        <v>818.2790707471173</v>
       </c>
       <c r="E96">
         <v>386.796</v>
@@ -9153,45 +9153,45 @@
         <v>166.6</v>
       </c>
       <c r="M96">
-        <v>196.5974656</v>
+        <v>108.15264</v>
       </c>
       <c r="N96">
-        <v>-29.99746560000003</v>
+        <v>58.44736</v>
       </c>
       <c r="O96">
-        <v>-7.739346124800007</v>
+        <v>15.07941888</v>
       </c>
       <c r="P96">
-        <v>-22.25811947520002</v>
+        <v>43.36794112</v>
       </c>
       <c r="Q96">
-        <v>35.14188052479999</v>
+        <v>100.76794112</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6104684302864651</v>
+        <v>0.5838219105747166</v>
       </c>
       <c r="T96">
-        <v>13.03245724459032</v>
+        <v>12.42544828117128</v>
       </c>
       <c r="U96">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V96">
-        <v>0.2186335407164069</v>
+        <v>0.258</v>
       </c>
       <c r="W96">
-        <v>0.1278315527387959</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8474168244821971</v>
+        <v>1.54041547205875</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.157967765391656</v>
+        <v>0.0979023634915393</v>
       </c>
       <c r="C97">
-        <v>-563.3089842487552</v>
+        <v>-126.1690774997562</v>
       </c>
       <c r="D97">
-        <v>379.5710157512451</v>
+        <v>816.7109225002439</v>
       </c>
       <c r="E97">
         <v>399.5800000000002</v>
@@ -9235,45 +9235,45 @@
         <v>166.6</v>
       </c>
       <c r="M97">
-        <v>198.6889280000001</v>
+        <v>109.3032</v>
       </c>
       <c r="N97">
-        <v>-32.08892800000004</v>
+        <v>57.29679999999999</v>
       </c>
       <c r="O97">
-        <v>-8.27894342400001</v>
+        <v>14.7825744</v>
       </c>
       <c r="P97">
-        <v>-23.80998457600003</v>
+        <v>42.51422559999999</v>
       </c>
       <c r="Q97">
-        <v>33.59001542399998</v>
+        <v>99.91422559999999</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7234021163437585</v>
+        <v>0.6892272698307869</v>
       </c>
       <c r="T97">
-        <v>15.6389486935084</v>
+        <v>14.85975219008746</v>
       </c>
       <c r="U97">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V97">
-        <v>0.2163321350246552</v>
+        <v>0.258</v>
       </c>
       <c r="W97">
-        <v>0.1282080627099664</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8384966473823845</v>
+        <v>1.524200572352868</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.159145765391656</v>
+        <v>0.09800221234859566</v>
       </c>
       <c r="C98">
-        <v>-580.0378573104872</v>
+        <v>-140.5152268510619</v>
       </c>
       <c r="D98">
-        <v>375.6261426895128</v>
+        <v>815.1487731489381</v>
       </c>
       <c r="E98">
         <v>412.364</v>
@@ -9317,45 +9317,45 @@
         <v>166.6</v>
       </c>
       <c r="M98">
-        <v>200.7803904</v>
+        <v>110.45376</v>
       </c>
       <c r="N98">
-        <v>-34.18039040000002</v>
+        <v>56.14623999999999</v>
       </c>
       <c r="O98">
-        <v>-8.818540723200005</v>
+        <v>14.48572992</v>
       </c>
       <c r="P98">
-        <v>-25.36184967680002</v>
+        <v>41.66051007999999</v>
       </c>
       <c r="Q98">
-        <v>32.03815032319999</v>
+        <v>99.06051008</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8928026454296963</v>
+        <v>0.8473353087148904</v>
       </c>
       <c r="T98">
-        <v>19.54868586688545</v>
+        <v>18.51120805346167</v>
       </c>
       <c r="U98">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V98">
-        <v>0.2140786752848151</v>
+        <v>0.258</v>
       </c>
       <c r="W98">
-        <v>0.1285767287234043</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.8297623073054847</v>
+        <v>1.508323483057525</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.160323765391656</v>
+        <v>0.1430036600019378</v>
       </c>
       <c r="C99">
-        <v>-596.6855758546251</v>
+        <v>-530.6808485288541</v>
       </c>
       <c r="D99">
-        <v>371.7624241453749</v>
+        <v>437.7671514711459</v>
       </c>
       <c r="E99">
         <v>425.1479999999999</v>
@@ -9399,37 +9399,37 @@
         <v>166.6</v>
       </c>
       <c r="M99">
-        <v>202.8718528</v>
+        <v>182.0390464</v>
       </c>
       <c r="N99">
-        <v>-36.2718528</v>
+        <v>-15.4390464</v>
       </c>
       <c r="O99">
-        <v>-9.358138022400002</v>
+        <v>-3.983273971199999</v>
       </c>
       <c r="P99">
-        <v>-26.9137147776</v>
+        <v>-11.4557724288</v>
       </c>
       <c r="Q99">
-        <v>30.4862852224</v>
+        <v>45.94422757120001</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.175136860572928</v>
+        <v>1.14100001424899</v>
       </c>
       <c r="T99">
-        <v>26.0649144891806</v>
+        <v>25.2933028694917</v>
       </c>
       <c r="U99">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2118716786323943</v>
+        <v>0.2361185737347392</v>
       </c>
       <c r="W99">
-        <v>0.1289377933757403</v>
+        <v>0.1121377933757403</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8212080567147065</v>
+        <v>0.9151882702896866</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.161501765391656</v>
+        <v>0.1440136600019378</v>
       </c>
       <c r="C100">
-        <v>-613.2546186684563</v>
+        <v>-547.9667154074241</v>
       </c>
       <c r="D100">
-        <v>367.9773813315438</v>
+        <v>433.2652845925761</v>
       </c>
       <c r="E100">
         <v>437.932</v>
@@ -9481,37 +9481,37 @@
         <v>166.6</v>
       </c>
       <c r="M100">
-        <v>204.9633152</v>
+        <v>183.9157376</v>
       </c>
       <c r="N100">
-        <v>-38.36331520000002</v>
+        <v>-17.31573760000001</v>
       </c>
       <c r="O100">
-        <v>-9.897735321600004</v>
+        <v>-4.467460300800002</v>
       </c>
       <c r="P100">
-        <v>-28.46557987840001</v>
+        <v>-12.8482772992</v>
       </c>
       <c r="Q100">
-        <v>28.93442012159999</v>
+        <v>44.5517227008</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.739805290859393</v>
+        <v>1.688600021373486</v>
       </c>
       <c r="T100">
-        <v>39.09737173377091</v>
+        <v>37.93995430423755</v>
       </c>
       <c r="U100">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2097097227279821</v>
+        <v>0.2337092005333642</v>
       </c>
       <c r="W100">
-        <v>0.1292914893617021</v>
+        <v>0.1124914893617021</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8128283826665973</v>
+        <v>0.905849614470404</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.162679765391656</v>
+        <v>0.1450236600019378</v>
       </c>
       <c r="C101">
-        <v>-629.7473646071221</v>
+        <v>-565.1609330654902</v>
       </c>
       <c r="D101">
-        <v>364.2686353928778</v>
+        <v>428.8550669345098</v>
       </c>
       <c r="E101">
         <v>450.7159999999999</v>
@@ -9563,37 +9563,37 @@
         <v>166.6</v>
       </c>
       <c r="M101">
-        <v>207.0547776</v>
+        <v>185.7924288</v>
       </c>
       <c r="N101">
-        <v>-40.4547776</v>
+        <v>-19.19242879999999</v>
       </c>
       <c r="O101">
-        <v>-10.4373326208</v>
+        <v>-4.951646630399997</v>
       </c>
       <c r="P101">
-        <v>-30.0174449792</v>
+        <v>-14.24078216959999</v>
       </c>
       <c r="Q101">
-        <v>27.38255502080001</v>
+        <v>43.15921783040002</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.433810581718785</v>
+        <v>3.331400042746971</v>
       </c>
       <c r="T101">
-        <v>78.1947434675418</v>
+        <v>75.87990860847509</v>
       </c>
       <c r="U101">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V101">
-        <v>0.2075914427004267</v>
+        <v>0.2313485015380778</v>
       </c>
       <c r="W101">
-        <v>0.1296380399742102</v>
+        <v>0.1128380399742102</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.8046179949628943</v>
+        <v>0.8966996183646425</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_metals_mining.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08841672207118731</v>
+        <v>0.08822199692824366</v>
       </c>
       <c r="C2">
-        <v>1270.094658517799</v>
+        <v>1261.893941465021</v>
       </c>
       <c r="D2">
-        <v>998.4946585177984</v>
+        <v>1003.077941465021</v>
       </c>
       <c r="E2">
-        <v>-814.9000000000001</v>
+        <v>-802.1160000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12.784</v>
       </c>
       <c r="G2">
         <v>271.6</v>
@@ -1445,28 +1445,28 @@
         <v>166.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6430352000000001</v>
       </c>
       <c r="N2">
-        <v>166.6</v>
+        <v>165.9569648</v>
       </c>
       <c r="O2">
-        <v>42.9828</v>
+        <v>42.8168969184</v>
       </c>
       <c r="P2">
-        <v>123.6172</v>
+        <v>123.1400678816</v>
       </c>
       <c r="Q2">
-        <v>181.0172</v>
+        <v>180.5400678816</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08841672207118731</v>
+        <v>0.08873613225075117</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.991596587777163</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>259.08379510173</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08822199692824366</v>
+        <v>0.08802727178529997</v>
       </c>
       <c r="C3">
-        <v>1261.893941465021</v>
+        <v>1253.735494745577</v>
       </c>
       <c r="D3">
-        <v>1003.077941465021</v>
+        <v>1007.703494745577</v>
       </c>
       <c r="E3">
-        <v>-802.1160000000001</v>
+        <v>-789.3320000000001</v>
       </c>
       <c r="F3">
-        <v>12.784</v>
+        <v>25.568</v>
       </c>
       <c r="G3">
         <v>271.6</v>
@@ -1527,28 +1527,28 @@
         <v>166.6</v>
       </c>
       <c r="M3">
-        <v>0.6430352000000001</v>
+        <v>1.2860704</v>
       </c>
       <c r="N3">
-        <v>165.9569648</v>
+        <v>165.3139296</v>
       </c>
       <c r="O3">
-        <v>42.8168969184</v>
+        <v>42.6509938368</v>
       </c>
       <c r="P3">
-        <v>123.1400678816</v>
+        <v>122.6629357632</v>
       </c>
       <c r="Q3">
-        <v>180.5400678816</v>
+        <v>180.0629357632</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08873613225075117</v>
+        <v>0.08906206100540814</v>
       </c>
       <c r="T3">
-        <v>0.991596587777163</v>
+        <v>0.9991238107484561</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>259.08379510173</v>
+        <v>129.541897550865</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08802727178529997</v>
+        <v>0.08783254664235632</v>
       </c>
       <c r="C4">
-        <v>1253.735494745577</v>
+        <v>1245.619905839694</v>
       </c>
       <c r="D4">
-        <v>1007.703494745577</v>
+        <v>1012.371905839694</v>
       </c>
       <c r="E4">
-        <v>-789.3320000000001</v>
+        <v>-776.5480000000001</v>
       </c>
       <c r="F4">
-        <v>25.568</v>
+        <v>38.352</v>
       </c>
       <c r="G4">
         <v>271.6</v>
@@ -1609,28 +1609,28 @@
         <v>166.6</v>
       </c>
       <c r="M4">
-        <v>1.2860704</v>
+        <v>1.9291056</v>
       </c>
       <c r="N4">
-        <v>165.3139296</v>
+        <v>164.6708944</v>
       </c>
       <c r="O4">
-        <v>42.6509938368</v>
+        <v>42.48509075520001</v>
       </c>
       <c r="P4">
-        <v>122.6629357632</v>
+        <v>122.1858036448</v>
       </c>
       <c r="Q4">
-        <v>180.0629357632</v>
+        <v>179.5858036448</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08906206100540814</v>
+        <v>0.08939470994057352</v>
       </c>
       <c r="T4">
-        <v>0.9991238107484561</v>
+        <v>1.006806234193384</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>129.541897550865</v>
+        <v>86.36126503391</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08783254664235632</v>
+        <v>0.08763782149941265</v>
       </c>
       <c r="C5">
-        <v>1245.619905839694</v>
+        <v>1237.547773164802</v>
       </c>
       <c r="D5">
-        <v>1012.371905839694</v>
+        <v>1017.083773164802</v>
       </c>
       <c r="E5">
-        <v>-776.5480000000001</v>
+        <v>-763.7640000000001</v>
       </c>
       <c r="F5">
-        <v>38.352</v>
+        <v>51.136</v>
       </c>
       <c r="G5">
         <v>271.6</v>
@@ -1691,28 +1691,28 @@
         <v>166.6</v>
       </c>
       <c r="M5">
-        <v>1.9291056</v>
+        <v>2.572140800000001</v>
       </c>
       <c r="N5">
-        <v>164.6708944</v>
+        <v>164.0278592</v>
       </c>
       <c r="O5">
-        <v>42.48509075520001</v>
+        <v>42.31918767360001</v>
       </c>
       <c r="P5">
-        <v>122.1858036448</v>
+        <v>121.7086715264</v>
       </c>
       <c r="Q5">
-        <v>179.5858036448</v>
+        <v>179.1086715264</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08939470994057352</v>
+        <v>0.08973428906188818</v>
       </c>
       <c r="T5">
-        <v>1.006806234193384</v>
+        <v>1.014648708126748</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>86.36126503391</v>
+        <v>64.77094877543252</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08763782149941265</v>
+        <v>0.08744309635646899</v>
       </c>
       <c r="C6">
-        <v>1237.547773164802</v>
+        <v>1229.519706331247</v>
       </c>
       <c r="D6">
-        <v>1017.083773164802</v>
+        <v>1021.839706331247</v>
       </c>
       <c r="E6">
-        <v>-763.7640000000001</v>
+        <v>-750.9800000000001</v>
       </c>
       <c r="F6">
-        <v>51.136</v>
+        <v>63.92000000000001</v>
       </c>
       <c r="G6">
         <v>271.6</v>
@@ -1773,28 +1773,28 @@
         <v>166.6</v>
       </c>
       <c r="M6">
-        <v>2.572140800000001</v>
+        <v>3.215176000000001</v>
       </c>
       <c r="N6">
-        <v>164.0278592</v>
+        <v>163.384824</v>
       </c>
       <c r="O6">
-        <v>42.31918767360001</v>
+        <v>42.15328459200001</v>
       </c>
       <c r="P6">
-        <v>121.7086715264</v>
+        <v>121.231539408</v>
       </c>
       <c r="Q6">
-        <v>179.1086715264</v>
+        <v>178.631539408</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08973428906188818</v>
+        <v>0.09008101721733579</v>
       </c>
       <c r="T6">
-        <v>1.014648708126748</v>
+        <v>1.022656286774499</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>64.77094877543252</v>
+        <v>51.816759020346</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08744309635646899</v>
+        <v>0.08724837121352533</v>
       </c>
       <c r="C7">
-        <v>1229.519706331247</v>
+        <v>1221.536326405213</v>
       </c>
       <c r="D7">
-        <v>1021.839706331247</v>
+        <v>1026.640326405213</v>
       </c>
       <c r="E7">
-        <v>-750.9800000000001</v>
+        <v>-738.1960000000001</v>
       </c>
       <c r="F7">
-        <v>63.92000000000001</v>
+        <v>76.70400000000001</v>
       </c>
       <c r="G7">
         <v>271.6</v>
@@ -1855,28 +1855,28 @@
         <v>166.6</v>
       </c>
       <c r="M7">
-        <v>3.215176000000001</v>
+        <v>3.858211200000001</v>
       </c>
       <c r="N7">
-        <v>163.384824</v>
+        <v>162.7417888</v>
       </c>
       <c r="O7">
-        <v>42.15328459200001</v>
+        <v>41.98738151040001</v>
       </c>
       <c r="P7">
-        <v>121.231539408</v>
+        <v>120.7544072896</v>
       </c>
       <c r="Q7">
-        <v>178.631539408</v>
+        <v>178.1544072896</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09008101721733579</v>
+        <v>0.09043512256758014</v>
       </c>
       <c r="T7">
-        <v>1.022656286774499</v>
+        <v>1.030834239436031</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.816759020346</v>
+        <v>43.18063251695501</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08724837121352533</v>
+        <v>0.08705364607058168</v>
       </c>
       <c r="C8">
-        <v>1221.536326405213</v>
+        <v>1213.598266179092</v>
       </c>
       <c r="D8">
-        <v>1026.640326405213</v>
+        <v>1031.486266179093</v>
       </c>
       <c r="E8">
-        <v>-738.1960000000001</v>
+        <v>-725.412</v>
       </c>
       <c r="F8">
-        <v>76.70400000000001</v>
+        <v>89.488</v>
       </c>
       <c r="G8">
         <v>271.6</v>
@@ -1937,28 +1937,28 @@
         <v>166.6</v>
       </c>
       <c r="M8">
-        <v>3.858211200000001</v>
+        <v>4.5012464</v>
       </c>
       <c r="N8">
-        <v>162.7417888</v>
+        <v>162.0987536</v>
       </c>
       <c r="O8">
-        <v>41.98738151040001</v>
+        <v>41.82147842880001</v>
       </c>
       <c r="P8">
-        <v>120.7544072896</v>
+        <v>120.2772751712</v>
       </c>
       <c r="Q8">
-        <v>178.1544072896</v>
+        <v>177.6772751712</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09043512256758014</v>
+        <v>0.09079684308664696</v>
       </c>
       <c r="T8">
-        <v>1.030834239436031</v>
+        <v>1.039188062047274</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>43.18063251695501</v>
+        <v>37.01197072881858</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08705364607058166</v>
+        <v>0.08685892092763801</v>
       </c>
       <c r="C9">
-        <v>1213.598266179093</v>
+        <v>1205.706170449547</v>
       </c>
       <c r="D9">
-        <v>1031.486266179093</v>
+        <v>1036.378170449547</v>
       </c>
       <c r="E9">
-        <v>-725.412</v>
+        <v>-712.628</v>
       </c>
       <c r="F9">
-        <v>89.48800000000001</v>
+        <v>102.272</v>
       </c>
       <c r="G9">
         <v>271.6</v>
@@ -2019,28 +2019,28 @@
         <v>166.6</v>
       </c>
       <c r="M9">
-        <v>4.501246400000001</v>
+        <v>5.144281600000001</v>
       </c>
       <c r="N9">
-        <v>162.0987536</v>
+        <v>161.4557184</v>
       </c>
       <c r="O9">
-        <v>41.82147842880001</v>
+        <v>41.65557534720001</v>
       </c>
       <c r="P9">
-        <v>120.2772751712</v>
+        <v>119.8001430528</v>
       </c>
       <c r="Q9">
-        <v>177.6772751712</v>
+        <v>177.2001430528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09079684308664696</v>
+        <v>0.0911664270952587</v>
       </c>
       <c r="T9">
-        <v>1.039188062047274</v>
+        <v>1.047723489497892</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.01197072881857</v>
+        <v>32.38547438771626</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08685892092763801</v>
+        <v>0.08666419578469434</v>
       </c>
       <c r="C10">
-        <v>1205.706170449547</v>
+        <v>1197.860696303519</v>
       </c>
       <c r="D10">
-        <v>1036.378170449547</v>
+        <v>1041.316696303519</v>
       </c>
       <c r="E10">
-        <v>-712.628</v>
+        <v>-699.8440000000001</v>
       </c>
       <c r="F10">
-        <v>102.272</v>
+        <v>115.056</v>
       </c>
       <c r="G10">
         <v>271.6</v>
@@ -2101,28 +2101,28 @@
         <v>166.6</v>
       </c>
       <c r="M10">
-        <v>5.144281600000001</v>
+        <v>5.7873168</v>
       </c>
       <c r="N10">
-        <v>161.4557184</v>
+        <v>160.8126832</v>
       </c>
       <c r="O10">
-        <v>41.65557534720001</v>
+        <v>41.48967226560001</v>
       </c>
       <c r="P10">
-        <v>119.8001430528</v>
+        <v>119.3230109344</v>
       </c>
       <c r="Q10">
-        <v>177.2001430528</v>
+        <v>176.7230109344</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0911664270952587</v>
+        <v>0.09154413382933443</v>
       </c>
       <c r="T10">
-        <v>1.047723489497892</v>
+        <v>1.056446508760611</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.38547438771626</v>
+        <v>28.78708834463667</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08666419578469434</v>
+        <v>0.08646947064175069</v>
       </c>
       <c r="C11">
-        <v>1197.860696303519</v>
+        <v>1190.062513412462</v>
       </c>
       <c r="D11">
-        <v>1041.316696303519</v>
+        <v>1046.302513412462</v>
       </c>
       <c r="E11">
-        <v>-699.8440000000001</v>
+        <v>-687.0600000000001</v>
       </c>
       <c r="F11">
-        <v>115.056</v>
+        <v>127.84</v>
       </c>
       <c r="G11">
         <v>271.6</v>
@@ -2183,28 +2183,28 @@
         <v>166.6</v>
       </c>
       <c r="M11">
-        <v>5.7873168</v>
+        <v>6.430352000000001</v>
       </c>
       <c r="N11">
-        <v>160.8126832</v>
+        <v>160.169648</v>
       </c>
       <c r="O11">
-        <v>41.48967226560001</v>
+        <v>41.32376918400001</v>
       </c>
       <c r="P11">
-        <v>119.3230109344</v>
+        <v>118.845878816</v>
       </c>
       <c r="Q11">
-        <v>176.7230109344</v>
+        <v>176.245878816</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09154413382933443</v>
+        <v>0.09193023404638964</v>
       </c>
       <c r="T11">
-        <v>1.056446508760611</v>
+        <v>1.065363372895835</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.78708834463667</v>
+        <v>25.90837951017301</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08646947064175069</v>
+        <v>0.08627474549880702</v>
       </c>
       <c r="C12">
-        <v>1190.062513412462</v>
+        <v>1182.312304335065</v>
       </c>
       <c r="D12">
-        <v>1046.302513412462</v>
+        <v>1051.336304335065</v>
       </c>
       <c r="E12">
-        <v>-687.0600000000001</v>
+        <v>-674.2760000000001</v>
       </c>
       <c r="F12">
-        <v>127.84</v>
+        <v>140.624</v>
       </c>
       <c r="G12">
         <v>271.6</v>
@@ -2265,28 +2265,28 @@
         <v>166.6</v>
       </c>
       <c r="M12">
-        <v>6.430352000000002</v>
+        <v>7.073387200000002</v>
       </c>
       <c r="N12">
-        <v>160.169648</v>
+        <v>159.5266128</v>
       </c>
       <c r="O12">
-        <v>41.32376918400001</v>
+        <v>41.15786610240001</v>
       </c>
       <c r="P12">
-        <v>118.845878816</v>
+        <v>118.3687466976</v>
       </c>
       <c r="Q12">
-        <v>176.245878816</v>
+        <v>175.7687466976</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09193023404638964</v>
+        <v>0.09232501067281687</v>
       </c>
       <c r="T12">
-        <v>1.065363372895835</v>
+        <v>1.07448061600039</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.908379510173</v>
+        <v>23.55307228197545</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08627474549880702</v>
+        <v>0.08608002035586335</v>
       </c>
       <c r="C13">
-        <v>1182.312304335065</v>
+        <v>1174.610764828751</v>
       </c>
       <c r="D13">
-        <v>1051.336304335065</v>
+        <v>1056.418764828751</v>
       </c>
       <c r="E13">
-        <v>-674.2760000000001</v>
+        <v>-661.4920000000001</v>
       </c>
       <c r="F13">
-        <v>140.624</v>
+        <v>153.408</v>
       </c>
       <c r="G13">
         <v>271.6</v>
@@ -2347,28 +2347,28 @@
         <v>166.6</v>
       </c>
       <c r="M13">
-        <v>7.073387200000002</v>
+        <v>7.716422400000002</v>
       </c>
       <c r="N13">
-        <v>159.5266128</v>
+        <v>158.8835776</v>
       </c>
       <c r="O13">
-        <v>41.15786610240001</v>
+        <v>40.99196302080001</v>
       </c>
       <c r="P13">
-        <v>118.3687466976</v>
+        <v>117.8916145792</v>
       </c>
       <c r="Q13">
-        <v>175.7687466976</v>
+        <v>175.2916145792</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09232501067281687</v>
+        <v>0.09272875949529927</v>
       </c>
       <c r="T13">
-        <v>1.07448061600039</v>
+        <v>1.083805069175503</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.55307228197545</v>
+        <v>21.5903162584775</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08608002035586335</v>
+        <v>0.08588529521291968</v>
       </c>
       <c r="C14">
-        <v>1174.610764828751</v>
+        <v>1166.958604170259</v>
       </c>
       <c r="D14">
-        <v>1056.418764828751</v>
+        <v>1061.550604170259</v>
       </c>
       <c r="E14">
-        <v>-661.4920000000001</v>
+        <v>-648.7080000000001</v>
       </c>
       <c r="F14">
-        <v>153.408</v>
+        <v>166.192</v>
       </c>
       <c r="G14">
         <v>271.6</v>
@@ -2429,28 +2429,28 @@
         <v>166.6</v>
       </c>
       <c r="M14">
-        <v>7.716422400000002</v>
+        <v>8.359457600000001</v>
       </c>
       <c r="N14">
-        <v>158.8835776</v>
+        <v>158.2405424</v>
       </c>
       <c r="O14">
-        <v>40.99196302080001</v>
+        <v>40.8260599392</v>
       </c>
       <c r="P14">
-        <v>117.8916145792</v>
+        <v>117.4144824608</v>
       </c>
       <c r="Q14">
-        <v>175.2916145792</v>
+        <v>174.8144824608</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09272875949529927</v>
+        <v>0.09314178989990768</v>
       </c>
       <c r="T14">
-        <v>1.083805069175503</v>
+        <v>1.09334387759602</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.5903162584775</v>
+        <v>19.92952270013308</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08588529521291968</v>
+        <v>0.08569057006997603</v>
       </c>
       <c r="C15">
-        <v>1166.958604170259</v>
+        <v>1159.356545485622</v>
       </c>
       <c r="D15">
-        <v>1061.550604170259</v>
+        <v>1066.732545485622</v>
       </c>
       <c r="E15">
-        <v>-648.7080000000001</v>
+        <v>-635.9240000000001</v>
       </c>
       <c r="F15">
-        <v>166.192</v>
+        <v>178.976</v>
       </c>
       <c r="G15">
         <v>271.6</v>
@@ -2511,28 +2511,28 @@
         <v>166.6</v>
       </c>
       <c r="M15">
-        <v>8.359457600000001</v>
+        <v>9.002492800000002</v>
       </c>
       <c r="N15">
-        <v>158.2405424</v>
+        <v>157.5975072</v>
       </c>
       <c r="O15">
-        <v>40.8260599392</v>
+        <v>40.66015685760001</v>
       </c>
       <c r="P15">
-        <v>117.4144824608</v>
+        <v>116.9373503424</v>
       </c>
       <c r="Q15">
-        <v>174.8144824608</v>
+        <v>174.3373503424</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09314178989990768</v>
+        <v>0.09356442566276282</v>
       </c>
       <c r="T15">
-        <v>1.09334387759602</v>
+        <v>1.103104518770504</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.92952270013308</v>
+        <v>18.50598536440929</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08569057006997603</v>
+        <v>0.08549584492703236</v>
       </c>
       <c r="C16">
-        <v>1159.356545485622</v>
+        <v>1151.805326089843</v>
       </c>
       <c r="D16">
-        <v>1066.732545485622</v>
+        <v>1071.965326089844</v>
       </c>
       <c r="E16">
-        <v>-635.9240000000001</v>
+        <v>-623.1400000000001</v>
       </c>
       <c r="F16">
-        <v>178.976</v>
+        <v>191.76</v>
       </c>
       <c r="G16">
         <v>271.6</v>
@@ -2593,28 +2593,28 @@
         <v>166.6</v>
       </c>
       <c r="M16">
-        <v>9.002492800000002</v>
+        <v>9.645528000000004</v>
       </c>
       <c r="N16">
-        <v>157.5975072</v>
+        <v>156.954472</v>
       </c>
       <c r="O16">
-        <v>40.66015685760001</v>
+        <v>40.494253776</v>
       </c>
       <c r="P16">
-        <v>116.9373503424</v>
+        <v>116.460218224</v>
       </c>
       <c r="Q16">
-        <v>174.3373503424</v>
+        <v>173.860218224</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09356442566276282</v>
+        <v>0.09399700579650866</v>
       </c>
       <c r="T16">
-        <v>1.103104518770504</v>
+        <v>1.113094822090269</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.50598536440929</v>
+        <v>17.272253006782</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08549584492703236</v>
+        <v>0.08530111978408869</v>
       </c>
       <c r="C17">
-        <v>1151.805326089843</v>
+        <v>1144.305697836631</v>
       </c>
       <c r="D17">
-        <v>1071.965326089844</v>
+        <v>1077.249697836631</v>
       </c>
       <c r="E17">
-        <v>-623.1400000000001</v>
+        <v>-610.3560000000001</v>
       </c>
       <c r="F17">
-        <v>191.76</v>
+        <v>204.544</v>
       </c>
       <c r="G17">
         <v>271.6</v>
@@ -2675,28 +2675,28 @@
         <v>166.6</v>
       </c>
       <c r="M17">
-        <v>9.645528000000002</v>
+        <v>10.2885632</v>
       </c>
       <c r="N17">
-        <v>156.954472</v>
+        <v>156.3114368</v>
       </c>
       <c r="O17">
-        <v>40.494253776</v>
+        <v>40.32835069440001</v>
       </c>
       <c r="P17">
-        <v>116.460218224</v>
+        <v>115.9830861056</v>
       </c>
       <c r="Q17">
-        <v>173.860218224</v>
+        <v>173.3830861056</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09399700579650866</v>
+        <v>0.09443988545724845</v>
       </c>
       <c r="T17">
-        <v>1.113094822090269</v>
+        <v>1.123322989774791</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.272253006782</v>
+        <v>16.19273719385813</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08530111978408869</v>
+        <v>0.08510639464114504</v>
       </c>
       <c r="C18">
-        <v>1144.305697836631</v>
+        <v>1136.858427478521</v>
       </c>
       <c r="D18">
-        <v>1077.249697836631</v>
+        <v>1082.586427478521</v>
       </c>
       <c r="E18">
-        <v>-610.3560000000001</v>
+        <v>-597.5720000000001</v>
       </c>
       <c r="F18">
-        <v>204.544</v>
+        <v>217.328</v>
       </c>
       <c r="G18">
         <v>271.6</v>
@@ -2757,28 +2757,28 @@
         <v>166.6</v>
       </c>
       <c r="M18">
-        <v>10.2885632</v>
+        <v>10.9315984</v>
       </c>
       <c r="N18">
-        <v>156.3114368</v>
+        <v>155.6684016</v>
       </c>
       <c r="O18">
-        <v>40.32835069440001</v>
+        <v>40.1624476128</v>
       </c>
       <c r="P18">
-        <v>115.9830861056</v>
+        <v>115.5059539872</v>
       </c>
       <c r="Q18">
-        <v>173.3830861056</v>
+        <v>172.9059539872</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09443988545724845</v>
+        <v>0.09489343691704222</v>
       </c>
       <c r="T18">
-        <v>1.123322989774791</v>
+        <v>1.133797619331229</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.19273719385813</v>
+        <v>15.24022324127824</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08510639464114504</v>
+        <v>0.08491166949820136</v>
       </c>
       <c r="C19">
-        <v>1136.858427478521</v>
+        <v>1129.464297037767</v>
       </c>
       <c r="D19">
-        <v>1082.586427478521</v>
+        <v>1087.976297037767</v>
       </c>
       <c r="E19">
-        <v>-597.5720000000001</v>
+        <v>-584.788</v>
       </c>
       <c r="F19">
-        <v>217.328</v>
+        <v>230.1120000000001</v>
       </c>
       <c r="G19">
         <v>271.6</v>
@@ -2839,28 +2839,28 @@
         <v>166.6</v>
       </c>
       <c r="M19">
-        <v>10.9315984</v>
+        <v>11.5746336</v>
       </c>
       <c r="N19">
-        <v>155.6684016</v>
+        <v>155.0253664</v>
       </c>
       <c r="O19">
-        <v>40.1624476128</v>
+        <v>39.99654453120001</v>
       </c>
       <c r="P19">
-        <v>115.5059539872</v>
+        <v>115.0288218688</v>
       </c>
       <c r="Q19">
-        <v>172.9059539872</v>
+        <v>172.4288218688</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09489343691704222</v>
+        <v>0.09535805060756264</v>
       </c>
       <c r="T19">
-        <v>1.133797619331229</v>
+        <v>1.144527727657336</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.24022324127824</v>
+        <v>14.39354417231833</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08491166949820136</v>
+        <v>0.08471694435525771</v>
       </c>
       <c r="C20">
-        <v>1129.464297037767</v>
+        <v>1122.12410418835</v>
       </c>
       <c r="D20">
-        <v>1087.976297037767</v>
+        <v>1093.42010418835</v>
       </c>
       <c r="E20">
-        <v>-584.7880000000001</v>
+        <v>-572.0040000000001</v>
       </c>
       <c r="F20">
-        <v>230.112</v>
+        <v>242.896</v>
       </c>
       <c r="G20">
         <v>271.6</v>
@@ -2921,28 +2921,28 @@
         <v>166.6</v>
       </c>
       <c r="M20">
-        <v>11.5746336</v>
+        <v>12.2176688</v>
       </c>
       <c r="N20">
-        <v>155.0253664</v>
+        <v>154.3823312</v>
       </c>
       <c r="O20">
-        <v>39.99654453120001</v>
+        <v>39.8306414496</v>
       </c>
       <c r="P20">
-        <v>115.0288218688</v>
+        <v>114.5516897504</v>
       </c>
       <c r="Q20">
-        <v>172.4288218688</v>
+        <v>171.9516897504</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09535805060756264</v>
+        <v>0.09583413624105891</v>
       </c>
       <c r="T20">
-        <v>1.144527727657336</v>
+        <v>1.155522776929767</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.39354417231834</v>
+        <v>13.63598921588053</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08471694435525771</v>
+        <v>0.08452221921231405</v>
       </c>
       <c r="C21">
-        <v>1122.12410418835</v>
+        <v>1114.83866264953</v>
       </c>
       <c r="D21">
-        <v>1093.42010418835</v>
+        <v>1098.91866264953</v>
       </c>
       <c r="E21">
-        <v>-572.0040000000001</v>
+        <v>-559.22</v>
       </c>
       <c r="F21">
-        <v>242.896</v>
+        <v>255.68</v>
       </c>
       <c r="G21">
         <v>271.6</v>
@@ -3003,28 +3003,28 @@
         <v>166.6</v>
       </c>
       <c r="M21">
-        <v>12.2176688</v>
+        <v>12.860704</v>
       </c>
       <c r="N21">
-        <v>154.3823312</v>
+        <v>153.739296</v>
       </c>
       <c r="O21">
-        <v>39.8306414496</v>
+        <v>39.66473836800001</v>
       </c>
       <c r="P21">
-        <v>114.5516897504</v>
+        <v>114.074557632</v>
       </c>
       <c r="Q21">
-        <v>171.9516897504</v>
+        <v>171.474557632</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09583413624105891</v>
+        <v>0.09632212401539256</v>
       </c>
       <c r="T21">
-        <v>1.155522776929767</v>
+        <v>1.166792702434008</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.63598921588053</v>
+        <v>12.9541897550865</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08452221921231405</v>
+        <v>0.0845612240693704</v>
       </c>
       <c r="C22">
-        <v>1114.83866264953</v>
+        <v>1100.948836753101</v>
       </c>
       <c r="D22">
-        <v>1098.91866264953</v>
+        <v>1097.812836753101</v>
       </c>
       <c r="E22">
-        <v>-559.22</v>
+        <v>-546.436</v>
       </c>
       <c r="F22">
-        <v>255.68</v>
+        <v>268.4640000000001</v>
       </c>
       <c r="G22">
         <v>271.6</v>
@@ -3085,45 +3085,45 @@
         <v>166.6</v>
       </c>
       <c r="M22">
-        <v>12.860704</v>
+        <v>13.9064352</v>
       </c>
       <c r="N22">
-        <v>153.739296</v>
+        <v>152.6935648</v>
       </c>
       <c r="O22">
-        <v>39.66473836800001</v>
+        <v>39.3949397184</v>
       </c>
       <c r="P22">
-        <v>114.074557632</v>
+        <v>113.2986250816</v>
       </c>
       <c r="Q22">
-        <v>171.474557632</v>
+        <v>170.6986250816</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09632212401539256</v>
+        <v>0.09682246591059543</v>
       </c>
       <c r="T22">
-        <v>1.166792702434008</v>
+        <v>1.178347942507977</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0373226</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>12.9541897550865</v>
+        <v>11.98006517155453</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08456122406937039</v>
+        <v>0.08437762892642672</v>
       </c>
       <c r="C23">
-        <v>1100.948836753101</v>
+        <v>1093.389447759482</v>
       </c>
       <c r="D23">
-        <v>1097.812836753101</v>
+        <v>1103.037447759482</v>
       </c>
       <c r="E23">
-        <v>-546.4360000000001</v>
+        <v>-533.652</v>
       </c>
       <c r="F23">
-        <v>268.464</v>
+        <v>281.248</v>
       </c>
       <c r="G23">
         <v>271.6</v>
@@ -3167,28 +3167,28 @@
         <v>166.6</v>
       </c>
       <c r="M23">
-        <v>13.9064352</v>
+        <v>14.5686464</v>
       </c>
       <c r="N23">
-        <v>152.6935648</v>
+        <v>152.0313536</v>
       </c>
       <c r="O23">
-        <v>39.3949397184</v>
+        <v>39.2240892288</v>
       </c>
       <c r="P23">
-        <v>113.2986250816</v>
+        <v>112.8072643712</v>
       </c>
       <c r="Q23">
-        <v>170.6986250816</v>
+        <v>170.2072643712</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09682246591059541</v>
+        <v>0.09733563708516246</v>
       </c>
       <c r="T23">
-        <v>1.178347942507977</v>
+        <v>1.190199470788971</v>
       </c>
       <c r="U23">
         <v>0.05180000000000001</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.98006517155453</v>
+        <v>11.43551675466569</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08437762892642672</v>
+        <v>0.08419403378348306</v>
       </c>
       <c r="C24">
-        <v>1093.389447759482</v>
+        <v>1085.880025550283</v>
       </c>
       <c r="D24">
-        <v>1103.037447759482</v>
+        <v>1108.312025550283</v>
       </c>
       <c r="E24">
-        <v>-533.652</v>
+        <v>-520.8680000000001</v>
       </c>
       <c r="F24">
-        <v>281.248</v>
+        <v>294.032</v>
       </c>
       <c r="G24">
         <v>271.6</v>
@@ -3249,28 +3249,28 @@
         <v>166.6</v>
       </c>
       <c r="M24">
-        <v>14.5686464</v>
+        <v>15.2308576</v>
       </c>
       <c r="N24">
-        <v>152.0313536</v>
+        <v>151.3691424</v>
       </c>
       <c r="O24">
-        <v>39.2240892288</v>
+        <v>39.0532387392</v>
       </c>
       <c r="P24">
-        <v>112.8072643712</v>
+        <v>112.3159036608</v>
       </c>
       <c r="Q24">
-        <v>170.2072643712</v>
+        <v>169.7159036608</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09733563708516246</v>
+        <v>0.09786213738114682</v>
       </c>
       <c r="T24">
-        <v>1.190199470788971</v>
+        <v>1.202358830973368</v>
       </c>
       <c r="U24">
         <v>0.05180000000000001</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.43551675466569</v>
+        <v>10.93832037402805</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08419403378348306</v>
+        <v>0.08401043864053939</v>
       </c>
       <c r="C25">
-        <v>1085.880025550283</v>
+        <v>1078.421290373105</v>
       </c>
       <c r="D25">
-        <v>1108.312025550283</v>
+        <v>1113.637290373105</v>
       </c>
       <c r="E25">
-        <v>-520.8680000000001</v>
+        <v>-508.0840000000001</v>
       </c>
       <c r="F25">
-        <v>294.032</v>
+        <v>306.816</v>
       </c>
       <c r="G25">
         <v>271.6</v>
@@ -3331,28 +3331,28 @@
         <v>166.6</v>
       </c>
       <c r="M25">
-        <v>15.2308576</v>
+        <v>15.8930688</v>
       </c>
       <c r="N25">
-        <v>151.3691424</v>
+        <v>150.7069312</v>
       </c>
       <c r="O25">
-        <v>39.0532387392</v>
+        <v>38.88238824960001</v>
       </c>
       <c r="P25">
-        <v>112.3159036608</v>
+        <v>111.8245429504</v>
       </c>
       <c r="Q25">
-        <v>169.7159036608</v>
+        <v>169.2245429504</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09786213738114682</v>
+        <v>0.09840249294807815</v>
       </c>
       <c r="T25">
-        <v>1.202358830973368</v>
+        <v>1.214838174320512</v>
       </c>
       <c r="U25">
         <v>0.05180000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.93832037402805</v>
+        <v>10.48255702511022</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08401043864053939</v>
+        <v>0.08382684349759573</v>
       </c>
       <c r="C26">
-        <v>1078.421290373105</v>
+        <v>1071.01397638509</v>
       </c>
       <c r="D26">
-        <v>1113.637290373105</v>
+        <v>1119.01397638509</v>
       </c>
       <c r="E26">
-        <v>-508.0840000000001</v>
+        <v>-495.3000000000001</v>
       </c>
       <c r="F26">
-        <v>306.816</v>
+        <v>319.6</v>
       </c>
       <c r="G26">
         <v>271.6</v>
@@ -3413,28 +3413,28 @@
         <v>166.6</v>
       </c>
       <c r="M26">
-        <v>15.8930688</v>
+        <v>16.55528</v>
       </c>
       <c r="N26">
-        <v>150.7069312</v>
+        <v>150.04472</v>
       </c>
       <c r="O26">
-        <v>38.88238824960001</v>
+        <v>38.71153776000001</v>
       </c>
       <c r="P26">
-        <v>111.8245429504</v>
+        <v>111.33318224</v>
       </c>
       <c r="Q26">
-        <v>169.2245429504</v>
+        <v>168.73318224</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09840249294807815</v>
+        <v>0.09895725799679431</v>
       </c>
       <c r="T26">
-        <v>1.214838174320512</v>
+        <v>1.227650300156913</v>
       </c>
       <c r="U26">
         <v>0.05180000000000001</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.48255702511022</v>
+        <v>10.06325474410581</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08382684349759573</v>
+        <v>0.08397121235465206</v>
       </c>
       <c r="C27">
-        <v>1071.01397638509</v>
+        <v>1053.997709217367</v>
       </c>
       <c r="D27">
-        <v>1119.01397638509</v>
+        <v>1114.781709217367</v>
       </c>
       <c r="E27">
-        <v>-495.3000000000001</v>
+        <v>-482.5160000000001</v>
       </c>
       <c r="F27">
-        <v>319.6</v>
+        <v>332.384</v>
       </c>
       <c r="G27">
         <v>271.6</v>
@@ -3495,45 +3495,45 @@
         <v>166.6</v>
       </c>
       <c r="M27">
-        <v>16.55528</v>
+        <v>17.782544</v>
       </c>
       <c r="N27">
-        <v>150.04472</v>
+        <v>148.817456</v>
       </c>
       <c r="O27">
-        <v>38.71153776000001</v>
+        <v>38.394903648</v>
       </c>
       <c r="P27">
-        <v>111.33318224</v>
+        <v>110.422552352</v>
       </c>
       <c r="Q27">
-        <v>168.73318224</v>
+        <v>167.822552352</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09895725799679431</v>
+        <v>0.09952701669547576</v>
       </c>
       <c r="T27">
-        <v>1.227650300156913</v>
+        <v>1.240808699664567</v>
       </c>
       <c r="U27">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.03843560000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>10.06325474410581</v>
+        <v>9.368738241277514</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08397121235465206</v>
+        <v>0.0838002312117084</v>
       </c>
       <c r="C28">
-        <v>1053.997709217367</v>
+        <v>1046.229643191894</v>
       </c>
       <c r="D28">
-        <v>1114.781709217367</v>
+        <v>1119.797643191893</v>
       </c>
       <c r="E28">
-        <v>-482.5160000000001</v>
+        <v>-469.732</v>
       </c>
       <c r="F28">
-        <v>332.384</v>
+        <v>345.1680000000001</v>
       </c>
       <c r="G28">
         <v>271.6</v>
@@ -3577,28 +3577,28 @@
         <v>166.6</v>
       </c>
       <c r="M28">
-        <v>17.782544</v>
+        <v>18.46648800000001</v>
       </c>
       <c r="N28">
-        <v>148.817456</v>
+        <v>148.133512</v>
       </c>
       <c r="O28">
-        <v>38.394903648</v>
+        <v>38.21844609600001</v>
       </c>
       <c r="P28">
-        <v>110.422552352</v>
+        <v>109.915065904</v>
       </c>
       <c r="Q28">
-        <v>167.822552352</v>
+        <v>167.315065904</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09952701669547576</v>
+        <v>0.1001123852215184</v>
       </c>
       <c r="T28">
-        <v>1.240808699664567</v>
+        <v>1.254327603268323</v>
       </c>
       <c r="U28">
         <v>0.05350000000000001</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.368738241277514</v>
+        <v>9.021747936045012</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0838002312117084</v>
+        <v>0.08362925006876473</v>
       </c>
       <c r="C29">
-        <v>1046.229643191894</v>
+        <v>1038.506919335368</v>
       </c>
       <c r="D29">
-        <v>1119.797643191893</v>
+        <v>1124.858919335368</v>
       </c>
       <c r="E29">
-        <v>-469.732</v>
+        <v>-456.948</v>
       </c>
       <c r="F29">
-        <v>345.1680000000001</v>
+        <v>357.9520000000001</v>
       </c>
       <c r="G29">
         <v>271.6</v>
@@ -3659,28 +3659,28 @@
         <v>166.6</v>
       </c>
       <c r="M29">
-        <v>18.46648800000001</v>
+        <v>19.15043200000001</v>
       </c>
       <c r="N29">
-        <v>148.133512</v>
+        <v>147.449568</v>
       </c>
       <c r="O29">
-        <v>38.21844609600001</v>
+        <v>38.04198854400001</v>
       </c>
       <c r="P29">
-        <v>109.915065904</v>
+        <v>109.407579456</v>
       </c>
       <c r="Q29">
-        <v>167.315065904</v>
+        <v>166.807579456</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1001123852215184</v>
+        <v>0.1007140139843955</v>
       </c>
       <c r="T29">
-        <v>1.254327603268323</v>
+        <v>1.268222031972182</v>
       </c>
       <c r="U29">
         <v>0.05350000000000001</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.021747936045012</v>
+        <v>8.699542652614834</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08362925006876473</v>
+        <v>0.08345826892582109</v>
       </c>
       <c r="C30">
-        <v>1038.506919335368</v>
+        <v>1030.830155253651</v>
       </c>
       <c r="D30">
-        <v>1124.858919335368</v>
+        <v>1129.966155253651</v>
       </c>
       <c r="E30">
-        <v>-456.948</v>
+        <v>-444.164</v>
       </c>
       <c r="F30">
-        <v>357.9520000000001</v>
+        <v>370.736</v>
       </c>
       <c r="G30">
         <v>271.6</v>
@@ -3741,28 +3741,28 @@
         <v>166.6</v>
       </c>
       <c r="M30">
-        <v>19.15043200000001</v>
+        <v>19.83437600000001</v>
       </c>
       <c r="N30">
-        <v>147.449568</v>
+        <v>146.765624</v>
       </c>
       <c r="O30">
-        <v>38.04198854400001</v>
+        <v>37.865530992</v>
       </c>
       <c r="P30">
-        <v>109.407579456</v>
+        <v>108.900093008</v>
       </c>
       <c r="Q30">
-        <v>166.807579456</v>
+        <v>166.300093008</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1007140139843955</v>
+        <v>0.1013325900363677</v>
       </c>
       <c r="T30">
-        <v>1.268222031972182</v>
+        <v>1.282507853033896</v>
       </c>
       <c r="U30">
         <v>0.05350000000000001</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.699542652614834</v>
+        <v>8.399558423214319</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08345826892582107</v>
+        <v>0.08328728778287742</v>
       </c>
       <c r="C31">
-        <v>1030.830155253652</v>
+        <v>1023.199979820313</v>
       </c>
       <c r="D31">
-        <v>1129.966155253652</v>
+        <v>1135.119979820313</v>
       </c>
       <c r="E31">
-        <v>-444.1640000000001</v>
+        <v>-431.3800000000001</v>
       </c>
       <c r="F31">
-        <v>370.736</v>
+        <v>383.52</v>
       </c>
       <c r="G31">
         <v>271.6</v>
@@ -3823,28 +3823,28 @@
         <v>166.6</v>
       </c>
       <c r="M31">
-        <v>19.834376</v>
+        <v>20.51832</v>
       </c>
       <c r="N31">
-        <v>146.765624</v>
+        <v>146.08168</v>
       </c>
       <c r="O31">
-        <v>37.86553099200001</v>
+        <v>37.68907344</v>
       </c>
       <c r="P31">
-        <v>108.900093008</v>
+        <v>108.39260656</v>
       </c>
       <c r="Q31">
-        <v>166.300093008</v>
+        <v>165.79260656</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1013325900363677</v>
+        <v>0.1019688396898249</v>
       </c>
       <c r="T31">
-        <v>1.282507853033896</v>
+        <v>1.29720184041166</v>
       </c>
       <c r="U31">
         <v>0.05350000000000001</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.399558423214323</v>
+        <v>8.119573142440512</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08328728778287742</v>
+        <v>0.08311630663993375</v>
       </c>
       <c r="C32">
-        <v>1023.199979820313</v>
+        <v>1015.617033434772</v>
       </c>
       <c r="D32">
-        <v>1135.119979820313</v>
+        <v>1140.321033434772</v>
       </c>
       <c r="E32">
-        <v>-431.3800000000001</v>
+        <v>-418.5960000000001</v>
       </c>
       <c r="F32">
-        <v>383.52</v>
+        <v>396.304</v>
       </c>
       <c r="G32">
         <v>271.6</v>
@@ -3905,28 +3905,28 @@
         <v>166.6</v>
       </c>
       <c r="M32">
-        <v>20.51832</v>
+        <v>21.202264</v>
       </c>
       <c r="N32">
-        <v>146.08168</v>
+        <v>145.397736</v>
       </c>
       <c r="O32">
-        <v>37.68907344</v>
+        <v>37.51261588800001</v>
       </c>
       <c r="P32">
-        <v>108.39260656</v>
+        <v>107.885120112</v>
       </c>
       <c r="Q32">
-        <v>165.79260656</v>
+        <v>165.285120112</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1019688396898249</v>
+        <v>0.1026235313622228</v>
       </c>
       <c r="T32">
-        <v>1.29720184041166</v>
+        <v>1.31232174046704</v>
       </c>
       <c r="U32">
         <v>0.05350000000000001</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.119573142440512</v>
+        <v>7.857651428168237</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08311630663993375</v>
+        <v>0.0831352774969901</v>
       </c>
       <c r="C33">
-        <v>1015.617033434772</v>
+        <v>1002.253611805312</v>
       </c>
       <c r="D33">
-        <v>1140.321033434772</v>
+        <v>1139.741611805312</v>
       </c>
       <c r="E33">
-        <v>-418.5960000000001</v>
+        <v>-405.8120000000001</v>
       </c>
       <c r="F33">
-        <v>396.304</v>
+        <v>409.088</v>
       </c>
       <c r="G33">
         <v>271.6</v>
@@ -3987,45 +3987,45 @@
         <v>166.6</v>
       </c>
       <c r="M33">
-        <v>21.202264</v>
+        <v>22.2134784</v>
       </c>
       <c r="N33">
-        <v>145.397736</v>
+        <v>144.3865216</v>
       </c>
       <c r="O33">
-        <v>37.51261588800001</v>
+        <v>37.25172257280001</v>
       </c>
       <c r="P33">
-        <v>107.885120112</v>
+        <v>107.1347990272</v>
       </c>
       <c r="Q33">
-        <v>165.285120112</v>
+        <v>164.5347990272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1026235313622228</v>
+        <v>0.1032974786720443</v>
       </c>
       <c r="T33">
-        <v>1.31232174046704</v>
+        <v>1.327886343465225</v>
       </c>
       <c r="U33">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.857651428168237</v>
+        <v>7.499951020728028</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0831352774969901</v>
+        <v>0.08297023235404642</v>
       </c>
       <c r="C34">
-        <v>1002.253611805312</v>
+        <v>994.5303500715552</v>
       </c>
       <c r="D34">
-        <v>1139.741611805312</v>
+        <v>1144.802350071555</v>
       </c>
       <c r="E34">
-        <v>-405.8120000000001</v>
+        <v>-393.028</v>
       </c>
       <c r="F34">
-        <v>409.088</v>
+        <v>421.8720000000001</v>
       </c>
       <c r="G34">
         <v>271.6</v>
@@ -4069,28 +4069,28 @@
         <v>166.6</v>
       </c>
       <c r="M34">
-        <v>22.2134784</v>
+        <v>22.90764960000001</v>
       </c>
       <c r="N34">
-        <v>144.3865216</v>
+        <v>143.6923504</v>
       </c>
       <c r="O34">
-        <v>37.25172257280001</v>
+        <v>37.0726264032</v>
       </c>
       <c r="P34">
-        <v>107.1347990272</v>
+        <v>106.6197239968</v>
       </c>
       <c r="Q34">
-        <v>164.5347990272</v>
+        <v>164.0197239968</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1032974786720443</v>
+        <v>0.1039915438120096</v>
       </c>
       <c r="T34">
-        <v>1.327886343465225</v>
+        <v>1.343915561478282</v>
       </c>
       <c r="U34">
         <v>0.05430000000000001</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.499951020728028</v>
+        <v>7.272679777675662</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08297023235404642</v>
+        <v>0.08280518721110275</v>
       </c>
       <c r="C35">
-        <v>994.5303500715552</v>
+        <v>986.8522306723461</v>
       </c>
       <c r="D35">
-        <v>1144.802350071555</v>
+        <v>1149.908230672346</v>
       </c>
       <c r="E35">
-        <v>-393.028</v>
+        <v>-380.244</v>
       </c>
       <c r="F35">
-        <v>421.8720000000001</v>
+        <v>434.6560000000001</v>
       </c>
       <c r="G35">
         <v>271.6</v>
@@ -4151,28 +4151,28 @@
         <v>166.6</v>
       </c>
       <c r="M35">
-        <v>22.90764960000001</v>
+        <v>23.60182080000001</v>
       </c>
       <c r="N35">
-        <v>143.6923504</v>
+        <v>142.9981792</v>
       </c>
       <c r="O35">
-        <v>37.0726264032</v>
+        <v>36.8935302336</v>
       </c>
       <c r="P35">
-        <v>106.6197239968</v>
+        <v>106.1046489664</v>
       </c>
       <c r="Q35">
-        <v>164.0197239968</v>
+        <v>163.5046489664</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1039915438120096</v>
+        <v>0.1047066412289436</v>
       </c>
       <c r="T35">
-        <v>1.343915561478282</v>
+        <v>1.360430513370521</v>
       </c>
       <c r="U35">
         <v>0.05430000000000001</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.272679777675662</v>
+        <v>7.058777431273437</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08280518721110275</v>
+        <v>0.08264014206815909</v>
       </c>
       <c r="C36">
-        <v>986.8522306723461</v>
+        <v>979.2198603254642</v>
       </c>
       <c r="D36">
-        <v>1149.908230672346</v>
+        <v>1155.059860325464</v>
       </c>
       <c r="E36">
-        <v>-380.244</v>
+        <v>-367.46</v>
       </c>
       <c r="F36">
-        <v>434.6560000000001</v>
+        <v>447.4400000000001</v>
       </c>
       <c r="G36">
         <v>271.6</v>
@@ -4233,28 +4233,28 @@
         <v>166.6</v>
       </c>
       <c r="M36">
-        <v>23.60182080000001</v>
+        <v>24.29599200000001</v>
       </c>
       <c r="N36">
-        <v>142.9981792</v>
+        <v>142.304008</v>
       </c>
       <c r="O36">
-        <v>36.8935302336</v>
+        <v>36.714434064</v>
       </c>
       <c r="P36">
-        <v>106.1046489664</v>
+        <v>105.589573936</v>
       </c>
       <c r="Q36">
-        <v>163.5046489664</v>
+        <v>162.989573936</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1047066412289436</v>
+        <v>0.1054437416433217</v>
       </c>
       <c r="T36">
-        <v>1.360430513370521</v>
+        <v>1.377453617628676</v>
       </c>
       <c r="U36">
         <v>0.05430000000000001</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.058777431273437</v>
+        <v>6.857098076094196</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08264014206815909</v>
+        <v>0.08247509692521542</v>
       </c>
       <c r="C37">
-        <v>979.2198603254642</v>
+        <v>971.6338566700856</v>
       </c>
       <c r="D37">
-        <v>1155.059860325464</v>
+        <v>1160.257856670086</v>
       </c>
       <c r="E37">
-        <v>-367.46</v>
+        <v>-354.676</v>
       </c>
       <c r="F37">
-        <v>447.4400000000001</v>
+        <v>460.2240000000001</v>
       </c>
       <c r="G37">
         <v>271.6</v>
@@ -4315,28 +4315,28 @@
         <v>166.6</v>
       </c>
       <c r="M37">
-        <v>24.29599200000001</v>
+        <v>24.99016320000001</v>
       </c>
       <c r="N37">
-        <v>142.304008</v>
+        <v>141.6098368</v>
       </c>
       <c r="O37">
-        <v>36.714434064</v>
+        <v>36.5353378944</v>
       </c>
       <c r="P37">
-        <v>105.589573936</v>
+        <v>105.0744989056</v>
       </c>
       <c r="Q37">
-        <v>162.989573936</v>
+        <v>162.4744989056</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1054437416433217</v>
+        <v>0.1062038764456491</v>
       </c>
       <c r="T37">
-        <v>1.377453617628676</v>
+        <v>1.395008693894899</v>
       </c>
       <c r="U37">
         <v>0.05430000000000001</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.857098076094196</v>
+        <v>6.666623129536023</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08247509692521543</v>
+        <v>0.08231005178227177</v>
       </c>
       <c r="C38">
-        <v>971.6338566700854</v>
+        <v>964.0948485136357</v>
       </c>
       <c r="D38">
-        <v>1160.257856670085</v>
+        <v>1165.502848513636</v>
       </c>
       <c r="E38">
-        <v>-354.6760000000001</v>
+        <v>-341.8920000000001</v>
       </c>
       <c r="F38">
-        <v>460.224</v>
+        <v>473.008</v>
       </c>
       <c r="G38">
         <v>271.6</v>
@@ -4397,28 +4397,28 @@
         <v>166.6</v>
       </c>
       <c r="M38">
-        <v>24.9901632</v>
+        <v>25.6843344</v>
       </c>
       <c r="N38">
-        <v>141.6098368</v>
+        <v>140.9156656</v>
       </c>
       <c r="O38">
-        <v>36.5353378944</v>
+        <v>36.35624172480001</v>
       </c>
       <c r="P38">
-        <v>105.0744989056</v>
+        <v>104.5594238752</v>
       </c>
       <c r="Q38">
-        <v>162.4744989056</v>
+        <v>161.9594238752</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1062038764456491</v>
+        <v>0.1069881425115425</v>
       </c>
       <c r="T38">
-        <v>1.395008693894899</v>
+        <v>1.413121074169573</v>
       </c>
       <c r="U38">
         <v>0.05430000000000001</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.666623129536025</v>
+        <v>6.48644412603505</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08231005178227177</v>
+        <v>0.08214500663932811</v>
       </c>
       <c r="C39">
-        <v>964.0948485136357</v>
+        <v>956.6034760853703</v>
       </c>
       <c r="D39">
-        <v>1165.502848513636</v>
+        <v>1170.79547608537</v>
       </c>
       <c r="E39">
-        <v>-341.8920000000001</v>
+        <v>-329.1080000000001</v>
       </c>
       <c r="F39">
-        <v>473.008</v>
+        <v>485.792</v>
       </c>
       <c r="G39">
         <v>271.6</v>
@@ -4479,28 +4479,28 @@
         <v>166.6</v>
       </c>
       <c r="M39">
-        <v>25.6843344</v>
+        <v>26.3785056</v>
       </c>
       <c r="N39">
-        <v>140.9156656</v>
+        <v>140.2214944</v>
       </c>
       <c r="O39">
-        <v>36.35624172480001</v>
+        <v>36.17714555520001</v>
       </c>
       <c r="P39">
-        <v>104.5594238752</v>
+        <v>104.0443488448</v>
       </c>
       <c r="Q39">
-        <v>161.9594238752</v>
+        <v>161.4443488448</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1069881425115425</v>
+        <v>0.1077977074827873</v>
       </c>
       <c r="T39">
-        <v>1.413121074169573</v>
+        <v>1.431817724775688</v>
       </c>
       <c r="U39">
         <v>0.05430000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.48644412603505</v>
+        <v>6.315748227981497</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08214500663932811</v>
+        <v>0.08197996149638445</v>
       </c>
       <c r="C40">
-        <v>956.6034760853703</v>
+        <v>949.1603912968917</v>
       </c>
       <c r="D40">
-        <v>1170.79547608537</v>
+        <v>1176.136391296892</v>
       </c>
       <c r="E40">
-        <v>-329.1080000000001</v>
+        <v>-316.324</v>
       </c>
       <c r="F40">
-        <v>485.792</v>
+        <v>498.5760000000001</v>
       </c>
       <c r="G40">
         <v>271.6</v>
@@ -4561,28 +4561,28 @@
         <v>166.6</v>
       </c>
       <c r="M40">
-        <v>26.3785056</v>
+        <v>27.07267680000001</v>
       </c>
       <c r="N40">
-        <v>140.2214944</v>
+        <v>139.5273232</v>
       </c>
       <c r="O40">
-        <v>36.17714555520001</v>
+        <v>35.99804938560001</v>
       </c>
       <c r="P40">
-        <v>104.0443488448</v>
+        <v>103.5292738144</v>
       </c>
       <c r="Q40">
-        <v>161.4443488448</v>
+        <v>160.9292738144</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1077977074827873</v>
+        <v>0.1086338155678434</v>
       </c>
       <c r="T40">
-        <v>1.431817724775688</v>
+        <v>1.451127380319708</v>
       </c>
       <c r="U40">
         <v>0.05430000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.315748227981497</v>
+        <v>6.15380596572556</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08197996149638445</v>
+        <v>0.08211171635344078</v>
       </c>
       <c r="C41">
-        <v>949.1603912968917</v>
+        <v>932.1088518447282</v>
       </c>
       <c r="D41">
-        <v>1176.136391296892</v>
+        <v>1171.868851844728</v>
       </c>
       <c r="E41">
-        <v>-316.324</v>
+        <v>-303.54</v>
       </c>
       <c r="F41">
-        <v>498.5760000000001</v>
+        <v>511.3600000000001</v>
       </c>
       <c r="G41">
         <v>271.6</v>
@@ -4643,45 +4643,45 @@
         <v>166.6</v>
       </c>
       <c r="M41">
-        <v>27.07267680000001</v>
+        <v>28.27820800000001</v>
       </c>
       <c r="N41">
-        <v>139.5273232</v>
+        <v>138.321792</v>
       </c>
       <c r="O41">
-        <v>35.99804938560001</v>
+        <v>35.68702233600001</v>
       </c>
       <c r="P41">
-        <v>103.5292738144</v>
+        <v>102.634769664</v>
       </c>
       <c r="Q41">
-        <v>160.9292738144</v>
+        <v>160.034769664</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1086338155678434</v>
+        <v>0.1094977939224013</v>
       </c>
       <c r="T41">
-        <v>1.451127380319708</v>
+        <v>1.471080691048529</v>
       </c>
       <c r="U41">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0402906</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>6.15380596572556</v>
+        <v>5.891462429302449</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08211171635344078</v>
+        <v>0.08195409121049711</v>
       </c>
       <c r="C42">
-        <v>932.1088518447282</v>
+        <v>924.4339830411897</v>
       </c>
       <c r="D42">
-        <v>1171.868851844728</v>
+        <v>1176.97798304119</v>
       </c>
       <c r="E42">
-        <v>-303.54</v>
+        <v>-290.756</v>
       </c>
       <c r="F42">
-        <v>511.3600000000001</v>
+        <v>524.1440000000001</v>
       </c>
       <c r="G42">
         <v>271.6</v>
@@ -4725,28 +4725,28 @@
         <v>166.6</v>
       </c>
       <c r="M42">
-        <v>28.27820800000001</v>
+        <v>28.98516320000001</v>
       </c>
       <c r="N42">
-        <v>138.321792</v>
+        <v>137.6148368</v>
       </c>
       <c r="O42">
-        <v>35.68702233600001</v>
+        <v>35.5046278944</v>
       </c>
       <c r="P42">
-        <v>102.634769664</v>
+        <v>102.1102089056</v>
       </c>
       <c r="Q42">
-        <v>160.034769664</v>
+        <v>159.5102089056</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1094977939224013</v>
+        <v>0.1103910596788087</v>
       </c>
       <c r="T42">
-        <v>1.471080691048529</v>
+        <v>1.491710385191886</v>
       </c>
       <c r="U42">
         <v>0.05530000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.891462429302449</v>
+        <v>5.747768223709707</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08195409121049711</v>
+        <v>0.08179646606755346</v>
       </c>
       <c r="C43">
-        <v>924.4339830411897</v>
+        <v>916.8038590486351</v>
       </c>
       <c r="D43">
-        <v>1176.97798304119</v>
+        <v>1182.131859048635</v>
       </c>
       <c r="E43">
-        <v>-290.756</v>
+        <v>-277.972</v>
       </c>
       <c r="F43">
-        <v>524.1440000000001</v>
+        <v>536.9280000000001</v>
       </c>
       <c r="G43">
         <v>271.6</v>
@@ -4807,28 +4807,28 @@
         <v>166.6</v>
       </c>
       <c r="M43">
-        <v>28.98516320000001</v>
+        <v>29.69211840000001</v>
       </c>
       <c r="N43">
-        <v>137.6148368</v>
+        <v>136.9078816</v>
       </c>
       <c r="O43">
-        <v>35.5046278944</v>
+        <v>35.3222334528</v>
       </c>
       <c r="P43">
-        <v>102.1102089056</v>
+        <v>101.5856481472</v>
       </c>
       <c r="Q43">
-        <v>159.5102089056</v>
+        <v>158.9856481472</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1103910596788087</v>
+        <v>0.1113151277026784</v>
       </c>
       <c r="T43">
-        <v>1.491710385191886</v>
+        <v>1.513051448098808</v>
       </c>
       <c r="U43">
         <v>0.05530000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.747768223709707</v>
+        <v>5.610916599335665</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08179646606755347</v>
+        <v>0.0816388409246098</v>
       </c>
       <c r="C44">
-        <v>916.8038590486348</v>
+        <v>909.2190702522785</v>
       </c>
       <c r="D44">
-        <v>1182.131859048635</v>
+        <v>1187.331070252278</v>
       </c>
       <c r="E44">
-        <v>-277.9720000000001</v>
+        <v>-265.1880000000001</v>
       </c>
       <c r="F44">
-        <v>536.928</v>
+        <v>549.712</v>
       </c>
       <c r="G44">
         <v>271.6</v>
@@ -4889,28 +4889,28 @@
         <v>166.6</v>
       </c>
       <c r="M44">
-        <v>29.69211840000001</v>
+        <v>30.3990736</v>
       </c>
       <c r="N44">
-        <v>136.9078816</v>
+        <v>136.2009264</v>
       </c>
       <c r="O44">
-        <v>35.32223345280001</v>
+        <v>35.1398390112</v>
       </c>
       <c r="P44">
-        <v>101.5856481472</v>
+        <v>101.0610873888</v>
       </c>
       <c r="Q44">
-        <v>158.9856481472</v>
+        <v>158.4610873888</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1113151277026784</v>
+        <v>0.1122716191659821</v>
       </c>
       <c r="T44">
-        <v>1.513051448098808</v>
+        <v>1.535141320230533</v>
       </c>
       <c r="U44">
         <v>0.05530000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.610916599335668</v>
+        <v>5.480430166792977</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0816388409246098</v>
+        <v>0.08148121578166614</v>
       </c>
       <c r="C45">
-        <v>909.2190702522785</v>
+        <v>901.6802174696581</v>
       </c>
       <c r="D45">
-        <v>1187.331070252278</v>
+        <v>1192.576217469658</v>
       </c>
       <c r="E45">
-        <v>-265.1880000000001</v>
+        <v>-252.404</v>
       </c>
       <c r="F45">
-        <v>549.712</v>
+        <v>562.4960000000001</v>
       </c>
       <c r="G45">
         <v>271.6</v>
@@ -4971,28 +4971,28 @@
         <v>166.6</v>
       </c>
       <c r="M45">
-        <v>30.3990736</v>
+        <v>31.10602880000001</v>
       </c>
       <c r="N45">
-        <v>136.2009264</v>
+        <v>135.4939712</v>
       </c>
       <c r="O45">
-        <v>35.1398390112</v>
+        <v>34.9574445696</v>
       </c>
       <c r="P45">
-        <v>101.0610873888</v>
+        <v>100.5365266304</v>
       </c>
       <c r="Q45">
-        <v>158.4610873888</v>
+        <v>157.9365266304</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1122716191659821</v>
+        <v>0.1132622710386895</v>
       </c>
       <c r="T45">
-        <v>1.535141320230533</v>
+        <v>1.558020116366963</v>
       </c>
       <c r="U45">
         <v>0.05530000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.480430166792977</v>
+        <v>5.355874935729499</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08148121578166614</v>
+        <v>0.08132359063872248</v>
       </c>
       <c r="C46">
-        <v>901.6802174696581</v>
+        <v>894.1879121820999</v>
       </c>
       <c r="D46">
-        <v>1192.576217469658</v>
+        <v>1197.8679121821</v>
       </c>
       <c r="E46">
-        <v>-252.404</v>
+        <v>-239.62</v>
       </c>
       <c r="F46">
-        <v>562.4960000000001</v>
+        <v>575.2800000000001</v>
       </c>
       <c r="G46">
         <v>271.6</v>
@@ -5053,28 +5053,28 @@
         <v>166.6</v>
       </c>
       <c r="M46">
-        <v>31.10602880000001</v>
+        <v>31.81298400000001</v>
       </c>
       <c r="N46">
-        <v>135.4939712</v>
+        <v>134.787016</v>
       </c>
       <c r="O46">
-        <v>34.9574445696</v>
+        <v>34.775050128</v>
       </c>
       <c r="P46">
-        <v>100.5365266304</v>
+        <v>100.011965872</v>
       </c>
       <c r="Q46">
-        <v>157.9365266304</v>
+        <v>157.411965872</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1132622710386895</v>
+        <v>0.114288946615859</v>
       </c>
       <c r="T46">
-        <v>1.558020116366963</v>
+        <v>1.581730868726537</v>
       </c>
       <c r="U46">
         <v>0.05530000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.355874935729499</v>
+        <v>5.236855492713289</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08132359063872248</v>
+        <v>0.08116596549577881</v>
       </c>
       <c r="C47">
-        <v>894.1879121820999</v>
+        <v>886.7427767723477</v>
       </c>
       <c r="D47">
-        <v>1197.8679121821</v>
+        <v>1203.206776772348</v>
       </c>
       <c r="E47">
-        <v>-239.62</v>
+        <v>-226.836</v>
       </c>
       <c r="F47">
-        <v>575.2800000000001</v>
+        <v>588.0640000000001</v>
       </c>
       <c r="G47">
         <v>271.6</v>
@@ -5135,28 +5135,28 @@
         <v>166.6</v>
       </c>
       <c r="M47">
-        <v>31.81298400000001</v>
+        <v>32.51993920000001</v>
       </c>
       <c r="N47">
-        <v>134.787016</v>
+        <v>134.0800608</v>
       </c>
       <c r="O47">
-        <v>34.775050128</v>
+        <v>34.59265568640001</v>
       </c>
       <c r="P47">
-        <v>100.011965872</v>
+        <v>99.4874051136</v>
       </c>
       <c r="Q47">
-        <v>157.411965872</v>
+        <v>156.8874051136</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.114288946615859</v>
+        <v>0.1153536472144052</v>
       </c>
       <c r="T47">
-        <v>1.581730868726537</v>
+        <v>1.606319797099427</v>
       </c>
       <c r="U47">
         <v>0.05530000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.236855492713289</v>
+        <v>5.123010808089087</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08116596549577881</v>
+        <v>0.08100834035283513</v>
       </c>
       <c r="C48">
-        <v>886.7427767723477</v>
+        <v>879.3454447685934</v>
       </c>
       <c r="D48">
-        <v>1203.206776772348</v>
+        <v>1208.593444768594</v>
       </c>
       <c r="E48">
-        <v>-226.836</v>
+        <v>-214.052</v>
       </c>
       <c r="F48">
-        <v>588.0640000000001</v>
+        <v>600.8480000000001</v>
       </c>
       <c r="G48">
         <v>271.6</v>
@@ -5217,28 +5217,28 @@
         <v>166.6</v>
       </c>
       <c r="M48">
-        <v>32.51993920000001</v>
+        <v>33.22689440000001</v>
       </c>
       <c r="N48">
-        <v>134.0800608</v>
+        <v>133.3731056</v>
       </c>
       <c r="O48">
-        <v>34.59265568640001</v>
+        <v>34.41026124480001</v>
       </c>
       <c r="P48">
-        <v>99.4874051136</v>
+        <v>98.96284435520002</v>
       </c>
       <c r="Q48">
-        <v>156.8874051136</v>
+        <v>156.3628443552</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1153536472144052</v>
+        <v>0.1164585251940286</v>
       </c>
       <c r="T48">
-        <v>1.606319797099427</v>
+        <v>1.631836609561861</v>
       </c>
       <c r="U48">
         <v>0.05530000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.123010808089087</v>
+        <v>5.014010578129746</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08100834035283513</v>
+        <v>0.08085071520989148</v>
       </c>
       <c r="C49">
-        <v>879.3454447685934</v>
+        <v>871.9965610950831</v>
       </c>
       <c r="D49">
-        <v>1208.593444768594</v>
+        <v>1214.028561095083</v>
       </c>
       <c r="E49">
-        <v>-214.052</v>
+        <v>-201.268</v>
       </c>
       <c r="F49">
-        <v>600.8480000000001</v>
+        <v>613.6320000000001</v>
       </c>
       <c r="G49">
         <v>271.6</v>
@@ -5299,28 +5299,28 @@
         <v>166.6</v>
       </c>
       <c r="M49">
-        <v>33.22689440000001</v>
+        <v>33.93384960000001</v>
       </c>
       <c r="N49">
-        <v>133.3731056</v>
+        <v>132.6661504</v>
       </c>
       <c r="O49">
-        <v>34.41026124480001</v>
+        <v>34.22786680320001</v>
       </c>
       <c r="P49">
-        <v>98.96284435520002</v>
+        <v>98.43828359680001</v>
       </c>
       <c r="Q49">
-        <v>156.3628443552</v>
+        <v>155.8382835968</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1164585251940286</v>
+        <v>0.1176058984805605</v>
       </c>
       <c r="T49">
-        <v>1.631836609561861</v>
+        <v>1.658334837888234</v>
       </c>
       <c r="U49">
         <v>0.05530000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.014010578129746</v>
+        <v>4.909552024418709</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08085071520989148</v>
+        <v>0.0806930900669478</v>
       </c>
       <c r="C50">
-        <v>871.9965610950831</v>
+        <v>864.6967823295209</v>
       </c>
       <c r="D50">
-        <v>1214.028561095083</v>
+        <v>1219.512782329521</v>
       </c>
       <c r="E50">
-        <v>-201.268</v>
+        <v>-188.484</v>
       </c>
       <c r="F50">
-        <v>613.6320000000001</v>
+        <v>626.4160000000001</v>
       </c>
       <c r="G50">
         <v>271.6</v>
@@ -5381,28 +5381,28 @@
         <v>166.6</v>
       </c>
       <c r="M50">
-        <v>33.93384960000001</v>
+        <v>34.64080480000001</v>
       </c>
       <c r="N50">
-        <v>132.6661504</v>
+        <v>131.9591952</v>
       </c>
       <c r="O50">
-        <v>34.22786680320001</v>
+        <v>34.04547236160001</v>
       </c>
       <c r="P50">
-        <v>98.43828359680001</v>
+        <v>97.91372283840001</v>
       </c>
       <c r="Q50">
-        <v>155.8382835968</v>
+        <v>155.3137228384</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1176058984805605</v>
+        <v>0.1187982667979369</v>
       </c>
       <c r="T50">
-        <v>1.658334837888234</v>
+        <v>1.685872212423485</v>
       </c>
       <c r="U50">
         <v>0.05530000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.909552024418709</v>
+        <v>4.809357085144858</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0806930900669478</v>
+        <v>0.08053546492400415</v>
       </c>
       <c r="C51">
-        <v>864.6967823295209</v>
+        <v>857.4467769674759</v>
       </c>
       <c r="D51">
-        <v>1219.512782329521</v>
+        <v>1225.046776967476</v>
       </c>
       <c r="E51">
-        <v>-188.484</v>
+        <v>-175.7</v>
       </c>
       <c r="F51">
-        <v>626.4160000000001</v>
+        <v>639.2</v>
       </c>
       <c r="G51">
         <v>271.6</v>
@@ -5463,28 +5463,28 @@
         <v>166.6</v>
       </c>
       <c r="M51">
-        <v>34.64080480000001</v>
+        <v>35.34776000000001</v>
       </c>
       <c r="N51">
-        <v>131.9591952</v>
+        <v>131.25224</v>
       </c>
       <c r="O51">
-        <v>34.04547236160001</v>
+        <v>33.86307792000001</v>
       </c>
       <c r="P51">
-        <v>97.91372283840001</v>
+        <v>97.38916208000002</v>
       </c>
       <c r="Q51">
-        <v>155.3137228384</v>
+        <v>154.78916208</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1187982667979369</v>
+        <v>0.1200383298480083</v>
       </c>
       <c r="T51">
-        <v>1.685872212423485</v>
+        <v>1.714511081940145</v>
       </c>
       <c r="U51">
         <v>0.05530000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.809357085144858</v>
+        <v>4.713169943441961</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08053546492400415</v>
+        <v>0.08037783978106049</v>
       </c>
       <c r="C52">
-        <v>857.4467769674759</v>
+        <v>850.2472256940254</v>
       </c>
       <c r="D52">
-        <v>1225.046776967476</v>
+        <v>1230.631225694025</v>
       </c>
       <c r="E52">
-        <v>-175.7</v>
+        <v>-162.9160000000001</v>
       </c>
       <c r="F52">
-        <v>639.2</v>
+        <v>651.984</v>
       </c>
       <c r="G52">
         <v>271.6</v>
@@ -5545,28 +5545,28 @@
         <v>166.6</v>
       </c>
       <c r="M52">
-        <v>35.34776000000001</v>
+        <v>36.05471520000001</v>
       </c>
       <c r="N52">
-        <v>131.25224</v>
+        <v>130.5452848</v>
       </c>
       <c r="O52">
-        <v>33.86307792000001</v>
+        <v>33.68068347840001</v>
       </c>
       <c r="P52">
-        <v>97.38916208000002</v>
+        <v>96.86460132160002</v>
       </c>
       <c r="Q52">
-        <v>154.78916208</v>
+        <v>154.2646013216</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1200383298480083</v>
+        <v>0.12132900771645</v>
       </c>
       <c r="T52">
-        <v>1.714511081940145</v>
+        <v>1.744318884906466</v>
       </c>
       <c r="U52">
         <v>0.05530000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.713169943441961</v>
+        <v>4.620754846511725</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08037783978106049</v>
+        <v>0.08022021463811682</v>
       </c>
       <c r="C53">
-        <v>850.2472256940254</v>
+        <v>843.0988216628589</v>
       </c>
       <c r="D53">
-        <v>1230.631225694025</v>
+        <v>1236.266821662859</v>
       </c>
       <c r="E53">
-        <v>-162.9160000000001</v>
+        <v>-150.1320000000001</v>
       </c>
       <c r="F53">
-        <v>651.984</v>
+        <v>664.768</v>
       </c>
       <c r="G53">
         <v>271.6</v>
@@ -5627,28 +5627,28 @@
         <v>166.6</v>
       </c>
       <c r="M53">
-        <v>36.05471520000001</v>
+        <v>36.76167040000001</v>
       </c>
       <c r="N53">
-        <v>130.5452848</v>
+        <v>129.8383296</v>
       </c>
       <c r="O53">
-        <v>33.68068347840001</v>
+        <v>33.4982890368</v>
       </c>
       <c r="P53">
-        <v>96.86460132160002</v>
+        <v>96.34004056320001</v>
       </c>
       <c r="Q53">
-        <v>154.2646013216</v>
+        <v>153.7400405632</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.12132900771645</v>
+        <v>0.1226734638294101</v>
       </c>
       <c r="T53">
-        <v>1.744318884906466</v>
+        <v>1.77536867966305</v>
       </c>
       <c r="U53">
         <v>0.05530000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.620754846511725</v>
+        <v>4.5318941763865</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08022021463811682</v>
+        <v>0.08104573949517316</v>
       </c>
       <c r="C54">
-        <v>843.0988216628589</v>
+        <v>801.3590100994074</v>
       </c>
       <c r="D54">
-        <v>1236.266821662859</v>
+        <v>1207.311010099408</v>
       </c>
       <c r="E54">
-        <v>-150.1320000000001</v>
+        <v>-137.348</v>
       </c>
       <c r="F54">
-        <v>664.768</v>
+        <v>677.5520000000001</v>
       </c>
       <c r="G54">
         <v>271.6</v>
@@ -5709,45 +5709,45 @@
         <v>166.6</v>
       </c>
       <c r="M54">
-        <v>36.76167040000001</v>
+        <v>39.16250560000001</v>
       </c>
       <c r="N54">
-        <v>129.8383296</v>
+        <v>127.4374944</v>
       </c>
       <c r="O54">
-        <v>33.4982890368</v>
+        <v>32.87887355520001</v>
       </c>
       <c r="P54">
-        <v>96.34004056320001</v>
+        <v>94.5586208448</v>
       </c>
       <c r="Q54">
-        <v>153.7400405632</v>
+        <v>151.9586208448</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1226734638294101</v>
+        <v>0.124075130840794</v>
       </c>
       <c r="T54">
-        <v>1.77536867966305</v>
+        <v>1.807739742281616</v>
       </c>
       <c r="U54">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.04103260000000001</v>
+        <v>0.0428876</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.5318941763865</v>
+        <v>4.254068973564348</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08104573949517316</v>
+        <v>0.0809066643522295</v>
       </c>
       <c r="C55">
-        <v>801.3590100994074</v>
+        <v>793.3577758336397</v>
       </c>
       <c r="D55">
-        <v>1207.311010099408</v>
+        <v>1212.09377583364</v>
       </c>
       <c r="E55">
-        <v>-137.348</v>
+        <v>-124.564</v>
       </c>
       <c r="F55">
-        <v>677.5520000000001</v>
+        <v>690.3360000000001</v>
       </c>
       <c r="G55">
         <v>271.6</v>
@@ -5791,28 +5791,28 @@
         <v>166.6</v>
       </c>
       <c r="M55">
-        <v>39.16250560000001</v>
+        <v>39.90142080000001</v>
       </c>
       <c r="N55">
-        <v>127.4374944</v>
+        <v>126.6985792</v>
       </c>
       <c r="O55">
-        <v>32.87887355520001</v>
+        <v>32.6882334336</v>
       </c>
       <c r="P55">
-        <v>94.5586208448</v>
+        <v>94.01034576640001</v>
       </c>
       <c r="Q55">
-        <v>151.9586208448</v>
+        <v>151.4103457664</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.124075130840794</v>
+        <v>0.1255377398961511</v>
       </c>
       <c r="T55">
-        <v>1.807739742281616</v>
+        <v>1.841518242405337</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.254068973564348</v>
+        <v>4.17528991849834</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0809066643522295</v>
+        <v>0.08076758920928584</v>
       </c>
       <c r="C56">
-        <v>793.3577758336397</v>
+        <v>785.3945861596319</v>
       </c>
       <c r="D56">
-        <v>1212.09377583364</v>
+        <v>1216.914586159632</v>
       </c>
       <c r="E56">
-        <v>-124.564</v>
+        <v>-111.78</v>
       </c>
       <c r="F56">
-        <v>690.3360000000001</v>
+        <v>703.1200000000001</v>
       </c>
       <c r="G56">
         <v>271.6</v>
@@ -5873,28 +5873,28 @@
         <v>166.6</v>
       </c>
       <c r="M56">
-        <v>39.90142080000001</v>
+        <v>40.64033600000001</v>
       </c>
       <c r="N56">
-        <v>126.6985792</v>
+        <v>125.959664</v>
       </c>
       <c r="O56">
-        <v>32.6882334336</v>
+        <v>32.497593312</v>
       </c>
       <c r="P56">
-        <v>94.01034576640001</v>
+        <v>93.46207068800001</v>
       </c>
       <c r="Q56">
-        <v>151.4103457664</v>
+        <v>150.862070688</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1255377398961511</v>
+        <v>0.127065353798413</v>
       </c>
       <c r="T56">
-        <v>1.841518242405337</v>
+        <v>1.876798009201223</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.17528991849834</v>
+        <v>4.099375556343825</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08076758920928584</v>
+        <v>0.08062851406634218</v>
       </c>
       <c r="C57">
-        <v>785.3945861596319</v>
+        <v>777.4698968295619</v>
       </c>
       <c r="D57">
-        <v>1216.914586159632</v>
+        <v>1221.773896829562</v>
       </c>
       <c r="E57">
-        <v>-111.78</v>
+        <v>-98.99599999999998</v>
       </c>
       <c r="F57">
-        <v>703.1200000000001</v>
+        <v>715.9040000000001</v>
       </c>
       <c r="G57">
         <v>271.6</v>
@@ -5955,28 +5955,28 @@
         <v>166.6</v>
       </c>
       <c r="M57">
-        <v>40.64033600000001</v>
+        <v>41.37925120000001</v>
       </c>
       <c r="N57">
-        <v>125.959664</v>
+        <v>125.2207488</v>
       </c>
       <c r="O57">
-        <v>32.497593312</v>
+        <v>32.30695319040001</v>
       </c>
       <c r="P57">
-        <v>93.46207068800001</v>
+        <v>92.91379560960002</v>
       </c>
       <c r="Q57">
-        <v>150.862070688</v>
+        <v>150.3137956096</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.127065353798413</v>
+        <v>0.1286624046962322</v>
       </c>
       <c r="T57">
-        <v>1.876798009201223</v>
+        <v>1.913681401760559</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.099375556343825</v>
+        <v>4.026172421409115</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08062851406634218</v>
+        <v>0.08196972892339852</v>
       </c>
       <c r="C58">
-        <v>777.4698968295619</v>
+        <v>719.3811253765648</v>
       </c>
       <c r="D58">
-        <v>1221.773896829562</v>
+        <v>1176.469125376565</v>
       </c>
       <c r="E58">
-        <v>-98.99599999999998</v>
+        <v>-86.21199999999999</v>
       </c>
       <c r="F58">
-        <v>715.9040000000001</v>
+        <v>728.6880000000001</v>
       </c>
       <c r="G58">
         <v>271.6</v>
@@ -6037,45 +6037,45 @@
         <v>166.6</v>
       </c>
       <c r="M58">
-        <v>41.37925120000001</v>
+        <v>44.66857440000001</v>
       </c>
       <c r="N58">
-        <v>125.2207488</v>
+        <v>121.9314256</v>
       </c>
       <c r="O58">
-        <v>32.30695319040001</v>
+        <v>31.4583078048</v>
       </c>
       <c r="P58">
-        <v>92.91379560960002</v>
+        <v>90.47311779520001</v>
       </c>
       <c r="Q58">
-        <v>150.3137956096</v>
+        <v>147.8731177952</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1286624046962322</v>
+        <v>0.1303337370311593</v>
       </c>
       <c r="T58">
-        <v>1.913681401760559</v>
+        <v>1.952280300950562</v>
       </c>
       <c r="U58">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0428876</v>
+        <v>0.04548460000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.026172421409115</v>
+        <v>3.729691449476838</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08196972892339852</v>
+        <v>0.08185662378045486</v>
       </c>
       <c r="C59">
-        <v>719.3811253765648</v>
+        <v>710.2875626566812</v>
       </c>
       <c r="D59">
-        <v>1176.469125376565</v>
+        <v>1180.159562656681</v>
       </c>
       <c r="E59">
-        <v>-86.21199999999999</v>
+        <v>-73.428</v>
       </c>
       <c r="F59">
-        <v>728.6880000000001</v>
+        <v>741.4720000000001</v>
       </c>
       <c r="G59">
         <v>271.6</v>
@@ -6119,28 +6119,28 @@
         <v>166.6</v>
       </c>
       <c r="M59">
-        <v>44.66857440000001</v>
+        <v>45.45223360000001</v>
       </c>
       <c r="N59">
-        <v>121.9314256</v>
+        <v>121.1477664</v>
       </c>
       <c r="O59">
-        <v>31.4583078048</v>
+        <v>31.2561237312</v>
       </c>
       <c r="P59">
-        <v>90.47311779520001</v>
+        <v>89.8916426688</v>
       </c>
       <c r="Q59">
-        <v>147.8731177952</v>
+        <v>147.2916426688</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1303337370311593</v>
+        <v>0.1320846566201306</v>
       </c>
       <c r="T59">
-        <v>1.952280300950562</v>
+        <v>1.992717242959136</v>
       </c>
       <c r="U59">
         <v>0.06130000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.729691449476838</v>
+        <v>3.665386424485858</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08185662378045486</v>
+        <v>0.08174351863751118</v>
       </c>
       <c r="C60">
-        <v>710.2875626566813</v>
+        <v>701.21722567829</v>
       </c>
       <c r="D60">
-        <v>1180.159562656681</v>
+        <v>1183.87322567829</v>
       </c>
       <c r="E60">
-        <v>-73.42800000000011</v>
+        <v>-60.64400000000012</v>
       </c>
       <c r="F60">
-        <v>741.472</v>
+        <v>754.256</v>
       </c>
       <c r="G60">
         <v>271.6</v>
@@ -6201,28 +6201,28 @@
         <v>166.6</v>
       </c>
       <c r="M60">
-        <v>45.45223360000001</v>
+        <v>46.2358928</v>
       </c>
       <c r="N60">
-        <v>121.1477664</v>
+        <v>120.3641072</v>
       </c>
       <c r="O60">
-        <v>31.25612373120001</v>
+        <v>31.05393965760001</v>
       </c>
       <c r="P60">
-        <v>89.89164266880002</v>
+        <v>89.31016754240001</v>
       </c>
       <c r="Q60">
-        <v>147.2916426688</v>
+        <v>146.7101675424</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1320846566201306</v>
+        <v>0.133920986920759</v>
       </c>
       <c r="T60">
-        <v>1.992717242959136</v>
+        <v>2.035126718724225</v>
       </c>
       <c r="U60">
         <v>0.06130000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.665386424485859</v>
+        <v>3.603261230850505</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08174351863751118</v>
+        <v>0.08163041349456751</v>
       </c>
       <c r="C61">
-        <v>701.21722567829</v>
+        <v>692.170334390078</v>
       </c>
       <c r="D61">
-        <v>1183.87322567829</v>
+        <v>1187.610334390078</v>
       </c>
       <c r="E61">
-        <v>-60.64400000000012</v>
+        <v>-47.86000000000001</v>
       </c>
       <c r="F61">
-        <v>754.256</v>
+        <v>767.0400000000001</v>
       </c>
       <c r="G61">
         <v>271.6</v>
@@ -6283,28 +6283,28 @@
         <v>166.6</v>
       </c>
       <c r="M61">
-        <v>46.2358928</v>
+        <v>47.01955200000001</v>
       </c>
       <c r="N61">
-        <v>120.3641072</v>
+        <v>119.580448</v>
       </c>
       <c r="O61">
-        <v>31.05393965760001</v>
+        <v>30.85175558400001</v>
       </c>
       <c r="P61">
-        <v>89.31016754240001</v>
+        <v>88.72869241600002</v>
       </c>
       <c r="Q61">
-        <v>146.7101675424</v>
+        <v>146.128692416</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.133920986920759</v>
+        <v>0.1358491337364188</v>
       </c>
       <c r="T61">
-        <v>2.035126718724225</v>
+        <v>2.07965666827757</v>
       </c>
       <c r="U61">
         <v>0.06130000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.603261230850505</v>
+        <v>3.543206877002997</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08163041349456751</v>
+        <v>0.08278464435162386</v>
       </c>
       <c r="C62">
-        <v>692.170334390078</v>
+        <v>642.3229390771571</v>
       </c>
       <c r="D62">
-        <v>1187.610334390078</v>
+        <v>1150.546939077157</v>
       </c>
       <c r="E62">
-        <v>-47.86000000000001</v>
+        <v>-35.07600000000002</v>
       </c>
       <c r="F62">
-        <v>767.0400000000001</v>
+        <v>779.8240000000001</v>
       </c>
       <c r="G62">
         <v>271.6</v>
@@ -6365,45 +6365,45 @@
         <v>166.6</v>
       </c>
       <c r="M62">
-        <v>47.01955200000001</v>
+        <v>49.98671840000001</v>
       </c>
       <c r="N62">
-        <v>119.580448</v>
+        <v>116.6132816</v>
       </c>
       <c r="O62">
-        <v>30.85175558400001</v>
+        <v>30.08622665280001</v>
       </c>
       <c r="P62">
-        <v>88.72869241600002</v>
+        <v>86.52705494720001</v>
       </c>
       <c r="Q62">
-        <v>146.128692416</v>
+        <v>143.9270549472</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1358491337364188</v>
+        <v>0.1378761598759586</v>
       </c>
       <c r="T62">
-        <v>2.07965666827757</v>
+        <v>2.126470204987497</v>
       </c>
       <c r="U62">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V62">
         <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.04548460000000001</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.543206877002997</v>
+        <v>3.332885320993586</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08278464435162386</v>
+        <v>0.08269231520868019</v>
       </c>
       <c r="C63">
-        <v>642.3229390771571</v>
+        <v>632.4183737832897</v>
       </c>
       <c r="D63">
-        <v>1150.546939077157</v>
+        <v>1153.42637378329</v>
       </c>
       <c r="E63">
-        <v>-35.07600000000002</v>
+        <v>-22.29200000000003</v>
       </c>
       <c r="F63">
-        <v>779.8240000000001</v>
+        <v>792.6080000000001</v>
       </c>
       <c r="G63">
         <v>271.6</v>
@@ -6447,28 +6447,28 @@
         <v>166.6</v>
       </c>
       <c r="M63">
-        <v>49.98671840000001</v>
+        <v>50.80617280000001</v>
       </c>
       <c r="N63">
-        <v>116.6132816</v>
+        <v>115.7938272</v>
       </c>
       <c r="O63">
-        <v>30.08622665280001</v>
+        <v>29.8748074176</v>
       </c>
       <c r="P63">
-        <v>86.52705494720001</v>
+        <v>85.9190197824</v>
       </c>
       <c r="Q63">
-        <v>143.9270549472</v>
+        <v>143.3190197824</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1378761598759586</v>
+        <v>0.14000987160179</v>
       </c>
       <c r="T63">
-        <v>2.126470204987497</v>
+        <v>2.175747612050577</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.332885320993586</v>
+        <v>3.279129106138851</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08269231520868019</v>
+        <v>0.08259998606573653</v>
       </c>
       <c r="C64">
-        <v>632.4183737832897</v>
+        <v>622.5282571763371</v>
       </c>
       <c r="D64">
-        <v>1153.42637378329</v>
+        <v>1156.320257176337</v>
       </c>
       <c r="E64">
-        <v>-22.29200000000003</v>
+        <v>-9.508000000000038</v>
       </c>
       <c r="F64">
-        <v>792.6080000000001</v>
+        <v>805.3920000000001</v>
       </c>
       <c r="G64">
         <v>271.6</v>
@@ -6529,28 +6529,28 @@
         <v>166.6</v>
       </c>
       <c r="M64">
-        <v>50.80617280000001</v>
+        <v>51.6256272</v>
       </c>
       <c r="N64">
-        <v>115.7938272</v>
+        <v>114.9743728</v>
       </c>
       <c r="O64">
-        <v>29.8748074176</v>
+        <v>29.66338818240001</v>
       </c>
       <c r="P64">
-        <v>85.9190197824</v>
+        <v>85.31098461760001</v>
       </c>
       <c r="Q64">
-        <v>143.3190197824</v>
+        <v>142.7109846176</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.14000987160179</v>
+        <v>0.1422589190965852</v>
       </c>
       <c r="T64">
-        <v>2.175747612050577</v>
+        <v>2.227688662738688</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.279129106138851</v>
+        <v>3.227079437787441</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08259998606573653</v>
+        <v>0.08250765692279285</v>
       </c>
       <c r="C65">
-        <v>622.5282571763371</v>
+        <v>612.6526982827271</v>
       </c>
       <c r="D65">
-        <v>1156.320257176337</v>
+        <v>1159.228698282727</v>
       </c>
       <c r="E65">
-        <v>-9.508000000000038</v>
+        <v>3.275999999999954</v>
       </c>
       <c r="F65">
-        <v>805.3920000000001</v>
+        <v>818.176</v>
       </c>
       <c r="G65">
         <v>271.6</v>
@@ -6611,28 +6611,28 @@
         <v>166.6</v>
       </c>
       <c r="M65">
-        <v>51.6256272</v>
+        <v>52.44508160000001</v>
       </c>
       <c r="N65">
-        <v>114.9743728</v>
+        <v>114.1549184</v>
       </c>
       <c r="O65">
-        <v>29.66338818240001</v>
+        <v>29.4519689472</v>
       </c>
       <c r="P65">
-        <v>85.31098461760001</v>
+        <v>84.70294945280001</v>
       </c>
       <c r="Q65">
-        <v>142.7109846176</v>
+        <v>142.1029494528</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1422589190965852</v>
+        <v>0.1446329136744246</v>
       </c>
       <c r="T65">
-        <v>2.227688662738688</v>
+        <v>2.282515327353917</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.227079437787441</v>
+        <v>3.176656321572012</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08250765692279285</v>
+        <v>0.0824153277798492</v>
       </c>
       <c r="C66">
-        <v>612.6526982827271</v>
+        <v>602.791807228567</v>
       </c>
       <c r="D66">
-        <v>1159.228698282727</v>
+        <v>1162.151807228567</v>
       </c>
       <c r="E66">
-        <v>3.275999999999954</v>
+        <v>16.05999999999995</v>
       </c>
       <c r="F66">
-        <v>818.176</v>
+        <v>830.96</v>
       </c>
       <c r="G66">
         <v>271.6</v>
@@ -6693,28 +6693,28 @@
         <v>166.6</v>
       </c>
       <c r="M66">
-        <v>52.44508160000001</v>
+        <v>53.26453600000001</v>
       </c>
       <c r="N66">
-        <v>114.1549184</v>
+        <v>113.335464</v>
       </c>
       <c r="O66">
-        <v>29.4519689472</v>
+        <v>29.240549712</v>
       </c>
       <c r="P66">
-        <v>84.70294945280001</v>
+        <v>84.09491428800001</v>
       </c>
       <c r="Q66">
-        <v>142.1029494528</v>
+        <v>141.494914288</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1446329136744246</v>
+        <v>0.1471425650852834</v>
       </c>
       <c r="T66">
-        <v>2.282515327353917</v>
+        <v>2.340474944232874</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.176656321572012</v>
+        <v>3.127784685855519</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0824153277798492</v>
+        <v>0.08232299863690554</v>
       </c>
       <c r="C67">
-        <v>602.791807228567</v>
+        <v>592.9456952535497</v>
       </c>
       <c r="D67">
-        <v>1162.151807228567</v>
+        <v>1165.08969525355</v>
       </c>
       <c r="E67">
-        <v>16.05999999999995</v>
+        <v>28.84400000000005</v>
       </c>
       <c r="F67">
-        <v>830.96</v>
+        <v>843.7440000000001</v>
       </c>
       <c r="G67">
         <v>271.6</v>
@@ -6775,28 +6775,28 @@
         <v>166.6</v>
       </c>
       <c r="M67">
-        <v>53.26453600000001</v>
+        <v>54.08399040000001</v>
       </c>
       <c r="N67">
-        <v>113.335464</v>
+        <v>112.5160096</v>
       </c>
       <c r="O67">
-        <v>29.240549712</v>
+        <v>29.02913047680001</v>
       </c>
       <c r="P67">
-        <v>84.09491428800001</v>
+        <v>83.48687912320001</v>
       </c>
       <c r="Q67">
-        <v>141.494914288</v>
+        <v>140.8868791232</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1471425650852834</v>
+        <v>0.1497998430497222</v>
       </c>
       <c r="T67">
-        <v>2.340474944232874</v>
+        <v>2.401843950340004</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.127784685855519</v>
+        <v>3.080394008797102</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08232299863690554</v>
+        <v>0.08223066949396188</v>
       </c>
       <c r="C68">
-        <v>592.9456952535497</v>
+        <v>583.1144747250629</v>
       </c>
       <c r="D68">
-        <v>1165.08969525355</v>
+        <v>1168.042474725063</v>
       </c>
       <c r="E68">
-        <v>28.84400000000005</v>
+        <v>41.62800000000004</v>
       </c>
       <c r="F68">
-        <v>843.7440000000001</v>
+        <v>856.5280000000001</v>
       </c>
       <c r="G68">
         <v>271.6</v>
@@ -6857,28 +6857,28 @@
         <v>166.6</v>
       </c>
       <c r="M68">
-        <v>54.08399040000001</v>
+        <v>54.90344480000001</v>
       </c>
       <c r="N68">
-        <v>112.5160096</v>
+        <v>111.6965552</v>
       </c>
       <c r="O68">
-        <v>29.02913047680001</v>
+        <v>28.8177112416</v>
       </c>
       <c r="P68">
-        <v>83.48687912320001</v>
+        <v>82.87884395840001</v>
       </c>
       <c r="Q68">
-        <v>140.8868791232</v>
+        <v>140.2788439584</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1497998430497222</v>
+        <v>0.1526181681635209</v>
       </c>
       <c r="T68">
-        <v>2.401843950340004</v>
+        <v>2.466932290150597</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.080394008797102</v>
+        <v>3.034417978815056</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08223066949396188</v>
+        <v>0.08607390835101822</v>
       </c>
       <c r="C69">
-        <v>583.1144747250629</v>
+        <v>458.8670878982887</v>
       </c>
       <c r="D69">
-        <v>1168.042474725063</v>
+        <v>1056.579087898289</v>
       </c>
       <c r="E69">
-        <v>41.62800000000004</v>
+        <v>54.41200000000003</v>
       </c>
       <c r="F69">
-        <v>856.5280000000001</v>
+        <v>869.3120000000001</v>
       </c>
       <c r="G69">
         <v>271.6</v>
@@ -6939,45 +6939,45 @@
         <v>166.6</v>
       </c>
       <c r="M69">
-        <v>54.90344480000001</v>
+        <v>62.50353280000002</v>
       </c>
       <c r="N69">
-        <v>111.6965552</v>
+        <v>104.0964672</v>
       </c>
       <c r="O69">
-        <v>28.8177112416</v>
+        <v>26.8568885376</v>
       </c>
       <c r="P69">
-        <v>82.87884395840001</v>
+        <v>77.23957866240001</v>
       </c>
       <c r="Q69">
-        <v>140.2788439584</v>
+        <v>134.6395786624</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1526181681635209</v>
+        <v>0.1556126385969319</v>
       </c>
       <c r="T69">
-        <v>2.466932290150597</v>
+        <v>2.536088651199352</v>
       </c>
       <c r="U69">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V69">
         <v>0.258</v>
       </c>
       <c r="W69">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.034417978815056</v>
+        <v>2.665449336009372</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08607390835101822</v>
+        <v>0.08603945520807454</v>
       </c>
       <c r="C70">
-        <v>458.8670878982887</v>
+        <v>446.9877341008381</v>
       </c>
       <c r="D70">
-        <v>1056.579087898289</v>
+        <v>1057.483734100838</v>
       </c>
       <c r="E70">
-        <v>54.41200000000003</v>
+        <v>67.19600000000003</v>
       </c>
       <c r="F70">
-        <v>869.3120000000001</v>
+        <v>882.0960000000001</v>
       </c>
       <c r="G70">
         <v>271.6</v>
@@ -7021,28 +7021,28 @@
         <v>166.6</v>
       </c>
       <c r="M70">
-        <v>62.50353280000002</v>
+        <v>63.42270240000001</v>
       </c>
       <c r="N70">
-        <v>104.0964672</v>
+        <v>103.1772976</v>
       </c>
       <c r="O70">
-        <v>26.8568885376</v>
+        <v>26.6197427808</v>
       </c>
       <c r="P70">
-        <v>77.23957866240001</v>
+        <v>76.55755481919999</v>
       </c>
       <c r="Q70">
-        <v>134.6395786624</v>
+        <v>133.9575548192</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1556126385969319</v>
+        <v>0.1588003006712082</v>
       </c>
       <c r="T70">
-        <v>2.536088651199352</v>
+        <v>2.609706712960929</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.665449336009372</v>
+        <v>2.626819635487497</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08603945520807454</v>
+        <v>0.08600500206513088</v>
       </c>
       <c r="C71">
-        <v>446.9877341008381</v>
+        <v>435.1099307525024</v>
       </c>
       <c r="D71">
-        <v>1057.483734100838</v>
+        <v>1058.389930752502</v>
       </c>
       <c r="E71">
-        <v>67.19600000000003</v>
+        <v>79.98000000000002</v>
       </c>
       <c r="F71">
-        <v>882.0960000000001</v>
+        <v>894.8800000000001</v>
       </c>
       <c r="G71">
         <v>271.6</v>
@@ -7103,28 +7103,28 @@
         <v>166.6</v>
       </c>
       <c r="M71">
-        <v>63.42270240000001</v>
+        <v>64.34187200000001</v>
       </c>
       <c r="N71">
-        <v>103.1772976</v>
+        <v>102.258128</v>
       </c>
       <c r="O71">
-        <v>26.6197427808</v>
+        <v>26.382597024</v>
       </c>
       <c r="P71">
-        <v>76.55755481919999</v>
+        <v>75.87553097600001</v>
       </c>
       <c r="Q71">
-        <v>133.9575548192</v>
+        <v>133.275530976</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1588003006712082</v>
+        <v>0.1622004735504363</v>
       </c>
       <c r="T71">
-        <v>2.609706712960929</v>
+        <v>2.688232645506612</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.626819635487497</v>
+        <v>2.589293640694819</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08600500206513088</v>
+        <v>0.08597054892218722</v>
       </c>
       <c r="C72">
-        <v>435.1099307525024</v>
+        <v>423.2336818426102</v>
       </c>
       <c r="D72">
-        <v>1058.389930752502</v>
+        <v>1059.29768184261</v>
       </c>
       <c r="E72">
-        <v>79.98000000000002</v>
+        <v>92.76400000000012</v>
       </c>
       <c r="F72">
-        <v>894.8800000000001</v>
+        <v>907.6640000000002</v>
       </c>
       <c r="G72">
         <v>271.6</v>
@@ -7185,28 +7185,28 @@
         <v>166.6</v>
       </c>
       <c r="M72">
-        <v>64.34187200000001</v>
+        <v>65.26104160000003</v>
       </c>
       <c r="N72">
-        <v>102.258128</v>
+        <v>101.3389584</v>
       </c>
       <c r="O72">
-        <v>26.382597024</v>
+        <v>26.1454512672</v>
       </c>
       <c r="P72">
-        <v>75.87553097600001</v>
+        <v>75.19350713279999</v>
       </c>
       <c r="Q72">
-        <v>133.275530976</v>
+        <v>132.5935071328</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1622004735504363</v>
+        <v>0.1658351411109905</v>
       </c>
       <c r="T72">
-        <v>2.688232645506612</v>
+        <v>2.77217415960717</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.589293640694819</v>
+        <v>2.552824716177989</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08597054892218722</v>
+        <v>0.08593609577924356</v>
       </c>
       <c r="C73">
-        <v>423.2336818426104</v>
+        <v>411.3589913741888</v>
       </c>
       <c r="D73">
-        <v>1059.29768184261</v>
+        <v>1060.206991374189</v>
       </c>
       <c r="E73">
-        <v>92.7639999999999</v>
+        <v>105.5479999999999</v>
       </c>
       <c r="F73">
-        <v>907.664</v>
+        <v>920.448</v>
       </c>
       <c r="G73">
         <v>271.6</v>
@@ -7267,28 +7267,28 @@
         <v>166.6</v>
       </c>
       <c r="M73">
-        <v>65.2610416</v>
+        <v>66.1802112</v>
       </c>
       <c r="N73">
-        <v>101.3389584</v>
+        <v>100.4197888</v>
       </c>
       <c r="O73">
-        <v>26.14545126720001</v>
+        <v>25.90830551040001</v>
       </c>
       <c r="P73">
-        <v>75.19350713280002</v>
+        <v>74.51148328960002</v>
       </c>
       <c r="Q73">
-        <v>132.5935071328</v>
+        <v>131.9114832896</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1658351411109904</v>
+        <v>0.1697294277830127</v>
       </c>
       <c r="T73">
-        <v>2.772174159607169</v>
+        <v>2.86211149614348</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.55282471617799</v>
+        <v>2.517368817342185</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08593609577924356</v>
+        <v>0.08801411663629991</v>
       </c>
       <c r="C74">
-        <v>411.3589913741888</v>
+        <v>346.3855245222861</v>
       </c>
       <c r="D74">
-        <v>1060.206991374189</v>
+        <v>1008.017524522286</v>
       </c>
       <c r="E74">
-        <v>105.5479999999999</v>
+        <v>118.332</v>
       </c>
       <c r="F74">
-        <v>920.448</v>
+        <v>933.2320000000001</v>
       </c>
       <c r="G74">
         <v>271.6</v>
@@ -7349,45 +7349,45 @@
         <v>166.6</v>
       </c>
       <c r="M74">
-        <v>66.1802112</v>
+        <v>70.73898560000001</v>
       </c>
       <c r="N74">
-        <v>100.4197888</v>
+        <v>95.86101440000002</v>
       </c>
       <c r="O74">
-        <v>25.90830551040001</v>
+        <v>24.7321417152</v>
       </c>
       <c r="P74">
-        <v>74.51148328960002</v>
+        <v>71.12887268480002</v>
       </c>
       <c r="Q74">
-        <v>131.9114832896</v>
+        <v>128.5288726848</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1697294277830127</v>
+        <v>0.173912180134444</v>
       </c>
       <c r="T74">
-        <v>2.86211149614348</v>
+        <v>2.958710857608407</v>
       </c>
       <c r="U74">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V74">
         <v>0.258</v>
       </c>
       <c r="W74">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.517368817342185</v>
+        <v>2.355136967075762</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08801411663629991</v>
+        <v>0.08800860149335624</v>
       </c>
       <c r="C75">
-        <v>346.3855245222861</v>
+        <v>333.733236082034</v>
       </c>
       <c r="D75">
-        <v>1008.017524522286</v>
+        <v>1008.149236082034</v>
       </c>
       <c r="E75">
-        <v>118.332</v>
+        <v>131.116</v>
       </c>
       <c r="F75">
-        <v>933.2320000000001</v>
+        <v>946.0160000000001</v>
       </c>
       <c r="G75">
         <v>271.6</v>
@@ -7431,28 +7431,28 @@
         <v>166.6</v>
       </c>
       <c r="M75">
-        <v>70.73898560000001</v>
+        <v>71.70801280000001</v>
       </c>
       <c r="N75">
-        <v>95.86101440000002</v>
+        <v>94.89198720000002</v>
       </c>
       <c r="O75">
-        <v>24.7321417152</v>
+        <v>24.4821326976</v>
       </c>
       <c r="P75">
-        <v>71.12887268480002</v>
+        <v>70.40985450240001</v>
       </c>
       <c r="Q75">
-        <v>128.5288726848</v>
+        <v>127.8098545024</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.173912180134444</v>
+        <v>0.1784166826667547</v>
       </c>
       <c r="T75">
-        <v>2.958710857608407</v>
+        <v>3.062740939186021</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.355136967075762</v>
+        <v>2.323310791845008</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08800860149335624</v>
+        <v>0.08800308635041257</v>
       </c>
       <c r="C76">
-        <v>333.733236082034</v>
+        <v>321.0809820661874</v>
       </c>
       <c r="D76">
-        <v>1008.149236082034</v>
+        <v>1008.280982066187</v>
       </c>
       <c r="E76">
-        <v>131.116</v>
+        <v>143.9</v>
       </c>
       <c r="F76">
-        <v>946.0160000000001</v>
+        <v>958.8000000000001</v>
       </c>
       <c r="G76">
         <v>271.6</v>
@@ -7513,28 +7513,28 @@
         <v>166.6</v>
       </c>
       <c r="M76">
-        <v>71.70801280000001</v>
+        <v>72.67704000000001</v>
       </c>
       <c r="N76">
-        <v>94.89198720000002</v>
+        <v>93.92296000000002</v>
       </c>
       <c r="O76">
-        <v>24.4821326976</v>
+        <v>24.23212368</v>
       </c>
       <c r="P76">
-        <v>70.40985450240001</v>
+        <v>69.69083632000002</v>
       </c>
       <c r="Q76">
-        <v>127.8098545024</v>
+        <v>127.09083632</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1784166826667547</v>
+        <v>0.1832815454016503</v>
       </c>
       <c r="T76">
-        <v>3.062740939186021</v>
+        <v>3.175093427289844</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.323310791845008</v>
+        <v>2.292333314620409</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08800308635041257</v>
+        <v>0.0879975712074689</v>
       </c>
       <c r="C77">
-        <v>321.0809820661874</v>
+        <v>308.4287624882438</v>
       </c>
       <c r="D77">
-        <v>1008.280982066187</v>
+        <v>1008.412762488244</v>
       </c>
       <c r="E77">
-        <v>143.9</v>
+        <v>156.684</v>
       </c>
       <c r="F77">
-        <v>958.8000000000001</v>
+        <v>971.5840000000001</v>
       </c>
       <c r="G77">
         <v>271.6</v>
@@ -7595,28 +7595,28 @@
         <v>166.6</v>
       </c>
       <c r="M77">
-        <v>72.67704000000001</v>
+        <v>73.6460672</v>
       </c>
       <c r="N77">
-        <v>93.92296000000002</v>
+        <v>92.95393280000002</v>
       </c>
       <c r="O77">
-        <v>24.23212368</v>
+        <v>23.9821146624</v>
       </c>
       <c r="P77">
-        <v>69.69083632000002</v>
+        <v>68.97181813760001</v>
       </c>
       <c r="Q77">
-        <v>127.09083632</v>
+        <v>126.3718181376</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1832815454016503</v>
+        <v>0.1885518133644538</v>
       </c>
       <c r="T77">
-        <v>3.175093427289844</v>
+        <v>3.296808622735653</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.292333314620409</v>
+        <v>2.262171034164877</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0879975712074689</v>
+        <v>0.08799205606452525</v>
       </c>
       <c r="C78">
-        <v>308.4287624882438</v>
+        <v>295.7765773617078</v>
       </c>
       <c r="D78">
-        <v>1008.412762488244</v>
+        <v>1008.544577361708</v>
       </c>
       <c r="E78">
-        <v>156.684</v>
+        <v>169.468</v>
       </c>
       <c r="F78">
-        <v>971.5840000000001</v>
+        <v>984.3680000000001</v>
       </c>
       <c r="G78">
         <v>271.6</v>
@@ -7677,28 +7677,28 @@
         <v>166.6</v>
       </c>
       <c r="M78">
-        <v>73.6460672</v>
+        <v>74.6150944</v>
       </c>
       <c r="N78">
-        <v>92.95393280000002</v>
+        <v>91.98490560000002</v>
       </c>
       <c r="O78">
-        <v>23.9821146624</v>
+        <v>23.7321056448</v>
       </c>
       <c r="P78">
-        <v>68.97181813760001</v>
+        <v>68.25279995520002</v>
       </c>
       <c r="Q78">
-        <v>126.3718181376</v>
+        <v>125.6527999552</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1885518133644538</v>
+        <v>0.1942803654979358</v>
       </c>
       <c r="T78">
-        <v>3.296808622735653</v>
+        <v>3.429107748220227</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.262171034164877</v>
+        <v>2.232792189565333</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08799205606452525</v>
+        <v>0.08798654092158158</v>
       </c>
       <c r="C79">
-        <v>295.7765773617078</v>
+        <v>283.1244267000915</v>
       </c>
       <c r="D79">
-        <v>1008.544577361708</v>
+        <v>1008.676426700092</v>
       </c>
       <c r="E79">
-        <v>169.468</v>
+        <v>182.2520000000001</v>
       </c>
       <c r="F79">
-        <v>984.3680000000001</v>
+        <v>997.1520000000002</v>
       </c>
       <c r="G79">
         <v>271.6</v>
@@ -7759,28 +7759,28 @@
         <v>166.6</v>
       </c>
       <c r="M79">
-        <v>74.6150944</v>
+        <v>75.58412160000002</v>
       </c>
       <c r="N79">
-        <v>91.98490560000002</v>
+        <v>91.01587840000001</v>
       </c>
       <c r="O79">
-        <v>23.7321056448</v>
+        <v>23.4820966272</v>
       </c>
       <c r="P79">
-        <v>68.25279995520002</v>
+        <v>67.53378177280001</v>
       </c>
       <c r="Q79">
-        <v>125.6527999552</v>
+        <v>124.9337817728</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1942803654979358</v>
+        <v>0.2005296950980981</v>
       </c>
       <c r="T79">
-        <v>3.429107748220227</v>
+        <v>3.573434066930672</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.232792189565333</v>
+        <v>2.204166648673469</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08798654092158158</v>
+        <v>0.08798102577863792</v>
       </c>
       <c r="C80">
-        <v>283.1244267000915</v>
+        <v>270.4723105169132</v>
       </c>
       <c r="D80">
-        <v>1008.676426700092</v>
+        <v>1008.808310516913</v>
       </c>
       <c r="E80">
-        <v>182.2520000000001</v>
+        <v>195.0360000000001</v>
       </c>
       <c r="F80">
-        <v>997.1520000000002</v>
+        <v>1009.936</v>
       </c>
       <c r="G80">
         <v>271.6</v>
@@ -7841,28 +7841,28 @@
         <v>166.6</v>
       </c>
       <c r="M80">
-        <v>75.58412160000002</v>
+        <v>76.55314880000002</v>
       </c>
       <c r="N80">
-        <v>91.01587840000001</v>
+        <v>90.04685120000001</v>
       </c>
       <c r="O80">
-        <v>23.4820966272</v>
+        <v>23.2320876096</v>
       </c>
       <c r="P80">
-        <v>67.53378177280001</v>
+        <v>66.81476359040001</v>
       </c>
       <c r="Q80">
-        <v>124.9337817728</v>
+        <v>124.2147635904</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2005296950980981</v>
+        <v>0.2073741989458949</v>
       </c>
       <c r="T80">
-        <v>3.573434066930672</v>
+        <v>3.731505749327826</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.204166648673469</v>
+        <v>2.176265805019375</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08798102577863792</v>
+        <v>0.08797551063569425</v>
       </c>
       <c r="C81">
-        <v>270.4723105169132</v>
+        <v>257.8202288256995</v>
       </c>
       <c r="D81">
-        <v>1008.808310516913</v>
+        <v>1008.9402288257</v>
       </c>
       <c r="E81">
-        <v>195.0360000000001</v>
+        <v>207.8200000000001</v>
       </c>
       <c r="F81">
-        <v>1009.936</v>
+        <v>1022.72</v>
       </c>
       <c r="G81">
         <v>271.6</v>
@@ -7923,28 +7923,28 @@
         <v>166.6</v>
       </c>
       <c r="M81">
-        <v>76.55314880000002</v>
+        <v>77.52217600000002</v>
       </c>
       <c r="N81">
-        <v>90.04685120000001</v>
+        <v>89.07782400000001</v>
       </c>
       <c r="O81">
-        <v>23.2320876096</v>
+        <v>22.982078592</v>
       </c>
       <c r="P81">
-        <v>66.81476359040001</v>
+        <v>66.095745408</v>
       </c>
       <c r="Q81">
-        <v>124.2147635904</v>
+        <v>123.495745408</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2073741989458949</v>
+        <v>0.2149031531784713</v>
       </c>
       <c r="T81">
-        <v>3.731505749327826</v>
+        <v>3.905384599964695</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.176265805019375</v>
+        <v>2.149062482456633</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08797551063569425</v>
+        <v>0.08796999549275059</v>
       </c>
       <c r="C82">
-        <v>257.8202288256995</v>
+        <v>245.168181639983</v>
       </c>
       <c r="D82">
-        <v>1008.9402288257</v>
+        <v>1009.072181639983</v>
       </c>
       <c r="E82">
-        <v>207.8200000000001</v>
+        <v>220.604</v>
       </c>
       <c r="F82">
-        <v>1022.72</v>
+        <v>1035.504</v>
       </c>
       <c r="G82">
         <v>271.6</v>
@@ -8005,28 +8005,28 @@
         <v>166.6</v>
       </c>
       <c r="M82">
-        <v>77.52217600000002</v>
+        <v>78.49120320000002</v>
       </c>
       <c r="N82">
-        <v>89.07782400000001</v>
+        <v>88.10879680000001</v>
       </c>
       <c r="O82">
-        <v>22.982078592</v>
+        <v>22.7320695744</v>
       </c>
       <c r="P82">
-        <v>66.095745408</v>
+        <v>65.37672722560001</v>
       </c>
       <c r="Q82">
-        <v>123.495745408</v>
+        <v>122.7767272256</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2149031531784713</v>
+        <v>0.2232246289092137</v>
       </c>
       <c r="T82">
-        <v>3.905384599964695</v>
+        <v>4.097566487510708</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.149062482456633</v>
+        <v>2.122530846870748</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08796999549275059</v>
+        <v>0.08796448034980693</v>
       </c>
       <c r="C83">
-        <v>245.168181639983</v>
+        <v>232.5161689733034</v>
       </c>
       <c r="D83">
-        <v>1009.072181639983</v>
+        <v>1009.204168973304</v>
       </c>
       <c r="E83">
-        <v>220.604</v>
+        <v>233.3880000000001</v>
       </c>
       <c r="F83">
-        <v>1035.504</v>
+        <v>1048.288</v>
       </c>
       <c r="G83">
         <v>271.6</v>
@@ -8087,28 +8087,28 @@
         <v>166.6</v>
       </c>
       <c r="M83">
-        <v>78.49120320000002</v>
+        <v>79.46023040000003</v>
       </c>
       <c r="N83">
-        <v>88.10879680000001</v>
+        <v>87.13976959999999</v>
       </c>
       <c r="O83">
-        <v>22.7320695744</v>
+        <v>22.4820605568</v>
       </c>
       <c r="P83">
-        <v>65.37672722560001</v>
+        <v>64.65770904319999</v>
       </c>
       <c r="Q83">
-        <v>122.7767272256</v>
+        <v>122.0577090432</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2232246289092137</v>
+        <v>0.232470713054483</v>
       </c>
       <c r="T83">
-        <v>4.097566487510708</v>
+        <v>4.31110191811739</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.122530846870748</v>
+        <v>2.096646324347934</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08796448034980693</v>
+        <v>0.08795896520686326</v>
       </c>
       <c r="C84">
-        <v>232.5161689733034</v>
+        <v>219.8641908392087</v>
       </c>
       <c r="D84">
-        <v>1009.204168973304</v>
+        <v>1009.336190839209</v>
       </c>
       <c r="E84">
-        <v>233.3880000000001</v>
+        <v>246.172</v>
       </c>
       <c r="F84">
-        <v>1048.288</v>
+        <v>1061.072</v>
       </c>
       <c r="G84">
         <v>271.6</v>
@@ -8169,28 +8169,28 @@
         <v>166.6</v>
       </c>
       <c r="M84">
-        <v>79.46023040000003</v>
+        <v>80.42925760000001</v>
       </c>
       <c r="N84">
-        <v>87.13976959999999</v>
+        <v>86.17074240000001</v>
       </c>
       <c r="O84">
-        <v>22.4820605568</v>
+        <v>22.2320515392</v>
       </c>
       <c r="P84">
-        <v>64.65770904319999</v>
+        <v>63.93869086080001</v>
       </c>
       <c r="Q84">
-        <v>122.0577090432</v>
+        <v>121.3386908608</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.232470713054483</v>
+        <v>0.2428045718050781</v>
       </c>
       <c r="T84">
-        <v>4.31110191811739</v>
+        <v>4.549759164089563</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.096646324347934</v>
+        <v>2.071385525259405</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08795896520686326</v>
+        <v>0.08795345006391959</v>
       </c>
       <c r="C85">
-        <v>219.8641908392087</v>
+        <v>207.2122472512519</v>
       </c>
       <c r="D85">
-        <v>1009.336190839209</v>
+        <v>1009.468247251252</v>
       </c>
       <c r="E85">
-        <v>246.172</v>
+        <v>258.9560000000001</v>
       </c>
       <c r="F85">
-        <v>1061.072</v>
+        <v>1073.856</v>
       </c>
       <c r="G85">
         <v>271.6</v>
@@ -8251,28 +8251,28 @@
         <v>166.6</v>
       </c>
       <c r="M85">
-        <v>80.42925760000001</v>
+        <v>81.39828480000003</v>
       </c>
       <c r="N85">
-        <v>86.17074240000001</v>
+        <v>85.2017152</v>
       </c>
       <c r="O85">
-        <v>22.2320515392</v>
+        <v>21.9820425216</v>
       </c>
       <c r="P85">
-        <v>63.93869086080001</v>
+        <v>63.21967267839999</v>
       </c>
       <c r="Q85">
-        <v>121.3386908608</v>
+        <v>120.6196726784</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2428045718050781</v>
+        <v>0.2544301628994975</v>
       </c>
       <c r="T85">
-        <v>4.549759164089563</v>
+        <v>4.818248565808258</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.071385525259405</v>
+        <v>2.046726173768221</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08795345006391959</v>
+        <v>0.08794793492097594</v>
       </c>
       <c r="C86">
-        <v>207.2122472512522</v>
+        <v>194.5603382229949</v>
       </c>
       <c r="D86">
-        <v>1009.468247251252</v>
+        <v>1009.600338222995</v>
       </c>
       <c r="E86">
-        <v>258.9559999999999</v>
+        <v>271.74</v>
       </c>
       <c r="F86">
-        <v>1073.856</v>
+        <v>1086.64</v>
       </c>
       <c r="G86">
         <v>271.6</v>
@@ -8333,28 +8333,28 @@
         <v>166.6</v>
       </c>
       <c r="M86">
-        <v>81.39828480000001</v>
+        <v>82.36731200000001</v>
       </c>
       <c r="N86">
-        <v>85.20171520000001</v>
+        <v>84.23268800000001</v>
       </c>
       <c r="O86">
-        <v>21.9820425216</v>
+        <v>21.732033504</v>
       </c>
       <c r="P86">
-        <v>63.2196726784</v>
+        <v>62.50065449600001</v>
       </c>
       <c r="Q86">
-        <v>120.6196726784</v>
+        <v>119.900654496</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2544301628994974</v>
+        <v>0.2676058328065062</v>
       </c>
       <c r="T86">
-        <v>4.818248565808255</v>
+        <v>5.122536554422776</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.046726173768222</v>
+        <v>2.022647042312125</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08794793492097594</v>
+        <v>0.09700372377803228</v>
       </c>
       <c r="C87">
-        <v>194.5603382229949</v>
+        <v>3.22042825453741</v>
       </c>
       <c r="D87">
-        <v>1009.600338222995</v>
+        <v>831.0444282545374</v>
       </c>
       <c r="E87">
-        <v>271.74</v>
+        <v>284.5239999999999</v>
       </c>
       <c r="F87">
-        <v>1086.64</v>
+        <v>1099.424</v>
       </c>
       <c r="G87">
         <v>271.6</v>
@@ -8415,45 +8415,45 @@
         <v>166.6</v>
       </c>
       <c r="M87">
-        <v>82.36731200000001</v>
+        <v>98.94816000000002</v>
       </c>
       <c r="N87">
-        <v>84.23268800000001</v>
+        <v>67.65184000000001</v>
       </c>
       <c r="O87">
-        <v>21.732033504</v>
+        <v>17.45417472</v>
       </c>
       <c r="P87">
-        <v>62.50065449600001</v>
+        <v>50.19766528000001</v>
       </c>
       <c r="Q87">
-        <v>119.900654496</v>
+        <v>107.59766528</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2676058328065062</v>
+        <v>0.2826637412716591</v>
       </c>
       <c r="T87">
-        <v>5.122536554422776</v>
+        <v>5.470294255696515</v>
       </c>
       <c r="U87">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V87">
         <v>0.258</v>
       </c>
       <c r="W87">
-        <v>0.0562436</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.022647042312125</v>
+        <v>1.683709934575842</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09700372377803228</v>
+        <v>0.09710357263508862</v>
       </c>
       <c r="C88">
-        <v>3.22042825453741</v>
+        <v>-11.18098028179338</v>
       </c>
       <c r="D88">
-        <v>831.0444282545374</v>
+        <v>829.4270197182067</v>
       </c>
       <c r="E88">
-        <v>284.5239999999999</v>
+        <v>297.308</v>
       </c>
       <c r="F88">
-        <v>1099.424</v>
+        <v>1112.208</v>
       </c>
       <c r="G88">
         <v>271.6</v>
@@ -8497,28 +8497,28 @@
         <v>166.6</v>
       </c>
       <c r="M88">
-        <v>98.94816000000002</v>
+        <v>100.09872</v>
       </c>
       <c r="N88">
-        <v>67.65184000000001</v>
+        <v>66.50128000000001</v>
       </c>
       <c r="O88">
-        <v>17.45417472</v>
+        <v>17.15733024</v>
       </c>
       <c r="P88">
-        <v>50.19766528000001</v>
+        <v>49.34394976</v>
       </c>
       <c r="Q88">
-        <v>107.59766528</v>
+        <v>106.74394976</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2826637412716591</v>
+        <v>0.3000382510391431</v>
       </c>
       <c r="T88">
-        <v>5.470294255696515</v>
+        <v>5.871553141781596</v>
       </c>
       <c r="U88">
         <v>0.09000000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.683709934575842</v>
+        <v>1.664356946822097</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09710357263508862</v>
+        <v>0.09720342149214495</v>
       </c>
       <c r="C89">
-        <v>-11.18098028179338</v>
+        <v>-25.57610533001935</v>
       </c>
       <c r="D89">
-        <v>829.4270197182067</v>
+        <v>827.8158946699809</v>
       </c>
       <c r="E89">
-        <v>297.308</v>
+        <v>310.0920000000001</v>
       </c>
       <c r="F89">
-        <v>1112.208</v>
+        <v>1124.992</v>
       </c>
       <c r="G89">
         <v>271.6</v>
@@ -8579,28 +8579,28 @@
         <v>166.6</v>
       </c>
       <c r="M89">
-        <v>100.09872</v>
+        <v>101.24928</v>
       </c>
       <c r="N89">
-        <v>66.50128000000001</v>
+        <v>65.35072</v>
       </c>
       <c r="O89">
-        <v>17.15733024</v>
+        <v>16.86048576</v>
       </c>
       <c r="P89">
-        <v>49.34394976</v>
+        <v>48.49023423999999</v>
       </c>
       <c r="Q89">
-        <v>106.74394976</v>
+        <v>105.89023424</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3000382510391431</v>
+        <v>0.3203085124345412</v>
       </c>
       <c r="T89">
-        <v>5.871553141781596</v>
+        <v>6.33968850888086</v>
       </c>
       <c r="U89">
         <v>0.09000000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.664356946822097</v>
+        <v>1.645443799699119</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09720342149214495</v>
+        <v>0.09730327034920128</v>
       </c>
       <c r="C90">
-        <v>-25.57610533001935</v>
+        <v>-39.96498343534017</v>
       </c>
       <c r="D90">
-        <v>827.8158946699809</v>
+        <v>826.2110165646599</v>
       </c>
       <c r="E90">
-        <v>310.0920000000001</v>
+        <v>322.876</v>
       </c>
       <c r="F90">
-        <v>1124.992</v>
+        <v>1137.776</v>
       </c>
       <c r="G90">
         <v>271.6</v>
@@ -8661,28 +8661,28 @@
         <v>166.6</v>
       </c>
       <c r="M90">
-        <v>101.24928</v>
+        <v>102.39984</v>
       </c>
       <c r="N90">
-        <v>65.35072</v>
+        <v>64.20016000000001</v>
       </c>
       <c r="O90">
-        <v>16.86048576</v>
+        <v>16.56364128</v>
       </c>
       <c r="P90">
-        <v>48.49023423999999</v>
+        <v>47.63651872000001</v>
       </c>
       <c r="Q90">
-        <v>105.89023424</v>
+        <v>105.03651872</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3203085124345412</v>
+        <v>0.3442642759018298</v>
       </c>
       <c r="T90">
-        <v>6.33968850888086</v>
+        <v>6.892939397270897</v>
       </c>
       <c r="U90">
         <v>0.09000000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.645443799699119</v>
+        <v>1.62695566711823</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09730327034920128</v>
+        <v>0.09740311920625763</v>
       </c>
       <c r="C91">
-        <v>-39.96498343534017</v>
+        <v>-54.34765086010589</v>
       </c>
       <c r="D91">
-        <v>826.2110165646599</v>
+        <v>824.6123491398941</v>
       </c>
       <c r="E91">
-        <v>322.876</v>
+        <v>335.6600000000001</v>
       </c>
       <c r="F91">
-        <v>1137.776</v>
+        <v>1150.56</v>
       </c>
       <c r="G91">
         <v>271.6</v>
@@ -8743,28 +8743,28 @@
         <v>166.6</v>
       </c>
       <c r="M91">
-        <v>102.39984</v>
+        <v>103.5504</v>
       </c>
       <c r="N91">
-        <v>64.20016000000001</v>
+        <v>63.0496</v>
       </c>
       <c r="O91">
-        <v>16.56364128</v>
+        <v>16.2667968</v>
       </c>
       <c r="P91">
-        <v>47.63651872000001</v>
+        <v>46.7828032</v>
       </c>
       <c r="Q91">
-        <v>105.03651872</v>
+        <v>104.1828032</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3442642759018298</v>
+        <v>0.3730111920625762</v>
       </c>
       <c r="T91">
-        <v>6.892939397270897</v>
+        <v>7.556840463338943</v>
       </c>
       <c r="U91">
         <v>0.09000000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.62695566711823</v>
+        <v>1.608878381928027</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09740311920625763</v>
+        <v>0.09750296806331396</v>
       </c>
       <c r="C92">
-        <v>-54.34765086010589</v>
+        <v>-68.72414358654532</v>
       </c>
       <c r="D92">
-        <v>824.6123491398941</v>
+        <v>823.0198564134548</v>
       </c>
       <c r="E92">
-        <v>335.6600000000001</v>
+        <v>348.444</v>
       </c>
       <c r="F92">
-        <v>1150.56</v>
+        <v>1163.344</v>
       </c>
       <c r="G92">
         <v>271.6</v>
@@ -8825,28 +8825,28 @@
         <v>166.6</v>
       </c>
       <c r="M92">
-        <v>103.5504</v>
+        <v>104.70096</v>
       </c>
       <c r="N92">
-        <v>63.0496</v>
+        <v>61.89904</v>
       </c>
       <c r="O92">
-        <v>16.2667968</v>
+        <v>15.96995232</v>
       </c>
       <c r="P92">
-        <v>46.7828032</v>
+        <v>45.92908767999999</v>
       </c>
       <c r="Q92">
-        <v>104.1828032</v>
+        <v>103.32908768</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3730111920625762</v>
+        <v>0.4081463118145996</v>
       </c>
       <c r="T92">
-        <v>7.556840463338943</v>
+        <v>8.368275099644332</v>
       </c>
       <c r="U92">
         <v>0.09000000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.608878381928027</v>
+        <v>1.591198399709038</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09750296806331396</v>
+        <v>0.0976028169203703</v>
       </c>
       <c r="C93">
-        <v>-68.72414358654532</v>
+        <v>-83.09449731946825</v>
       </c>
       <c r="D93">
-        <v>823.0198564134548</v>
+        <v>821.4335026805318</v>
       </c>
       <c r="E93">
-        <v>348.444</v>
+        <v>361.2280000000001</v>
       </c>
       <c r="F93">
-        <v>1163.344</v>
+        <v>1176.128</v>
       </c>
       <c r="G93">
         <v>271.6</v>
@@ -8907,28 +8907,28 @@
         <v>166.6</v>
       </c>
       <c r="M93">
-        <v>104.70096</v>
+        <v>105.85152</v>
       </c>
       <c r="N93">
-        <v>61.89904</v>
+        <v>60.74848</v>
       </c>
       <c r="O93">
-        <v>15.96995232</v>
+        <v>15.67310784</v>
       </c>
       <c r="P93">
-        <v>45.92908767999999</v>
+        <v>45.07537216</v>
       </c>
       <c r="Q93">
-        <v>103.32908768</v>
+        <v>102.47537216</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4081463118145996</v>
+        <v>0.4520652115046289</v>
       </c>
       <c r="T93">
-        <v>8.368275099644332</v>
+        <v>9.382568395026071</v>
       </c>
       <c r="U93">
         <v>0.09000000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.591198399709038</v>
+        <v>1.573902764929592</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0976028169203703</v>
+        <v>0.09770266577742663</v>
       </c>
       <c r="C94">
-        <v>-83.09449731946825</v>
+        <v>-97.45874748893243</v>
       </c>
       <c r="D94">
-        <v>821.4335026805318</v>
+        <v>819.8532525110675</v>
       </c>
       <c r="E94">
-        <v>361.2280000000001</v>
+        <v>374.0119999999999</v>
       </c>
       <c r="F94">
-        <v>1176.128</v>
+        <v>1188.912</v>
       </c>
       <c r="G94">
         <v>271.6</v>
@@ -8989,28 +8989,28 @@
         <v>166.6</v>
       </c>
       <c r="M94">
-        <v>105.85152</v>
+        <v>107.00208</v>
       </c>
       <c r="N94">
-        <v>60.74848</v>
+        <v>59.59792</v>
       </c>
       <c r="O94">
-        <v>15.67310784</v>
+        <v>15.37626336</v>
       </c>
       <c r="P94">
-        <v>45.07537216</v>
+        <v>44.22165664</v>
       </c>
       <c r="Q94">
-        <v>102.47537216</v>
+        <v>101.62165664</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4520652115046289</v>
+        <v>0.5085323682489521</v>
       </c>
       <c r="T94">
-        <v>9.382568395026071</v>
+        <v>10.68665977480259</v>
       </c>
       <c r="U94">
         <v>0.09000000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.573902764929592</v>
+        <v>1.556979079285188</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09770266577742663</v>
+        <v>0.09780251463448297</v>
       </c>
       <c r="C95">
-        <v>-97.45874748893243</v>
+        <v>-111.8169292528828</v>
       </c>
       <c r="D95">
-        <v>819.8532525110675</v>
+        <v>818.2790707471173</v>
       </c>
       <c r="E95">
-        <v>374.0119999999999</v>
+        <v>386.796</v>
       </c>
       <c r="F95">
-        <v>1188.912</v>
+        <v>1201.696</v>
       </c>
       <c r="G95">
         <v>271.6</v>
@@ -9071,28 +9071,28 @@
         <v>166.6</v>
       </c>
       <c r="M95">
-        <v>107.00208</v>
+        <v>108.15264</v>
       </c>
       <c r="N95">
-        <v>59.59792</v>
+        <v>58.44736</v>
       </c>
       <c r="O95">
-        <v>15.37626336</v>
+        <v>15.07941888</v>
       </c>
       <c r="P95">
-        <v>44.22165664</v>
+        <v>43.36794112</v>
       </c>
       <c r="Q95">
-        <v>101.62165664</v>
+        <v>100.76794112</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5085323682489521</v>
+        <v>0.5838219105747166</v>
       </c>
       <c r="T95">
-        <v>10.68665977480259</v>
+        <v>12.42544828117128</v>
       </c>
       <c r="U95">
         <v>0.09000000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.556979079285188</v>
+        <v>1.54041547205875</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09780251463448297</v>
+        <v>0.0979023634915393</v>
       </c>
       <c r="C96">
-        <v>-111.8169292528828</v>
+        <v>-126.1690774997562</v>
       </c>
       <c r="D96">
-        <v>818.2790707471173</v>
+        <v>816.7109225002439</v>
       </c>
       <c r="E96">
-        <v>386.796</v>
+        <v>399.5800000000002</v>
       </c>
       <c r="F96">
-        <v>1201.696</v>
+        <v>1214.48</v>
       </c>
       <c r="G96">
         <v>271.6</v>
@@ -9153,28 +9153,28 @@
         <v>166.6</v>
       </c>
       <c r="M96">
-        <v>108.15264</v>
+        <v>109.3032</v>
       </c>
       <c r="N96">
-        <v>58.44736</v>
+        <v>57.29679999999999</v>
       </c>
       <c r="O96">
-        <v>15.07941888</v>
+        <v>14.7825744</v>
       </c>
       <c r="P96">
-        <v>43.36794112</v>
+        <v>42.51422559999999</v>
       </c>
       <c r="Q96">
-        <v>100.76794112</v>
+        <v>99.91422559999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5838219105747166</v>
+        <v>0.6892272698307869</v>
       </c>
       <c r="T96">
-        <v>12.42544828117128</v>
+        <v>14.85975219008746</v>
       </c>
       <c r="U96">
         <v>0.09000000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.54041547205875</v>
+        <v>1.524200572352868</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0979023634915393</v>
+        <v>0.09800221234859563</v>
       </c>
       <c r="C97">
-        <v>-126.1690774997562</v>
+        <v>-140.5152268510615</v>
       </c>
       <c r="D97">
-        <v>816.7109225002439</v>
+        <v>815.1487731489385</v>
       </c>
       <c r="E97">
-        <v>399.5800000000002</v>
+        <v>412.364</v>
       </c>
       <c r="F97">
-        <v>1214.48</v>
+        <v>1227.264</v>
       </c>
       <c r="G97">
         <v>271.6</v>
@@ -9235,28 +9235,28 @@
         <v>166.6</v>
       </c>
       <c r="M97">
-        <v>109.3032</v>
+        <v>110.45376</v>
       </c>
       <c r="N97">
-        <v>57.29679999999999</v>
+        <v>56.14623999999999</v>
       </c>
       <c r="O97">
-        <v>14.7825744</v>
+        <v>14.48572992</v>
       </c>
       <c r="P97">
-        <v>42.51422559999999</v>
+        <v>41.66051007999999</v>
       </c>
       <c r="Q97">
-        <v>99.91422559999999</v>
+        <v>99.06051008</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6892272698307869</v>
+        <v>0.8473353087148924</v>
       </c>
       <c r="T97">
-        <v>14.85975219008746</v>
+        <v>18.51120805346172</v>
       </c>
       <c r="U97">
         <v>0.09000000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.524200572352868</v>
+        <v>1.508323483057525</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09800221234859566</v>
+        <v>0.1430036600019378</v>
       </c>
       <c r="C98">
-        <v>-140.5152268510619</v>
+        <v>-530.6808485288541</v>
       </c>
       <c r="D98">
-        <v>815.1487731489381</v>
+        <v>437.7671514711459</v>
       </c>
       <c r="E98">
-        <v>412.364</v>
+        <v>425.1479999999999</v>
       </c>
       <c r="F98">
-        <v>1227.264</v>
+        <v>1240.048</v>
       </c>
       <c r="G98">
         <v>271.6</v>
@@ -9317,45 +9317,45 @@
         <v>166.6</v>
       </c>
       <c r="M98">
-        <v>110.45376</v>
+        <v>182.0390464</v>
       </c>
       <c r="N98">
-        <v>56.14623999999999</v>
+        <v>-15.4390464</v>
       </c>
       <c r="O98">
-        <v>14.48572992</v>
+        <v>-3.983273971199999</v>
       </c>
       <c r="P98">
-        <v>41.66051007999999</v>
+        <v>-11.4557724288</v>
       </c>
       <c r="Q98">
-        <v>99.06051008</v>
+        <v>45.94422757120001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8473353087148904</v>
+        <v>1.14100001424899</v>
       </c>
       <c r="T98">
-        <v>18.51120805346167</v>
+        <v>25.2933028694917</v>
       </c>
       <c r="U98">
-        <v>0.09000000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.258</v>
+        <v>0.2361185737347392</v>
       </c>
       <c r="W98">
-        <v>0.06678000000000001</v>
+        <v>0.1121377933757403</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.508323483057525</v>
+        <v>0.9151882702896866</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1430036600019378</v>
+        <v>0.1440136600019378</v>
       </c>
       <c r="C99">
-        <v>-530.6808485288541</v>
+        <v>-547.9667154074241</v>
       </c>
       <c r="D99">
-        <v>437.7671514711459</v>
+        <v>433.2652845925761</v>
       </c>
       <c r="E99">
-        <v>425.1479999999999</v>
+        <v>437.932</v>
       </c>
       <c r="F99">
-        <v>1240.048</v>
+        <v>1252.832</v>
       </c>
       <c r="G99">
         <v>271.6</v>
@@ -9399,37 +9399,37 @@
         <v>166.6</v>
       </c>
       <c r="M99">
-        <v>182.0390464</v>
+        <v>183.9157376</v>
       </c>
       <c r="N99">
-        <v>-15.4390464</v>
+        <v>-17.31573760000001</v>
       </c>
       <c r="O99">
-        <v>-3.983273971199999</v>
+        <v>-4.467460300800002</v>
       </c>
       <c r="P99">
-        <v>-11.4557724288</v>
+        <v>-12.8482772992</v>
       </c>
       <c r="Q99">
-        <v>45.94422757120001</v>
+        <v>44.5517227008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.14100001424899</v>
+        <v>1.688600021373486</v>
       </c>
       <c r="T99">
-        <v>25.2933028694917</v>
+        <v>37.93995430423755</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2361185737347392</v>
+        <v>0.2337092005333642</v>
       </c>
       <c r="W99">
-        <v>0.1121377933757403</v>
+        <v>0.1124914893617021</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9151882702896866</v>
+        <v>0.905849614470404</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1440136600019378</v>
+        <v>0.1450236600019378</v>
       </c>
       <c r="C100">
-        <v>-547.9667154074241</v>
+        <v>-565.1609330654902</v>
       </c>
       <c r="D100">
-        <v>433.2652845925761</v>
+        <v>428.8550669345098</v>
       </c>
       <c r="E100">
-        <v>437.932</v>
+        <v>450.7159999999999</v>
       </c>
       <c r="F100">
-        <v>1252.832</v>
+        <v>1265.616</v>
       </c>
       <c r="G100">
         <v>271.6</v>
@@ -9481,37 +9481,37 @@
         <v>166.6</v>
       </c>
       <c r="M100">
-        <v>183.9157376</v>
+        <v>185.7924288</v>
       </c>
       <c r="N100">
-        <v>-17.31573760000001</v>
+        <v>-19.19242879999999</v>
       </c>
       <c r="O100">
-        <v>-4.467460300800002</v>
+        <v>-4.951646630399997</v>
       </c>
       <c r="P100">
-        <v>-12.8482772992</v>
+        <v>-14.24078216959999</v>
       </c>
       <c r="Q100">
-        <v>44.5517227008</v>
+        <v>43.15921783040002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.688600021373486</v>
+        <v>3.331400042746971</v>
       </c>
       <c r="T100">
-        <v>37.93995430423755</v>
+        <v>75.87990860847509</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2337092005333642</v>
+        <v>0.2313485015380778</v>
       </c>
       <c r="W100">
-        <v>0.1124914893617021</v>
+        <v>0.1128380399742102</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.905849614470404</v>
+        <v>0.8966996183646425</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1450236600019378</v>
-      </c>
-      <c r="C101">
-        <v>-565.1609330654902</v>
-      </c>
-      <c r="D101">
-        <v>428.8550669345098</v>
-      </c>
-      <c r="E101">
-        <v>450.7159999999999</v>
-      </c>
-      <c r="F101">
-        <v>1265.616</v>
-      </c>
-      <c r="G101">
-        <v>271.6</v>
-      </c>
-      <c r="H101">
-        <v>463.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>224</v>
-      </c>
-      <c r="K101">
-        <v>57.40000000000001</v>
-      </c>
-      <c r="L101">
-        <v>166.6</v>
-      </c>
-      <c r="M101">
-        <v>185.7924288</v>
-      </c>
-      <c r="N101">
-        <v>-19.19242879999999</v>
-      </c>
-      <c r="O101">
-        <v>-4.951646630399997</v>
-      </c>
-      <c r="P101">
-        <v>-14.24078216959999</v>
-      </c>
-      <c r="Q101">
-        <v>43.15921783040002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.331400042746971</v>
-      </c>
-      <c r="T101">
-        <v>75.87990860847509</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2313485015380778</v>
-      </c>
-      <c r="W101">
-        <v>0.1128380399742102</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8966996183646425</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
